--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,13 +1472,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1487,34 +1487,34 @@
         <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52</v>
+        <v>44.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>13.67</v>
+        <v>12.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BM2" t="n">
         <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU2" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY2" t="n">
         <v>2.26</v>
@@ -1610,136 +1610,136 @@
         <v>2.29</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.01</v>
+        <v>3.7</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CY2" t="n">
         <v>1.68</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DG2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>92.67</v>
+        <v>87</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.67</v>
+        <v>6.5</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.33</v>
+        <v>34.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DP2" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.33</v>
+        <v>7.25</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.33</v>
+        <v>50</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.67</v>
+        <v>13</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.67</v>
+        <v>9.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>20</v>
+        <v>18.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0.5</v>
@@ -1872,127 +1872,127 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>35.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
         <v>12</v>
       </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6</v>
-      </c>
       <c r="BB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4</v>
       </c>
-      <c r="BC3" t="n">
-        <v>2</v>
-      </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.66</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.67</v>
+        <v>10.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>2.34</v>
@@ -2013,55 +2013,55 @@
         <v>2.36</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CB3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CF3" t="n">
         <v>3.13</v>
       </c>
-      <c r="CC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>3.17</v>
-      </c>
       <c r="CG3" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="CR3" t="n">
         <v>1.5</v>
@@ -2076,10 +2076,10 @@
         <v>1.34</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX3" t="n">
         <v>1.5</v>
@@ -2097,85 +2097,85 @@
         <v>1.41</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="DH3" t="n">
-        <v>84</v>
+        <v>87.5</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>28.33</v>
+        <v>34.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.67</v>
+        <v>14.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47</v>
+        <v>50.5</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.67</v>
+        <v>14</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.67</v>
+        <v>9.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.67</v>
+        <v>23.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -3003,46 +3003,46 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>70.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>66</v>
+        <v>49.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48</v>
+        <v>43.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.01</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
@@ -3162,43 +3162,43 @@
         <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CC6" t="n">
         <v>3.25</v>
@@ -3234,34 +3234,34 @@
         <v>3.8</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CO6" t="n">
         <v>1.39</v>
@@ -3270,7 +3270,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="CR6" t="n">
         <v>1.49</v>
@@ -3285,10 +3285,10 @@
         <v>1.34</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3299,55 +3299,55 @@
         <v>2.17</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DH6" t="n">
-        <v>97.67</v>
+        <v>88.5</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.67</v>
+        <v>44.75</v>
       </c>
       <c r="DN6" t="n">
         <v>2</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DP6" t="n">
-        <v>18.33</v>
+        <v>17.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>12.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>53</v>
+        <v>49.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DX6" t="n">
-        <v>19.33</v>
+        <v>16.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.67</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3886,46 +3886,46 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>49</v>
+        <v>69.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -3949,19 +3949,19 @@
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -3973,37 +3973,37 @@
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.04</v>
@@ -4024,25 +4024,25 @@
         <v>2.11</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.12</v>
+        <v>3.61</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.03</v>
+        <v>4.26</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4060,37 +4060,37 @@
         <v>1.66</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CN8" t="n">
         <v>2.08</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4102,7 +4102,7 @@
         <v>2.5</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.38</v>
@@ -4111,49 +4111,49 @@
         <v>2.21</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>72.33</v>
+        <v>76.75</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DM8" t="n">
-        <v>9.67</v>
+        <v>10.25</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DP8" t="n">
         <v>13</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.67</v>
+        <v>17</v>
       </c>
       <c r="DR8" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.33</v>
+        <v>53.75</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.33</v>
+        <v>9.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.67</v>
+        <v>6.25</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="EA8" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>74</v>
+        <v>81.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="Q9" t="n">
         <v>19</v>
       </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
         <v>15</v>
       </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
       <c r="AD9" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>1.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
         <v>3</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.33</v>
+        <v>7.25</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="CC9" t="n">
         <v>5.59</v>
@@ -4442,117 +4442,121 @@
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CO9" t="n">
         <v>1.4</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CX9" t="inlineStr"/>
+        <v>2.11</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.55</v>
+      </c>
       <c r="CY9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CZ9" t="inlineStr"/>
+        <v>1.68</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.33</v>
+      </c>
       <c r="DA9" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DH9" t="n">
-        <v>70.33</v>
+        <v>75</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.33</v>
+        <v>23.75</v>
       </c>
       <c r="DN9" t="n">
         <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DP9" t="n">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.67</v>
+        <v>12.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>12.67</v>
+        <v>10.75</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4564,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>36.67</v>
+        <v>38</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.33</v>
+        <v>12.25</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.33</v>
+        <v>9.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>11.33</v>
+        <v>13.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4595,58 +4599,58 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>40</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P10" t="n">
         <v>12</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>67</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>9</v>
-      </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
@@ -4661,28 +4665,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4766,37 +4770,37 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4805,10 +4809,10 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4817,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
         <v>3.6</v>
@@ -4838,52 +4842,52 @@
         <v>3.24</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CK10" t="n">
         <v>1.4</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS10" t="n">
         <v>3.29</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CU10" t="n">
         <v>1.36</v>
@@ -4892,7 +4896,7 @@
         <v>1.8</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX10" t="n">
         <v>1.55</v>
@@ -4904,91 +4908,91 @@
         <v>2.38</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB10" t="n">
         <v>1.39</v>
       </c>
       <c r="DC10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>101</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>14</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="EC10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>108.33</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>55.33</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -5401,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5494,124 +5498,124 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>96</v>
+        <v>99.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AL12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>4</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>49</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>58</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2.67</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5623,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY12" t="n">
         <v>1.8</v>
@@ -5632,136 +5636,136 @@
         <v>1.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.5</v>
+        <v>4.18</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.82</v>
+        <v>4.62</v>
       </c>
       <c r="CE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CR12" t="n">
         <v>1.41</v>
       </c>
-      <c r="CF12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="CS12" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="CX12" t="n">
         <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.93</v>
+        <v>3.78</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG12" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>101</v>
+        <v>101.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.67</v>
+        <v>5.5</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.67</v>
+        <v>42.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5773,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.33</v>
+        <v>55.5</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="13">
@@ -5804,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -5816,82 +5820,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>79</v>
+        <v>102.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>29</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5975,34 +5979,34 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
         <v>3</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>4</v>
@@ -6014,31 +6018,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CC13" t="n">
         <v>4.35</v>
@@ -6050,31 +6054,31 @@
         <v>1.4</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
         <v>1.31</v>
@@ -6083,37 +6087,37 @@
         <v>2.08</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
         <v>1.35</v>
@@ -6122,82 +6126,82 @@
         <v>2.12</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>30.67</v>
+        <v>40.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.67</v>
+        <v>6.25</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.67</v>
+        <v>49.25</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.33</v>
+        <v>12.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="EA13" t="n">
-        <v>12.67</v>
+        <v>14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14">
@@ -6207,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6297,130 +6301,130 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG14" t="n">
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>77</v>
+        <v>91.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>33.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>12</v>
       </c>
-      <c r="AT14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>35</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BE14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP14" t="n">
         <v>5</v>
       </c>
-      <c r="BD14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>7</v>
-      </c>
       <c r="BQ14" t="n">
-        <v>6.33</v>
+        <v>4.5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6429,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY14" t="n">
         <v>2.34</v>
@@ -6438,55 +6442,55 @@
         <v>2.61</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="CC14" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="CD14" t="n">
-        <v>7.38</v>
+        <v>4.8</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF14" t="n">
         <v>2.89</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CL14" t="n">
         <v>1.88</v>
       </c>
-      <c r="CJ14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1.87</v>
-      </c>
       <c r="CM14" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="CN14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP14" t="n">
         <v>2.01</v>
       </c>
-      <c r="CO14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CQ14" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6501,73 +6505,73 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="CX14" t="n">
         <v>1.51</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>6.33</v>
+        <v>4.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>107</v>
+        <v>106.75</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="DL14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.67</v>
+        <v>46.25</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56</v>
+        <v>56.75</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
@@ -6588,19 +6592,19 @@
         <v>18</v>
       </c>
       <c r="DY14" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.67</v>
+        <v>16.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15">
@@ -7013,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60</v>
+        <v>47.5</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7184,37 +7188,37 @@
         <v>1.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
@@ -7226,28 +7230,28 @@
         <v>100</v>
       </c>
       <c r="BU16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BV16" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX16" t="n">
         <v>100</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC16" t="n">
         <v>2.24</v>
@@ -7256,59 +7260,67 @@
         <v>2.43</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO16" t="n">
         <v>1.29</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="CR16" t="inlineStr"/>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="inlineStr"/>
+        <v>3.35</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.44</v>
+      </c>
       <c r="CV16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
         <v>1.44</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
@@ -7320,85 +7332,85 @@
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="DH16" t="n">
-        <v>69.33</v>
+        <v>70</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>31.33</v>
+        <v>35</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="DP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.33</v>
+        <v>14.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.33</v>
+        <v>7.75</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.67</v>
+        <v>45.25</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.67</v>
+        <v>6.75</v>
       </c>
       <c r="DZ16" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="EA16" t="n">
-        <v>15.67</v>
+        <v>14</v>
       </c>
       <c r="EB16" t="n">
         <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="17">
@@ -7408,94 +7420,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
         <v>15</v>
       </c>
-      <c r="Q17" t="n">
-        <v>9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>37</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18</v>
-      </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>7</v>
       </c>
       <c r="AC17" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7579,37 +7591,37 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>8</v>
+        <v>10.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ17" t="n">
         <v>1</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -7618,31 +7630,31 @@
         <v>100</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BV17" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="CC17" t="n">
         <v>6.55</v>
@@ -7654,40 +7666,40 @@
         <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="CO17" t="n">
         <v>1.32</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7702,69 +7714,69 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="DH17" t="n">
-        <v>87.67</v>
+        <v>85.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.33</v>
+        <v>4.25</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="DM17" t="n">
-        <v>20</v>
+        <v>21.75</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DP17" t="n">
-        <v>15.33</v>
+        <v>15</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7776,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.33</v>
+        <v>44.25</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.67</v>
+        <v>15.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>12</v>
+        <v>10.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="18">
@@ -8210,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8303,124 +8315,124 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4</v>
       </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3</v>
-      </c>
       <c r="BD19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="BF19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8432,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.94</v>
@@ -8444,22 +8456,22 @@
         <v>3.16</v>
       </c>
       <c r="CB19" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC19" t="n">
         <v>3.15</v>
       </c>
-      <c r="CC19" t="n">
-        <v>3.45</v>
-      </c>
       <c r="CD19" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="CE19" t="n">
         <v>1.48</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CH19" t="n">
         <v>1.3</v>
@@ -8471,139 +8483,139 @@
         <v>1.94</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
         <v>2.29</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="CU19" t="n">
         <v>1.34</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CX19" t="n">
         <v>1.56</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.64</v>
+        <v>4.56</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>78.67</v>
+        <v>83.5</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="DN19" t="n">
         <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.33</v>
+        <v>14.25</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.33</v>
+        <v>11</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.67</v>
+        <v>51.75</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>11.67</v>
+        <v>13.75</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1679,16 +1679,16 @@
         <v>1.97</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY2" t="n">
         <v>1.68</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DB2" t="n">
         <v>1.37</v>
@@ -6108,16 +6108,16 @@
         <v>1.91</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="DB13" t="n">
         <v>1.35</v>
@@ -6307,7 +6307,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
         <v>91.5</v>
@@ -6322,7 +6322,7 @@
         <v>7.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
         <v>33.5</v>
@@ -6331,7 +6331,7 @@
         <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>15.5</v>
@@ -6409,10 +6409,10 @@
         <v>1.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -6538,7 +6538,7 @@
         <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="DH14" t="n">
         <v>106.75</v>
@@ -6553,7 +6553,7 @@
         <v>11</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DM14" t="n">
         <v>46.25</v>
@@ -6562,7 +6562,7 @@
         <v>0.25</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="DP14" t="n">
         <v>13.75</v>
@@ -7089,10 +7089,10 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB16" t="n">
         <v>7</v>
@@ -7101,7 +7101,7 @@
         <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -7395,10 +7395,10 @@
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="DZ16" t="n">
         <v>6.75</v>
@@ -7407,7 +7407,7 @@
         <v>14</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="EC16" t="n">
         <v>1.75</v>
@@ -7435,7 +7435,7 @@
         <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
         <v>84</v>
@@ -7450,7 +7450,7 @@
         <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>20</v>
@@ -7459,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
         <v>14.5</v>
@@ -7492,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AB17" t="n">
         <v>7</v>
@@ -7504,7 +7504,7 @@
         <v>20.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
         <v>3.5</v>
@@ -7618,10 +7618,10 @@
         <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -7743,7 +7743,7 @@
         <v>2.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
         <v>85.5</v>
@@ -7758,7 +7758,7 @@
         <v>4.25</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
         <v>21.75</v>
@@ -7767,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
         <v>15</v>
@@ -7794,10 +7794,10 @@
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.25</v>
@@ -7806,7 +7806,7 @@
         <v>17.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
         <v>3.25</v>
@@ -7819,94 +7819,94 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>102</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>19</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE18" t="n">
         <v>3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>115</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>18</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>21</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7990,37 +7990,37 @@
         <v>3</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BJ18" t="n">
         <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
@@ -8029,31 +8029,31 @@
         <v>100</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX18" t="n">
         <v>100</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="CC18" t="n">
         <v>2.95</v>
@@ -8065,40 +8065,40 @@
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="CN18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP18" t="n">
         <v>2.12</v>
       </c>
-      <c r="CO18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>2.17</v>
-      </c>
       <c r="CQ18" t="n">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
@@ -8113,10 +8113,10 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
@@ -8128,91 +8128,91 @@
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>33</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>23</v>
+      </c>
+      <c r="EB18" t="n">
         <v>1.42</v>
       </c>
-      <c r="DC18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DD18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG18" t="n">
+      <c r="EC18" t="n">
         <v>3</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>117.67</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>29</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="EA18" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="EB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="EC18" t="n">
-        <v>3.67</v>
       </c>
     </row>
     <row r="19">
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>3</v>
@@ -8327,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>5.5</v>
@@ -8390,7 +8390,7 @@
         <v>0.97</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
         <v>2</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DG19" t="n">
         <v>2.5</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="DK19" t="n">
         <v>4</v>
@@ -8615,7 +8615,7 @@
         <v>1.23</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="20">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8718,13 +8718,13 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -8733,109 +8733,109 @@
         <v>1</v>
       </c>
       <c r="AL20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>32.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD20" t="n">
         <v>16</v>
       </c>
-      <c r="AS20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>53</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>13</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BF20" t="n">
         <v>1</v>
       </c>
       <c r="BG20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BH20" t="n">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="BI20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BN20" t="n">
         <v>1</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT20" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
@@ -8847,7 +8847,7 @@
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY20" t="n">
         <v>1.92</v>
@@ -8856,28 +8856,28 @@
         <v>1.94</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CB20" t="n">
         <v>3.55</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CI20" t="n">
         <v>1.92</v>
@@ -8886,19 +8886,19 @@
         <v>1.8</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP20" t="n">
         <v>1.95</v>
@@ -8928,13 +8928,13 @@
         <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.13</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DB20" t="n">
         <v>1.31</v>
@@ -8943,49 +8943,49 @@
         <v>2</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="DH20" t="n">
-        <v>114.67</v>
+        <v>111.75</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DK20" t="n">
-        <v>9</v>
+        <v>7.25</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>46.33</v>
+        <v>47.5</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DO20" t="n">
-        <v>5.67</v>
+        <v>4.5</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.67</v>
+        <v>14.25</v>
       </c>
       <c r="DQ20" t="n">
-        <v>13.67</v>
+        <v>15</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8997,28 +8997,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>60.67</v>
+        <v>60.5</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>23</v>
+        <v>21.25</v>
       </c>
       <c r="DY20" t="n">
-        <v>15.67</v>
+        <v>15.25</v>
       </c>
       <c r="DZ20" t="n">
-        <v>7.33</v>
+        <v>6</v>
       </c>
       <c r="EA20" t="n">
-        <v>15.67</v>
+        <v>16.5</v>
       </c>
       <c r="EB20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,40 +1379,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="H2" t="n">
-        <v>95</v>
+        <v>85.67</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>29.33</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1421,19 +1421,19 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.5</v>
+        <v>48.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="BZ2" t="n">
         <v>2.29</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC2" t="n">
         <v>3.34</v>
@@ -1622,124 +1622,124 @@
         <v>3.7</v>
       </c>
       <c r="CE2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CK2" t="n">
         <v>1.43</v>
       </c>
-      <c r="CF2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CH2" t="n">
+      <c r="CL2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DB2" t="n">
         <v>1.36</v>
       </c>
-      <c r="CI2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.37</v>
-      </c>
       <c r="DC2" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="DH2" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.5</v>
+        <v>32.4</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.5</v>
+        <v>16.4</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.25</v>
+        <v>8.6</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.25</v>
+        <v>17.6</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -2197,43 +2197,43 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>110</v>
+        <v>113.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42</v>
+        <v>52.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2359,43 +2359,43 @@
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.31</v>
+        <v>3.39</v>
       </c>
       <c r="CC4" t="n">
         <v>2.99</v>
@@ -2431,7 +2431,7 @@
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG4" t="n">
         <v>2.83</v>
@@ -2440,22 +2440,22 @@
         <v>1.39</v>
       </c>
       <c r="CI4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
         <v>1.29</v>
@@ -2464,13 +2464,13 @@
         <v>1.98</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
         <v>3.03</v>
@@ -2479,58 +2479,58 @@
         <v>1.42</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="CW4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
         <v>1.75</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>2.33</v>
-      </c>
       <c r="DG4" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.33</v>
+        <v>98.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DM4" t="n">
-        <v>29</v>
+        <v>28.25</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
@@ -2539,46 +2539,46 @@
         <v>4</v>
       </c>
       <c r="DP4" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.67</v>
+        <v>14.75</v>
       </c>
       <c r="DR4" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.33</v>
+        <v>46</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.67</v>
+        <v>12.75</v>
       </c>
       <c r="DY4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.67</v>
+        <v>20.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>97.33</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
         <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.5</v>
+        <v>64</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>13.67</v>
       </c>
       <c r="AA8" t="n">
         <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>18.5</v>
+        <v>19.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3967,43 +3967,43 @@
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="CC8" t="n">
         <v>3.61</v>
@@ -4036,61 +4036,61 @@
         <v>4.26</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN8" t="n">
         <v>2.08</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP8" t="n">
         <v>2.17</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU8" t="n">
         <v>1.34</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4108,52 +4108,52 @@
         <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="DH8" t="n">
-        <v>76.75</v>
+        <v>86.2</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>10.25</v>
+        <v>23</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.75</v>
+        <v>7.8</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.75</v>
+        <v>57.6</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.75</v>
+        <v>19.4</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4289,49 +4289,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>68.5</v>
+        <v>63.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.5</v>
+        <v>9.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4343,82 +4343,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>40.5</v>
+        <v>36</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>15.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
         <v>2.45</v>
@@ -4427,55 +4427,55 @@
         <v>2.68</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.59</v>
+        <v>5.73</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.56</v>
+        <v>6.47</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CK9" t="n">
         <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="CR9" t="n">
         <v>1.48</v>
@@ -4484,79 +4484,79 @@
         <v>3.36</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU9" t="n">
         <v>1.35</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DH9" t="n">
-        <v>75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DP9" t="n">
-        <v>8.75</v>
+        <v>10.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.75</v>
+        <v>13.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.75</v>
+        <v>10.4</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.25</v>
+        <v>10.6</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="EA9" t="n">
-        <v>13.5</v>
+        <v>15.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
         <v>2</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -4692,61 +4692,61 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>88</v>
+        <v>89.33</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK10" t="n">
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>37.5</v>
+        <v>35.67</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.5</v>
+        <v>13.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49</v>
+        <v>51.33</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -4761,46 +4761,46 @@
         <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.5</v>
+        <v>21.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF10" t="n">
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4809,10 +4809,10 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.62</v>
@@ -4830,55 +4830,55 @@
         <v>1.56</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.24</v>
+        <v>4.31</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4893,106 +4893,106 @@
         <v>1.36</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="DH10" t="n">
-        <v>101</v>
+        <v>99.2</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.75</v>
+        <v>37.4</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="DY10" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -5002,25 +5002,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>156</v>
+        <v>116.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -5032,61 +5032,61 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>65</v>
+        <v>54.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5173,37 +5173,37 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5212,7 +5212,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5224,19 +5224,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="CC11" t="n">
         <v>1.88</v>
@@ -5245,43 +5245,43 @@
         <v>1.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI11" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="CR11" t="n">
         <v>1.48</v>
@@ -5296,103 +5296,103 @@
         <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DH11" t="n">
-        <v>129.33</v>
+        <v>116.25</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.33</v>
+        <v>47</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="DP11" t="n">
         <v>17</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.67</v>
+        <v>17.25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6301,52 +6301,52 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>5.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>91.5</v>
+        <v>105.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>7.5</v>
+        <v>9.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>33.5</v>
+        <v>43</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.5</v>
+        <v>16.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>17.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,73 +6358,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.5</v>
+        <v>15.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.5</v>
+        <v>5.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>15.67</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>2.34</v>
@@ -6442,22 +6442,22 @@
         <v>2.61</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="CC14" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.8</v>
+        <v>4.29</v>
       </c>
       <c r="CE14" t="n">
         <v>1.39</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CG14" t="n">
         <v>2.76</v>
@@ -6466,112 +6466,112 @@
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CK14" t="n">
         <v>1.48</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CV14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA14" t="n">
         <v>2.03</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>2.06</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD14" t="n">
         <v>3.36</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DG14" t="n">
-        <v>5.75</v>
+        <v>6.6</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.75</v>
+        <v>112.2</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DK14" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.25</v>
+        <v>49.4</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DO14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.75</v>
+        <v>14.6</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.75</v>
+        <v>14.2</v>
       </c>
       <c r="DR14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.75</v>
+        <v>58.4</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.5</v>
+        <v>17.8</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -6614,11 +6614,11 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
@@ -6626,46 +6626,46 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>85.5</v>
+        <v>84.67</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M15" t="n">
-        <v>42.5</v>
+        <v>41.67</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>11.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5</v>
+        <v>5.67</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -6680,28 +6680,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.5</v>
+        <v>52.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.5</v>
+        <v>17.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6785,37 +6785,37 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6827,7 +6827,7 @@
         <v>100</v>
       </c>
       <c r="BU15" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6839,16 +6839,16 @@
         <v>100</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.24</v>
+        <v>3.37</v>
       </c>
       <c r="CC15" t="n">
         <v>2.6</v>
@@ -6857,43 +6857,43 @@
         <v>2.53</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="CH15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CO15" t="n">
         <v>1.33</v>
       </c>
-      <c r="CI15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP15" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="CR15" t="n">
         <v>1.46</v>
@@ -6908,22 +6908,22 @@
         <v>1.36</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
         <v>1.38</v>
@@ -6938,43 +6938,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.67</v>
+        <v>87.25</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DK15" t="n">
         <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.67</v>
+        <v>36</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.33</v>
+        <v>11</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.67</v>
+        <v>10.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.67</v>
+        <v>6.25</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.33</v>
+        <v>55</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.67</v>
+        <v>15.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.67</v>
+        <v>7.25</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.33</v>
+        <v>20.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7912,115 +7912,115 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>119</v>
+        <v>113.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AN18" t="n">
-        <v>34.5</v>
+        <v>37.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
         <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD18" t="n">
-        <v>26.5</v>
+        <v>24.67</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BF18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.75</v>
+        <v>11.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ18" t="n">
         <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
@@ -8029,16 +8029,16 @@
         <v>100</v>
       </c>
       <c r="BT18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX18" t="n">
         <v>100</v>
@@ -8050,55 +8050,55 @@
         <v>2.22</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.47</v>
+        <v>3.98</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
@@ -8113,22 +8113,22 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="DB18" t="n">
         <v>1.4</v>
@@ -8143,76 +8143,76 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>110.5</v>
+        <v>108.8</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="DK18" t="n">
         <v>7</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DO18" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.75</v>
+        <v>14.2</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.75</v>
+        <v>14.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="EA18" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -9028,13 +9028,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9121,47 +9121,47 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT21" t="n">
         <v>3</v>
       </c>
-      <c r="AH21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5</v>
-      </c>
       <c r="AU21" t="n">
         <v>1</v>
       </c>
@@ -9175,61 +9175,61 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="BF21" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BH21" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BJ21" t="n">
         <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BN21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9238,19 +9238,19 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU21" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW21" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX21" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY21" t="n">
         <v>3.5</v>
@@ -9259,46 +9259,46 @@
         <v>3.9</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="CC21" t="n">
-        <v>7.75</v>
+        <v>6.1</v>
       </c>
       <c r="CD21" t="n">
-        <v>10.32</v>
+        <v>7.8</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CH21" t="n">
         <v>1.38</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CO21" t="n">
         <v>1.28</v>
@@ -9307,88 +9307,88 @@
         <v>2.01</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC21" t="n">
         <v>2.06</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DG21" t="n">
         <v>3</v>
       </c>
       <c r="DH21" t="n">
-        <v>83</v>
+        <v>81.75</v>
       </c>
       <c r="DI21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DJ21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="DL21" t="n">
         <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>34.67</v>
+        <v>27.75</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DO21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="DQ21" t="n">
-        <v>16.67</v>
+        <v>16.75</v>
       </c>
       <c r="DR21" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="DS21" t="n">
         <v>0</v>
@@ -9400,28 +9400,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>42</v>
+        <v>40.75</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>13</v>
+        <v>11.25</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="EA21" t="n">
-        <v>23</v>
+        <v>20.75</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="EC21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1607,13 +1607,13 @@
         <v>2.27</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="CA2" t="n">
         <v>3.43</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC2" t="n">
         <v>3.34</v>
@@ -1667,7 +1667,7 @@
         <v>3.08</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU2" t="n">
         <v>1.4</v>
@@ -1682,22 +1682,22 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="DE2" t="n">
         <v>0.2</v>
@@ -2419,7 +2419,7 @@
         <v>3.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CC4" t="n">
         <v>2.99</v>
@@ -2467,13 +2467,13 @@
         <v>3.32</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CU4" t="n">
         <v>1.42</v>
@@ -2482,7 +2482,7 @@
         <v>2.08</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
@@ -2500,10 +2500,10 @@
         <v>1.31</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>106.5</v>
+        <v>111.33</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>42.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21.5</v>
+        <v>18.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,67 +3138,67 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>55.5</v>
+        <v>57.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>19.5</v>
+        <v>19.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>20.67</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>2.18</v>
@@ -3222,132 +3222,136 @@
         <v>2.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CC6" t="n">
         <v>3.25</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="CE6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="CR6" t="n">
         <v>1.46</v>
       </c>
-      <c r="CF6" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CK6" t="n">
+      <c r="CS6" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CU6" t="n">
         <v>1.36</v>
       </c>
-      <c r="CL6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="CR6" t="n">
+      <c r="CV6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CX6" t="n">
         <v>1.49</v>
       </c>
-      <c r="CS6" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CZ6" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="DA6" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.49</v>
+        <v>4.32</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.5</v>
+        <v>95</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.75</v>
+        <v>45.4</v>
       </c>
       <c r="DN6" t="n">
         <v>2</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.75</v>
+        <v>16.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.25</v>
+        <v>12.4</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.5</v>
+        <v>51.8</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.25</v>
+        <v>17</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="EC6" t="n">
         <v>4</v>
@@ -3390,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3486,46 +3490,46 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>57</v>
+        <v>62.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3537,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -3552,46 +3556,46 @@
         <v>1</v>
       </c>
       <c r="BD7" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="n">
-        <v>13.33</v>
+        <v>14.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
         <v>2</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>8.67</v>
+        <v>8.75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3600,19 +3604,19 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BW7" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BX7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY7" t="n">
         <v>2.6</v>
@@ -3621,55 +3625,55 @@
         <v>2.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.55</v>
+        <v>6.78</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.68</v>
+        <v>7.8</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN7" t="n">
         <v>2.05</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
       <c r="CR7" t="n">
         <v>1.46</v>
@@ -3684,10 +3688,10 @@
         <v>1.36</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX7" t="n">
         <v>1.51</v>
@@ -3702,88 +3706,88 @@
         <v>2.06</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.96</v>
+        <v>3.69</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.33</v>
+        <v>9.25</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>39.33</v>
+        <v>38.75</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.67</v>
+        <v>7.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>17</v>
+        <v>20.75</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -3838,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>18.67</v>
       </c>
       <c r="R8" t="n">
         <v>4.67</v>
@@ -4021,13 +4025,13 @@
         <v>1.88</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CA8" t="n">
         <v>3.36</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CC8" t="n">
         <v>3.61</v>
@@ -4078,7 +4082,7 @@
         <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CT8" t="n">
         <v>2.75</v>
@@ -4090,7 +4094,7 @@
         <v>1.89</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4111,7 +4115,7 @@
         <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
@@ -4150,7 +4154,7 @@
         <v>13.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="DR8" t="n">
         <v>7.8</v>
@@ -4430,13 +4434,13 @@
         <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CC9" t="n">
         <v>5.73</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.47</v>
+        <v>6.31</v>
       </c>
       <c r="CE9" t="n">
         <v>1.47</v>
@@ -4484,37 +4488,37 @@
         <v>3.36</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU9" t="n">
         <v>1.35</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4833,13 +4837,13 @@
         <v>3.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CC10" t="n">
         <v>3.72</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.31</v>
+        <v>4.67</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
@@ -4881,31 +4885,31 @@
         <v>3.59</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA10" t="n">
         <v>2.05</v>
@@ -4917,7 +4921,7 @@
         <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="DE10" t="n">
         <v>0.2</v>
@@ -5230,13 +5234,13 @@
         <v>1.44</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="CA11" t="n">
         <v>3.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CC11" t="n">
         <v>1.88</v>
@@ -5284,43 +5288,43 @@
         <v>3.59</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CX11" t="n">
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="DE11" t="n">
         <v>0.25</v>
@@ -5405,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5498,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>99.5</v>
+        <v>106.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5552,19 +5556,19 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>61.5</v>
+        <v>63.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.5</v>
+        <v>15.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>13</v>
@@ -5573,49 +5577,49 @@
         <v>1.74</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5627,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>1.8</v>
@@ -5636,55 +5640,55 @@
         <v>1.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.18</v>
+        <v>3.42</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.62</v>
+        <v>3.72</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF12" t="n">
         <v>2.84</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="CR12" t="n">
         <v>1.41</v>
@@ -5699,73 +5703,73 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CW12" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
         <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>101.5</v>
+        <v>105.4</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="DP12" t="n">
         <v>14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5777,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.5</v>
+        <v>57.8</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.75</v>
+        <v>13.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.25</v>
+        <v>15.6</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5808,91 +5812,91 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>102.5</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>50</v>
+        <v>42.33</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>5.67</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53</v>
+        <v>48.33</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -5979,34 +5983,34 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP13" t="n">
         <v>4</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>4</v>
@@ -6018,19 +6022,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY13" t="n">
         <v>2.22</v>
@@ -6039,10 +6043,10 @@
         <v>2.34</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CC13" t="n">
         <v>4.35</v>
@@ -6051,19 +6055,19 @@
         <v>5.23</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CH13" t="n">
         <v>1.36</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.8</v>
@@ -6072,28 +6076,28 @@
         <v>1.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.31</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
         <v>2.92</v>
@@ -6102,22 +6106,22 @@
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA13" t="n">
         <v>1.93</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB13" t="n">
         <v>1.35</v>
@@ -6126,82 +6130,82 @@
         <v>2.12</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH13" t="n">
-        <v>93</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.75</v>
+        <v>38</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.25</v>
+        <v>7.6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.25</v>
+        <v>47.2</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.25</v>
+        <v>12.4</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="EA13" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -6334,7 +6338,7 @@
         <v>4.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>17.33</v>
@@ -6445,13 +6449,13 @@
         <v>3.55</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
         <v>4.33</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.29</v>
+        <v>4.46</v>
       </c>
       <c r="CE14" t="n">
         <v>1.39</v>
@@ -6493,43 +6497,43 @@
         <v>3.23</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW14" t="n">
         <v>1.84</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY14" t="n">
         <v>1.75</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB14" t="n">
         <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DE14" t="n">
         <v>0.2</v>
@@ -6565,7 +6569,7 @@
         <v>5</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="DQ14" t="n">
         <v>14.2</v>
@@ -6656,7 +6660,7 @@
         <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>9</v>
@@ -6968,7 +6972,7 @@
         <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="DQ15" t="n">
         <v>10.5</v>
@@ -7017,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -7110,28 +7114,28 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>62</v>
+        <v>68.33</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>27.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -7140,19 +7144,19 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>15.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7164,61 +7168,61 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43</v>
+        <v>45.33</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>10.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.5</v>
+        <v>5.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>15</v>
+        <v>15.67</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BP16" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
@@ -7230,13 +7234,13 @@
         <v>100</v>
       </c>
       <c r="BU16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX16" t="n">
         <v>100</v>
@@ -7248,40 +7252,40 @@
         <v>1.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CE16" t="n">
         <v>1.4</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CM16" t="n">
         <v>2.6</v>
@@ -7293,124 +7297,124 @@
         <v>1.29</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CX16" t="n">
         <v>1.44</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="DH16" t="n">
-        <v>70</v>
+        <v>72.2</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DM16" t="n">
-        <v>35</v>
+        <v>33.2</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DP16" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.5</v>
+        <v>12.8</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.25</v>
+        <v>46.2</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.75</v>
+        <v>12.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="EA16" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17">
@@ -7420,61 +7424,61 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H17" t="n">
-        <v>84</v>
+        <v>83.67</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.5</v>
+        <v>12.33</v>
       </c>
       <c r="R17" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7486,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7591,37 +7595,37 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BM17" t="n">
         <v>1</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP17" t="n">
         <v>5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -7630,31 +7634,31 @@
         <v>100</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX17" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.78</v>
+        <v>3.17</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.22</v>
+        <v>3.53</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC17" t="n">
         <v>6.55</v>
@@ -7663,43 +7667,43 @@
         <v>6.38</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF17" t="n">
         <v>2.86</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7714,10 +7718,10 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
@@ -7725,58 +7729,58 @@
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="DH17" t="n">
-        <v>85.5</v>
+        <v>85</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DM17" t="n">
-        <v>21.75</v>
+        <v>25</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.75</v>
+        <v>12.2</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7788,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.25</v>
+        <v>42</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.25</v>
+        <v>14.2</v>
       </c>
       <c r="DY17" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8222,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -8234,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>79</v>
+        <v>87.67</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>5.33</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>43.5</v>
+        <v>43.67</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5</v>
+        <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>10.5</v>
+        <v>11.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="T19" t="n">
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>49.5</v>
+        <v>54</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>15.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.5</v>
+        <v>10.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8396,43 +8400,43 @@
         <v>2</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.75</v>
+        <v>10.4</v>
       </c>
       <c r="BI19" t="n">
         <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8444,19 +8448,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.94</v>
+        <v>2.42</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.13</v>
+        <v>3.47</v>
       </c>
       <c r="CC19" t="n">
         <v>3.15</v>
@@ -8465,16 +8469,16 @@
         <v>3.3</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="CI19" t="n">
         <v>1.77</v>
@@ -8483,25 +8487,25 @@
         <v>1.94</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.18</v>
+        <v>3.94</v>
       </c>
       <c r="CR19" t="n">
         <v>1.53</v>
@@ -8534,88 +8538,88 @@
         <v>1.94</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.56</v>
+        <v>4.23</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.5</v>
+        <v>87.8</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DK19" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="DL19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DM19" t="n">
-        <v>32</v>
+        <v>34.4</v>
       </c>
       <c r="DN19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.75</v>
+        <v>54</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.25</v>
+        <v>12.6</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="EA19" t="n">
-        <v>13.75</v>
+        <v>13.6</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20">
@@ -8625,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G20" t="n">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H20" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>62.5</v>
+        <v>59.67</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O20" t="n">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="P20" t="n">
-        <v>15.5</v>
+        <v>12.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>12.5</v>
+        <v>14.33</v>
       </c>
       <c r="R20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8691,25 +8695,25 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>64.5</v>
+        <v>59.67</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>24.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.5</v>
+        <v>16.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.5</v>
+        <v>7.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="n">
         <v>2</v>
@@ -8796,46 +8800,46 @@
         <v>1</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.75</v>
+        <v>11.4</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BN20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
@@ -8847,19 +8851,19 @@
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="CA20" t="n">
         <v>3.41</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="CC20" t="n">
         <v>3.92</v>
@@ -8871,121 +8875,121 @@
         <v>1.4</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO20" t="n">
         <v>1.29</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ20" t="n">
         <v>3.39</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CX20" t="n">
         <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.13</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="DB20" t="n">
         <v>1.31</v>
       </c>
       <c r="DC20" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="DH20" t="n">
-        <v>111.75</v>
+        <v>115</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DK20" t="n">
-        <v>7.25</v>
+        <v>7.6</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="DM20" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DO20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.25</v>
+        <v>12.6</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8997,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>60.5</v>
+        <v>58.4</v>
       </c>
       <c r="DW20" t="n">
         <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>21.25</v>
+        <v>20.4</v>
       </c>
       <c r="DY20" t="n">
-        <v>15.25</v>
+        <v>14.4</v>
       </c>
       <c r="DZ20" t="n">
         <v>6</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="EB20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -9268,7 +9272,7 @@
         <v>6.1</v>
       </c>
       <c r="CD21" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="CE21" t="n">
         <v>1.37</v>
@@ -9310,13 +9314,13 @@
         <v>3.4</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CU21" t="n">
         <v>1.38</v>
@@ -9325,7 +9329,7 @@
         <v>1.78</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX21" t="n">
         <v>1.59</v>
@@ -9343,10 +9347,10 @@
         <v>1.33</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>79</v>
+        <v>90.67</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>37</v>
+        <v>44.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.5</v>
+        <v>8.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>14</v>
+        <v>15.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.5</v>
+        <v>5.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.5</v>
+        <v>52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>17</v>
+        <v>20.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BH2" t="n">
-        <v>13.2</v>
+        <v>13.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.8</v>
+        <v>6.67</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>2.27</v>
@@ -1610,73 +1610,73 @@
         <v>2.23</v>
       </c>
       <c r="CA2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CB2" t="n">
         <v>3.43</v>
       </c>
-      <c r="CB2" t="n">
-        <v>3.51</v>
-      </c>
       <c r="CC2" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CH2" t="n">
         <v>1.37</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK2" t="n">
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM2" t="n">
         <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CX2" t="n">
         <v>1.46</v>
@@ -1691,55 +1691,55 @@
         <v>2.11</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.8</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>83</v>
+        <v>88.17</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.6</v>
+        <v>6.33</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0.16</v>
       </c>
       <c r="DM2" t="n">
-        <v>32.4</v>
+        <v>37</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.4</v>
+        <v>16.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.6</v>
+        <v>7.84</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47</v>
+        <v>50.34</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.8</v>
+        <v>11.84</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="EA2" t="n">
-        <v>17.6</v>
+        <v>19.34</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0.5</v>
@@ -1872,52 +1872,52 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>35.5</v>
+        <v>28.67</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>23.5</v>
+        <v>20.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>2.34</v>
@@ -2013,67 +2013,67 @@
         <v>2.36</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.1</v>
+        <v>4.39</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV3" t="n">
         <v>1.86</v>
@@ -2082,100 +2082,100 @@
         <v>1.98</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="DH3" t="n">
-        <v>87.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>34.5</v>
+        <v>30.6</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.5</v>
+        <v>44.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.5</v>
+        <v>21.6</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,124 +2278,124 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>83.5</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.5</v>
+        <v>21.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>15.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.5</v>
+        <v>42</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.5</v>
+        <v>8.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.5</v>
+        <v>20.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>1.95</v>
@@ -2416,73 +2416,73 @@
         <v>1.96</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF4" t="n">
         <v>2.78</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="CH4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CR4" t="n">
         <v>1.39</v>
       </c>
-      <c r="CI4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="CS4" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
@@ -2497,88 +2497,88 @@
         <v>1.93</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH4" t="n">
-        <v>98.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DM4" t="n">
-        <v>28.25</v>
+        <v>26.2</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.75</v>
+        <v>15</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.75</v>
+        <v>15.8</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.25</v>
+        <v>9.4</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.75</v>
+        <v>11.6</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.5</v>
+        <v>19.6</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>62</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>28</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
         <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP5" t="n">
         <v>3</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>3.67</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.45</v>
+        <v>3.46</v>
       </c>
       <c r="CA5" t="n">
         <v>3.15</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CC5" t="n">
         <v>3.8</v>
@@ -2834,49 +2834,49 @@
         <v>1.48</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM5" t="n">
         <v>2.46</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="CR5" t="n">
         <v>1.48</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU5" t="n">
         <v>1.35</v>
@@ -2888,16 +2888,16 @@
         <v>2</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
         <v>1.42</v>
@@ -2906,7 +2906,7 @@
         <v>2.32</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2915,40 +2915,40 @@
         <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DH5" t="n">
-        <v>75</v>
+        <v>74.75</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>19.33</v>
+        <v>16.75</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.33</v>
+        <v>13.25</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.67</v>
+        <v>49.25</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="EA5" t="n">
-        <v>14.67</v>
+        <v>16</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -3003,13 +3003,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>70.5</v>
+        <v>75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3018,31 +3018,31 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>49.5</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.5</v>
+        <v>45.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z6" t="n">
         <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>17</v>
+        <v>19.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,46 +3162,46 @@
         <v>4.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC6" t="n">
         <v>3.25</v>
@@ -3234,13 +3234,13 @@
         <v>3.63</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CH6" t="n">
         <v>1.32</v>
@@ -3252,106 +3252,106 @@
         <v>1.9</v>
       </c>
       <c r="CK6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CO6" t="n">
         <v>1.38</v>
       </c>
-      <c r="CL6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.37</v>
-      </c>
       <c r="CP6" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="CU6" t="n">
         <v>1.36</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX6" t="n">
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
         <v>2.33</v>
       </c>
-      <c r="DD6" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>2.4</v>
-      </c>
       <c r="DG6" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="DH6" t="n">
-        <v>95</v>
+        <v>93.16</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>45.4</v>
+        <v>38.84</v>
       </c>
       <c r="DN6" t="n">
         <v>2</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.6</v>
+        <v>14.66</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DX6" t="n">
-        <v>17</v>
+        <v>16.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
         <v>4</v>
@@ -3517,7 +3517,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="DQ7" t="n">
         <v>10</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,46 +3890,46 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>69.5</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.5</v>
+        <v>17.33</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,70 +3944,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48</v>
+        <v>50.67</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4</v>
       </c>
-      <c r="BB8" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BC8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BD8" t="n">
         <v>19</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.88</v>
@@ -4028,43 +4028,43 @@
         <v>1.96</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.61</v>
+        <v>3.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.26</v>
+        <v>3.85</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CN8" t="n">
         <v>2.08</v>
@@ -4073,22 +4073,22 @@
         <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV8" t="n">
         <v>1.89</v>
@@ -4100,19 +4100,19 @@
         <v>1.49</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.5</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD8" t="n">
         <v>4.07</v>
@@ -4121,43 +4121,43 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.2</v>
+        <v>84.66</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.2</v>
+        <v>17.67</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.8</v>
+        <v>7.84</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.6</v>
+        <v>57.34</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DY8" t="n">
         <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.4</v>
+        <v>19.34</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>81.5</v>
+        <v>71.33</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>22.33</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="P9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>16.33</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>11.67</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>35.5</v>
+        <v>37.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>11.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,67 +4371,67 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BH9" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
         <v>3.53</v>
@@ -4443,43 +4443,43 @@
         <v>6.31</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="CR9" t="n">
         <v>1.48</v>
@@ -4494,73 +4494,73 @@
         <v>1.35</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.43</v>
+        <v>4.24</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>70.59999999999999</v>
+        <v>67.33</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>24</v>
+        <v>26.17</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.2</v>
+        <v>12.83</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.4</v>
+        <v>11.17</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,22 +4572,22 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>35.8</v>
+        <v>36.84</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="DY9" t="n">
-        <v>8</v>
+        <v>7.34</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="EB9" t="n">
         <v>1.03</v>
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="H10" t="n">
-        <v>114</v>
+        <v>106.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="K10" t="n">
-        <v>8.5</v>
+        <v>7.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>30.67</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>8.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58</v>
+        <v>58.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>16.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.5</v>
+        <v>12.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.4</v>
+        <v>10.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
         <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>6.17</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="CC10" t="n">
         <v>3.72</v>
@@ -4849,31 +4849,31 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO10" t="n">
         <v>1.34</v>
@@ -4882,7 +4882,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4897,10 +4897,10 @@
         <v>1.37</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4921,82 +4921,82 @@
         <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="DH10" t="n">
-        <v>99.2</v>
+        <v>97.83</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.4</v>
+        <v>33.17</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="DO10" t="n">
         <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.8</v>
+        <v>10.17</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.2</v>
+        <v>13.66</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54</v>
+        <v>54.83</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.8</v>
+        <v>14.84</v>
       </c>
       <c r="DY10" t="n">
-        <v>10</v>
+        <v>10.66</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>19.16</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0.5</v>
@@ -5099,115 +5099,115 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>116</v>
+        <v>118.33</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>47</v>
+        <v>35.33</v>
       </c>
       <c r="AO11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AT11" t="n">
         <v>1</v>
       </c>
-      <c r="AP11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AU11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA11" t="n">
         <v>13</v>
       </c>
-      <c r="AS11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>20.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="BF11" t="n">
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5216,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>1.44</v>
@@ -5237,22 +5237,22 @@
         <v>1.46</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
         <v>2.75</v>
@@ -5261,142 +5261,142 @@
         <v>1.36</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN11" t="n">
         <v>1.87</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS11" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CX11" t="n">
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DH11" t="n">
-        <v>116.25</v>
+        <v>117.6</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>17</v>
+        <v>15.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56</v>
+        <v>56.4</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.75</v>
+        <v>9.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.25</v>
+        <v>16.4</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5409,62 +5409,62 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>108.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.5</v>
+        <v>59.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>14.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.5</v>
+        <v>7.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CC12" t="n">
         <v>3.42</v>
@@ -5652,31 +5652,31 @@
         <v>3.72</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CK12" t="n">
         <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN12" t="n">
         <v>1.97</v>
@@ -5685,37 +5685,37 @@
         <v>1.32</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY12" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="DA12" t="n">
         <v>2.01</v>
@@ -5724,52 +5724,52 @@
         <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="DH12" t="n">
-        <v>105.4</v>
+        <v>107.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.8</v>
+        <v>47.66</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.8</v>
+        <v>61.33</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.6</v>
+        <v>15.34</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="13">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>6.67</v>
       </c>
       <c r="H14" t="n">
-        <v>122</v>
+        <v>120.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>59</v>
+        <v>61.33</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>14.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>66.5</v>
+        <v>62</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.5</v>
+        <v>19.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>17</v>
+        <v>15.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>21</v>
+        <v>24.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0.33</v>
@@ -6386,49 +6386,49 @@
         <v>1.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BH14" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.6</v>
+        <v>6.83</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CC14" t="n">
         <v>4.33</v>
@@ -6458,61 +6458,61 @@
         <v>4.46</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CN14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP14" t="n">
         <v>1.95</v>
       </c>
-      <c r="CO14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>1.99</v>
-      </c>
       <c r="CQ14" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CX14" t="n">
         <v>1.49</v>
@@ -6527,55 +6527,55 @@
         <v>2.05</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DG14" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="DH14" t="n">
-        <v>112.2</v>
+        <v>113</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="DK14" t="n">
-        <v>11.6</v>
+        <v>10.84</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.4</v>
+        <v>52.16</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="DP14" t="n">
-        <v>15</v>
+        <v>15.66</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.2</v>
+        <v>15.16</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.4</v>
+        <v>57.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>12.8</v>
+        <v>12.66</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6717,43 +6717,43 @@
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP15" t="n">
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,73 +6765,73 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>24.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BP15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BU15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BY15" t="n">
         <v>2.09</v>
@@ -6849,70 +6849,70 @@
         <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.53</v>
+        <v>3.94</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="CH15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CK15" t="n">
         <v>1.35</v>
       </c>
-      <c r="CI15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CL15" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
         <v>1.88</v>
@@ -6921,13 +6921,13 @@
         <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="DB15" t="n">
         <v>1.38</v>
@@ -6942,43 +6942,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="DH15" t="n">
-        <v>87.25</v>
+        <v>93.2</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>36</v>
+        <v>42.2</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55</v>
+        <v>55.4</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.25</v>
+        <v>14.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="DZ15" t="n">
-        <v>7.25</v>
+        <v>6.2</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.75</v>
+        <v>20.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="H16" t="n">
-        <v>78</v>
+        <v>79.33</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>40.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA16" t="n">
         <v>8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>15.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="BI16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BP16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>6.67</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="CC16" t="n">
         <v>2.3</v>
@@ -7267,70 +7267,70 @@
         <v>1.4</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CH16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK16" t="n">
         <v>1.4</v>
       </c>
-      <c r="CI16" t="n">
+      <c r="CL16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP16" t="n">
         <v>1.91</v>
       </c>
-      <c r="CJ16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CQ16" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX16" t="n">
         <v>1.44</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
@@ -7342,79 +7342,79 @@
         <v>3.43</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="DH16" t="n">
-        <v>72.2</v>
+        <v>73.83</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.2</v>
+        <v>33.83</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.4</v>
+        <v>7.84</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.2</v>
+        <v>45.66</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.6</v>
+        <v>12.34</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.6</v>
+        <v>6.66</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6</v>
+        <v>5.66</v>
       </c>
       <c r="EA16" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0.33</v>
@@ -7520,10 +7520,10 @@
         <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -7532,35 +7532,35 @@
         <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>23.5</v>
+        <v>30.67</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU17" t="n">
         <v>1</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49.5</v>
+        <v>52.33</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>15.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.5</v>
+        <v>14.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BF17" t="n">
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.17</v>
@@ -7655,55 +7655,55 @@
         <v>3.53</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.55</v>
+        <v>5.87</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="CE17" t="n">
         <v>1.39</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7718,39 +7718,39 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
         <v>2</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="DH17" t="n">
-        <v>85</v>
+        <v>84.84</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.6</v>
+        <v>4.84</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="DM17" t="n">
-        <v>25</v>
+        <v>28.33</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.4</v>
+        <v>13.16</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.2</v>
+        <v>12.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.6</v>
+        <v>7.66</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,25 +7792,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42</v>
+        <v>44.66</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.2</v>
+        <v>14.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.8</v>
+        <v>4.17</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.4</v>
+        <v>16.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC17" t="n">
         <v>3</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -7835,49 +7835,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>102</v>
+        <v>98.67</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M18" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>17.67</v>
       </c>
       <c r="R18" t="n">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7889,28 +7889,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>45</v>
+        <v>44.67</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,37 +7994,37 @@
         <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="BH18" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="BJ18" t="n">
         <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
@@ -8033,31 +8033,31 @@
         <v>100</v>
       </c>
       <c r="BT18" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX18" t="n">
         <v>100</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="CA18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CB18" t="n">
         <v>3.31</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>3.36</v>
       </c>
       <c r="CC18" t="n">
         <v>3.38</v>
@@ -8066,13 +8066,13 @@
         <v>3.98</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH18" t="n">
         <v>1.35</v>
@@ -8087,31 +8087,31 @@
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO18" t="n">
         <v>1.33</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU18" t="n">
         <v>1.35</v>
@@ -8126,97 +8126,97 @@
         <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB18" t="n">
         <v>1.4</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DH18" t="n">
-        <v>108.8</v>
+        <v>106</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="DK18" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>35</v>
+        <v>34.16</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="DO18" t="n">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.6</v>
+        <v>12.16</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.2</v>
+        <v>14.34</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.6</v>
+        <v>6.34</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.2</v>
+        <v>48.34</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.2</v>
+        <v>13.66</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.4</v>
+        <v>9.83</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="EA18" t="n">
-        <v>22.6</v>
+        <v>21.83</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>11.33</v>
+        <v>10.33</v>
       </c>
       <c r="Q19" t="n">
         <v>12.33</v>
@@ -8319,124 +8319,124 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
         <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>88</v>
+        <v>82.33</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>20.5</v>
+        <v>15.33</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18</v>
+        <v>13.33</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.5</v>
+        <v>12.33</v>
       </c>
       <c r="AS19" t="n">
         <v>9</v>
       </c>
       <c r="AT19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="n">
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AW19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.4</v>
-      </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.4</v>
+        <v>5.67</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>2.42</v>
@@ -8457,34 +8457,34 @@
         <v>2.4</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK19" t="n">
         <v>1.43</v>
@@ -8496,130 +8496,130 @@
         <v>2.59</v>
       </c>
       <c r="CN19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS19" t="n">
         <v>3.39</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CU19" t="n">
         <v>1.34</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX19" t="n">
         <v>1.56</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.33</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DG19" t="n">
         <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.8</v>
+        <v>85</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.4</v>
+        <v>5.16</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM19" t="n">
-        <v>34.4</v>
+        <v>29.5</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="DP19" t="n">
-        <v>14</v>
+        <v>11.83</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.2</v>
+        <v>12.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.6</v>
+        <v>7.84</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54</v>
+        <v>53.34</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.6</v>
+        <v>11.16</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>6.83</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.6</v>
+        <v>4.34</v>
       </c>
       <c r="EA19" t="n">
-        <v>13.6</v>
+        <v>14.84</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8722,136 +8722,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
         <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>101.5</v>
+        <v>96.33</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AM20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ20" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN20" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.4</v>
-      </c>
       <c r="BK20" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP20" t="n">
-        <v>7.4</v>
+        <v>6.83</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BX20" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY20" t="n">
         <v>2.28</v>
@@ -8860,55 +8860,55 @@
         <v>2.33</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.92</v>
+        <v>4.17</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.11</v>
+        <v>4.23</v>
       </c>
       <c r="CE20" t="n">
         <v>1.4</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG20" t="n">
         <v>2.78</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="CR20" t="n">
         <v>1.39</v>
@@ -8923,10 +8923,10 @@
         <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CX20" t="n">
         <v>1.68</v>
@@ -8941,55 +8941,55 @@
         <v>2.01</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>115</v>
+        <v>110.16</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="DJ20" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DK20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="DM20" t="n">
-        <v>48.8</v>
+        <v>41.34</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.6</v>
+        <v>11.33</v>
       </c>
       <c r="DQ20" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.4</v>
+        <v>6.33</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>58.4</v>
+        <v>55.5</v>
       </c>
       <c r="DW20" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DX20" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="DY20" t="n">
-        <v>14.4</v>
+        <v>13.34</v>
       </c>
       <c r="DZ20" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.4</v>
+        <v>17.17</v>
       </c>
       <c r="EB20" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="21">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -9047,46 +9047,46 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="H21" t="n">
-        <v>89.5</v>
+        <v>86.33</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>36.5</v>
+        <v>36.67</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>13.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>18.5</v>
+        <v>16.67</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9098,28 +9098,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>43</v>
+        <v>39.67</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>25.5</v>
+        <v>23.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,37 +9203,37 @@
         <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
         <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9242,31 +9242,31 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX21" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.81</v>
+        <v>3.67</v>
       </c>
       <c r="CB21" t="n">
-        <v>4.04</v>
+        <v>3.83</v>
       </c>
       <c r="CC21" t="n">
         <v>6.1</v>
@@ -9275,55 +9275,55 @@
         <v>7.83</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="CH21" t="n">
         <v>1.38</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV21" t="n">
         <v>1.78</v>
@@ -9344,55 +9344,55 @@
         <v>1.89</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.57</v>
+        <v>3.84</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DG21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="DH21" t="n">
-        <v>81.75</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="DL21" t="n">
         <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>27.75</v>
+        <v>29.6</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DP21" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="DQ21" t="n">
-        <v>16.75</v>
+        <v>16</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="DS21" t="n">
         <v>0</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>40.75</v>
+        <v>39.2</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="DZ21" t="n">
         <v>4</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.75</v>
+        <v>20.4</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -3033,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>15.33</v>
       </c>
       <c r="Q6" t="n">
         <v>12.33</v>
@@ -3345,7 +3345,7 @@
         <v>1.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.66</v>
+        <v>16.83</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.5</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>70.5</v>
+        <v>69</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25.5</v>
+        <v>23.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="Q7" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
       <c r="R7" t="n">
-        <v>13</v>
+        <v>11.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>13.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>17</v>
+        <v>15.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,37 +3565,37 @@
         <v>0.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>14.25</v>
+        <v>13.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>8.75</v>
+        <v>7.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3604,31 +3604,31 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="CC7" t="n">
         <v>6.78</v>
@@ -3637,61 +3637,61 @@
         <v>7.8</v>
       </c>
       <c r="CE7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK7" t="n">
         <v>1.4</v>
       </c>
-      <c r="CF7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.41</v>
-      </c>
       <c r="CL7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="CX7" t="n">
         <v>1.51</v>
@@ -3706,13 +3706,13 @@
         <v>2.06</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3721,73 +3721,73 @@
         <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DH7" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
         <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR7" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>38.75</v>
+        <v>38</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.25</v>
+        <v>7.8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.75</v>
+        <v>19</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -3953,16 +3953,16 @@
         <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BC8" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD8" t="n">
         <v>19</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="BF8" t="n">
         <v>3</v>
@@ -4178,16 +4178,16 @@
         <v>9.83</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
         <v>19.34</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="EC8" t="n">
         <v>3</v>
@@ -4645,7 +4645,7 @@
         <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>8.67</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
         <v>14</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.33</v>
+        <v>58.67</v>
       </c>
       <c r="Y10" t="n">
         <v>0.33</v>
@@ -4906,13 +4906,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
@@ -4957,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.17</v>
+        <v>11.34</v>
       </c>
       <c r="DQ10" t="n">
         <v>13.66</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.83</v>
+        <v>55</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>83.5</v>
+        <v>92.67</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5920,100 +5920,100 @@
         <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="AO13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6022,19 +6022,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BY13" t="n">
         <v>2.22</v>
@@ -6043,16 +6043,16 @@
         <v>2.34</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.23</v>
+        <v>4.29</v>
       </c>
       <c r="CE13" t="n">
         <v>1.39</v>
@@ -6061,55 +6061,55 @@
         <v>2.86</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CO13" t="n">
         <v>1.31</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CX13" t="n">
         <v>1.5</v>
@@ -6124,88 +6124,88 @@
         <v>1.93</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.40000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>38</v>
+        <v>35.66</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.4</v>
+        <v>12.16</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.6</v>
+        <v>7.84</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.2</v>
+        <v>50.16</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.4</v>
+        <v>7.66</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="EA13" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="14">
@@ -7033,7 +7033,7 @@
         <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
         <v>2.33</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>4.33</v>
@@ -7108,7 +7108,7 @@
         <v>1.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
         <v>2.33</v>
@@ -7357,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="DK16" t="n">
         <v>4.83</v>
@@ -7414,7 +7414,7 @@
         <v>1.42</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="17">
@@ -7898,16 +7898,16 @@
         <v>10.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.67</v>
+        <v>3.33</v>
       </c>
       <c r="AC18" t="n">
         <v>19</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE18" t="n">
         <v>3.33</v>
@@ -8204,10 +8204,10 @@
         <v>13.66</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.83</v>
+        <v>3.67</v>
       </c>
       <c r="EA18" t="n">
         <v>21.83</v>
@@ -8349,7 +8349,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.33</v>
+        <v>16.33</v>
       </c>
       <c r="AR19" t="n">
         <v>12.33</v>
@@ -8580,7 +8580,7 @@
         <v>2.16</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.83</v>
+        <v>13.33</v>
       </c>
       <c r="DQ19" t="n">
         <v>12.33</v>
@@ -8752,7 +8752,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.33</v>
+        <v>12.33</v>
       </c>
       <c r="AR20" t="n">
         <v>14.67</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>51.33</v>
+        <v>51</v>
       </c>
       <c r="AZ20" t="n">
         <v>0.33</v>
@@ -8932,13 +8932,13 @@
         <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.13</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="DB20" t="n">
         <v>1.33</v>
@@ -8983,7 +8983,7 @@
         <v>4</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.33</v>
+        <v>12.33</v>
       </c>
       <c r="DQ20" t="n">
         <v>14.5</v>
@@ -9001,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>55.5</v>
+        <v>55.34</v>
       </c>
       <c r="DW20" t="n">
         <v>0.16</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>85.67</v>
+        <v>80.25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>29.33</v>
+        <v>29.75</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.67</v>
+        <v>43.75</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1454,19 +1454,19 @@
         <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.67</v>
+        <v>8.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD2" t="n">
         <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BH2" t="n">
-        <v>13.33</v>
+        <v>12.14</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.67</v>
+        <v>5.86</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="CC2" t="n">
         <v>3.31</v>
@@ -1625,55 +1625,55 @@
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.84</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
         <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW2" t="n">
         <v>1.95</v>
@@ -1682,10 +1682,10 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DA2" t="n">
         <v>2.11</v>
@@ -1694,52 +1694,52 @@
         <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.17</v>
+        <v>84.72</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM2" t="n">
-        <v>37</v>
+        <v>36.14</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="DP2" t="n">
-        <v>11</v>
+        <v>11.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.67</v>
+        <v>16.71</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.84</v>
+        <v>7.86</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.34</v>
+        <v>47.29</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.84</v>
+        <v>12</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.34</v>
+        <v>19.72</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
@@ -1782,25 +1782,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>92.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1809,64 +1809,64 @@
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>33.5</v>
+        <v>32.67</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>18.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56</v>
+        <v>53.33</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>13.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.5</v>
+        <v>22.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1953,67 +1953,67 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CB3" t="n">
         <v>3.23</v>
@@ -2028,55 +2028,55 @@
         <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
         <v>1.35</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW3" t="n">
         <v>1.98</v>
@@ -2100,79 +2100,79 @@
         <v>2.28</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="DH3" t="n">
-        <v>79.40000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK3" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.6</v>
+        <v>30.67</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.8</v>
+        <v>15.84</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.6</v>
+        <v>45.16</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="DY3" t="n">
-        <v>8</v>
+        <v>7.34</v>
       </c>
       <c r="DZ3" t="n">
         <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.6</v>
+        <v>21.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="EC3" t="n">
         <v>2</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -2197,31 +2197,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H4" t="n">
-        <v>113.5</v>
+        <v>108</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>33</v>
+        <v>37.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -2230,16 +2230,16 @@
         <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="R4" t="n">
         <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.5</v>
+        <v>54</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.5</v>
+        <v>16.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,46 +2356,46 @@
         <v>3.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BH4" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.2</v>
+        <v>5.83</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.8</v>
+        <v>4.83</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -2407,19 +2407,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="CC4" t="n">
         <v>3.33</v>
@@ -2431,154 +2431,154 @@
         <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CH4" t="n">
         <v>1.41</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.74</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CL4" t="n">
         <v>1.88</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>26.2</v>
+        <v>29.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.8</v>
+        <v>15.84</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.2</v>
+        <v>48</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.6</v>
+        <v>12.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.4</v>
+        <v>5.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.6</v>
+        <v>18.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>81.5</v>
+        <v>82.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>22.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.5</v>
+        <v>8.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.5</v>
+        <v>52.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
         <v>3.2</v>
@@ -2819,73 +2819,73 @@
         <v>3.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.8</v>
+        <v>4.83</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.23</v>
+        <v>5.07</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CK5" t="n">
         <v>1.48</v>
       </c>
-      <c r="CF5" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CU5" t="n">
         <v>1.38</v>
       </c>
-      <c r="CP5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CV5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX5" t="n">
         <v>1.59</v>
@@ -2900,55 +2900,55 @@
         <v>1.86</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.18</v>
+        <v>3.95</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG5" t="n">
         <v>1</v>
       </c>
-      <c r="DG5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="DH5" t="n">
-        <v>74.75</v>
+        <v>76.8</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>16.75</v>
+        <v>20.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DP5" t="n">
         <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.25</v>
+        <v>13.2</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.25</v>
+        <v>7.6</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.25</v>
+        <v>49</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="DY5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="EA5" t="n">
         <v>16</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,124 +3084,124 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>111.33</v>
+        <v>105</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.67</v>
+        <v>42.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.33</v>
+        <v>17.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.67</v>
+        <v>13.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AT6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BO6" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.67</v>
+        <v>4.57</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY6" t="n">
         <v>2.25</v>
@@ -3222,67 +3222,67 @@
         <v>2.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.63</v>
+        <v>4.13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CK6" t="n">
         <v>1.39</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.03</v>
+        <v>3.93</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV6" t="n">
         <v>1.86</v>
@@ -3303,88 +3303,88 @@
         <v>2.11</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="DG6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>92.14</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>11</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="EB6" t="n">
         <v>1.66</v>
       </c>
-      <c r="DH6" t="n">
-        <v>93.16</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>38.84</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>6</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>16.34</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>20</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="EC6" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="H7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="K7" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>23.67</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="n">
-        <v>9.67</v>
+        <v>11.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>11.33</v>
+        <v>11.25</v>
       </c>
       <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.33</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>0.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>13.2</v>
+        <v>12.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.6</v>
+        <v>6.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.6</v>
+        <v>6.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.73</v>
+        <v>3.63</v>
       </c>
       <c r="CC7" t="n">
         <v>6.78</v>
@@ -3640,19 +3640,19 @@
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
         <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CK7" t="n">
         <v>1.4</v>
@@ -3661,19 +3661,19 @@
         <v>1.81</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="CR7" t="n">
         <v>1.42</v>
@@ -3706,13 +3706,13 @@
         <v>2.06</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3721,73 +3721,73 @@
         <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>66.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>19.6</v>
+        <v>21.17</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.2</v>
+        <v>11.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>38</v>
+        <v>37.67</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.8</v>
+        <v>11.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.8</v>
+        <v>8.33</v>
       </c>
       <c r="DZ7" t="n">
         <v>3</v>
       </c>
       <c r="EA7" t="n">
-        <v>19</v>
+        <v>18.83</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="n">
         <v>2</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI8" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>17.33</v>
+        <v>24.75</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.67</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,70 +3944,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.67</v>
+        <v>54</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.67</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>19</v>
+        <v>19.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.68</v>
+        <v>0.87</v>
       </c>
       <c r="BF8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.67</v>
+        <v>5.43</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY8" t="n">
         <v>1.88</v>
@@ -4028,25 +4028,25 @@
         <v>1.96</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.49</v>
+        <v>3.17</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4055,28 +4055,28 @@
         <v>1.84</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
         <v>1.39</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO8" t="n">
         <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
@@ -4091,10 +4091,10 @@
         <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4112,52 +4112,52 @@
         <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="DH8" t="n">
-        <v>84.66</v>
+        <v>89.14</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DK8" t="n">
         <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM8" t="n">
-        <v>24.67</v>
+        <v>27.86</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>1.14</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.67</v>
+        <v>17.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.84</v>
+        <v>7.86</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.34</v>
+        <v>58.29</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.83</v>
+        <v>10.29</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.84</v>
+        <v>7.14</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.34</v>
+        <v>19.72</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="EC8" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4293,49 +4293,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.33</v>
+        <v>60.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.67</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>36</v>
+        <v>34.75</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.33</v>
+        <v>14.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BM9" t="n">
         <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY9" t="n">
         <v>2.2</v>
@@ -4431,25 +4431,25 @@
         <v>2.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.73</v>
+        <v>5.7</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.31</v>
+        <v>6.25</v>
       </c>
       <c r="CE9" t="n">
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CH9" t="n">
         <v>1.32</v>
@@ -4458,43 +4458,43 @@
         <v>1.71</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CM9" t="n">
         <v>2.95</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CO9" t="n">
         <v>1.36</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW9" t="n">
         <v>2.08</v>
@@ -4515,52 +4515,52 @@
         <v>1.4</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>67.33</v>
+        <v>65.14</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.17</v>
+        <v>28.14</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DP9" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>36.84</v>
+        <v>36</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.17</v>
+        <v>10.71</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.34</v>
+        <v>7.72</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="EA9" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="EC9" t="n">
         <v>2</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0.67</v>
@@ -4699,112 +4699,112 @@
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>89.33</v>
+        <v>89.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>35.67</v>
+        <v>31</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.67</v>
+        <v>13.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.33</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.33</v>
+        <v>51.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB10" t="n">
         <v>9</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.33</v>
+        <v>19.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.17</v>
+        <v>10.14</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>1.7</v>
@@ -4834,46 +4834,46 @@
         <v>1.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO10" t="n">
         <v>1.34</v>
@@ -4882,25 +4882,25 @@
         <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU10" t="n">
         <v>1.37</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4915,88 +4915,88 @@
         <v>2.07</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG10" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="DH10" t="n">
-        <v>97.83</v>
+        <v>96.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DM10" t="n">
-        <v>33.17</v>
+        <v>30.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.34</v>
+        <v>12.29</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.66</v>
+        <v>15.43</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55</v>
+        <v>54.57</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.84</v>
+        <v>14.29</v>
       </c>
       <c r="DY10" t="n">
-        <v>10.66</v>
+        <v>10.43</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.16</v>
+        <v>3.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.16</v>
+        <v>18.29</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="11">
@@ -5006,25 +5006,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="H11" t="n">
-        <v>116.5</v>
+        <v>128.33</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -5033,64 +5033,64 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>15</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>14.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>12.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5177,37 +5177,37 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5216,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.66</v>
+        <v>4.22</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.86</v>
+        <v>4.64</v>
       </c>
       <c r="CC11" t="n">
         <v>1.93</v>
@@ -5249,43 +5249,43 @@
         <v>1.95</v>
       </c>
       <c r="CE11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CH11" t="n">
         <v>1.42</v>
       </c>
-      <c r="CF11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
@@ -5300,103 +5300,103 @@
         <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CX11" t="n">
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.01</v>
+        <v>3.69</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>117.6</v>
+        <v>123.33</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>40</v>
+        <v>42.66</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.4</v>
+        <v>13.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.4</v>
+        <v>57.84</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.4</v>
+        <v>13.84</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.4</v>
+        <v>16.33</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5499,52 +5499,52 @@
         <v>2.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>106.67</v>
+        <v>102</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>49</v>
+        <v>43.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>63.33</v>
+        <v>59.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.33</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>1.74</v>
@@ -5640,25 +5640,25 @@
         <v>1.76</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="CE12" t="n">
         <v>1.4</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH12" t="n">
         <v>1.36</v>
@@ -5673,7 +5673,7 @@
         <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CM12" t="n">
         <v>2.55</v>
@@ -5682,13 +5682,13 @@
         <v>1.97</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5703,10 +5703,10 @@
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
@@ -5721,55 +5721,55 @@
         <v>2.01</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.5</v>
+        <v>104.71</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>47.66</v>
+        <v>44.71</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.84</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="DR12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>61.33</v>
+        <v>59.43</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.34</v>
+        <v>15.43</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>90.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M13" t="n">
-        <v>42.33</v>
+        <v>41.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="R13" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="S13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.67</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="AR13" t="n">
         <v>13.33</v>
@@ -5983,37 +5983,37 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6022,31 +6022,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX13" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>2.22</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
         <v>3.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC13" t="n">
         <v>3.6</v>
@@ -6061,55 +6061,55 @@
         <v>2.86</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI13" t="n">
         <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP13" t="n">
         <v>2.04</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX13" t="n">
         <v>1.5</v>
@@ -6127,85 +6127,85 @@
         <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="DH13" t="n">
-        <v>91.34</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM13" t="n">
-        <v>35.66</v>
+        <v>36.14</v>
       </c>
       <c r="DN13" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.5</v>
+        <v>12.14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.16</v>
+        <v>12.86</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.84</v>
+        <v>7.57</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.16</v>
+        <v>49.14</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.5</v>
+        <v>12.71</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.66</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.84</v>
+        <v>4.72</v>
       </c>
       <c r="EA13" t="n">
-        <v>14.5</v>
+        <v>14.86</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,52 +6305,52 @@
         <v>2.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AI14" t="n">
-        <v>105.67</v>
+        <v>102.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.67</v>
+        <v>9.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>43</v>
+        <v>42.75</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.33</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,73 +6362,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53</v>
+        <v>49.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.33</v>
+        <v>15.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.67</v>
+        <v>17.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>14</v>
+        <v>13.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY14" t="n">
         <v>2.15</v>
@@ -6446,55 +6446,55 @@
         <v>2.35</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6509,16 +6509,16 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="n">
         <v>1.49</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.5</v>
@@ -6536,46 +6536,46 @@
         <v>3.27</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="DG14" t="n">
-        <v>6</v>
+        <v>5.72</v>
       </c>
       <c r="DH14" t="n">
-        <v>113</v>
+        <v>110.28</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DK14" t="n">
-        <v>10.84</v>
+        <v>10.43</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DM14" t="n">
-        <v>52.16</v>
+        <v>50.71</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.66</v>
+        <v>14.86</v>
       </c>
       <c r="DQ14" t="n">
-        <v>15.16</v>
+        <v>13.86</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.5</v>
+        <v>54.86</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.5</v>
+        <v>17.43</v>
       </c>
       <c r="DY14" t="n">
-        <v>12.66</v>
+        <v>12.43</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="EA14" t="n">
-        <v>20</v>
+        <v>20.43</v>
       </c>
       <c r="EB14" t="n">
         <v>1.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -6630,49 +6630,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="H15" t="n">
-        <v>84.67</v>
+        <v>99.25</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>6.67</v>
+        <v>6.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="M15" t="n">
-        <v>41.67</v>
+        <v>51.25</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R15" t="n">
-        <v>5.67</v>
+        <v>6.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,25 +6684,25 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>52.33</v>
+        <v>56.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.67</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.67</v>
+        <v>18.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -6789,49 +6789,49 @@
         <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
         <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.6</v>
+        <v>4.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CC15" t="n">
         <v>3.8</v>
@@ -6861,7 +6861,7 @@
         <v>3.94</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
         <v>2.83</v>
@@ -6873,49 +6873,49 @@
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
@@ -6936,49 +6936,49 @@
         <v>2.22</v>
       </c>
       <c r="DD15" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.2</v>
+        <v>101.5</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.2</v>
+        <v>48.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.4</v>
+        <v>57.67</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.6</v>
+        <v>15.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.4</v>
+        <v>20.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>79.33</v>
+        <v>79.5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M16" t="n">
-        <v>40.33</v>
+        <v>39</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>46</v>
+        <v>47.5</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>15.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="AB16" t="n">
         <v>6</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.33</v>
+        <v>17.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BH16" t="n">
-        <v>13</v>
+        <v>12.14</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BP16" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.67</v>
+        <v>6.14</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX16" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CC16" t="n">
         <v>2.3</v>
@@ -7264,13 +7264,13 @@
         <v>2.44</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CH16" t="n">
         <v>1.41</v>
@@ -7285,37 +7285,37 @@
         <v>1.4</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CN16" t="n">
         <v>2.08</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW16" t="n">
         <v>1.9</v>
@@ -7333,88 +7333,88 @@
         <v>2.12</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="DH16" t="n">
-        <v>73.83</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.83</v>
+        <v>34</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.84</v>
+        <v>7.43</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.66</v>
+        <v>46.57</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.34</v>
+        <v>13.29</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.66</v>
+        <v>7.57</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.66</v>
+        <v>5.71</v>
       </c>
       <c r="EA16" t="n">
-        <v>15.5</v>
+        <v>16.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>0.33</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>30.67</v>
+        <v>31</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.33</v>
+        <v>13.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.33</v>
+        <v>12.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.33</v>
+        <v>48</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.33</v>
+        <v>13.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.67</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.67</v>
+        <v>13.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.67</v>
+        <v>5.43</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY17" t="n">
         <v>3.17</v>
@@ -7655,55 +7655,55 @@
         <v>3.53</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.63</v>
+        <v>4.33</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.87</v>
+        <v>8.65</v>
       </c>
       <c r="CD17" t="n">
-        <v>6</v>
+        <v>9.92</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7718,69 +7718,69 @@
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.84</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.84</v>
+        <v>4.43</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DM17" t="n">
-        <v>28.33</v>
+        <v>28.86</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.16</v>
+        <v>12.71</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.33</v>
+        <v>12.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.66</v>
+        <v>7.28</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.66</v>
+        <v>43.29</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.16</v>
+        <v>13.14</v>
       </c>
       <c r="DY17" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.17</v>
+        <v>15.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="H18" t="n">
-        <v>98.67</v>
+        <v>99.25</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>5.33</v>
+        <v>4.75</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M18" t="n">
-        <v>31</v>
+        <v>38.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.67</v>
+        <v>16</v>
       </c>
       <c r="R18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44.67</v>
+        <v>48.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>19</v>
+        <v>17.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,37 +7994,37 @@
         <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BH18" t="n">
         <v>11</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.5</v>
+        <v>4.86</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
@@ -8033,28 +8033,28 @@
         <v>100</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX18" t="n">
         <v>100</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB18" t="n">
         <v>3.31</v>
@@ -8066,43 +8066,43 @@
         <v>3.98</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
@@ -8117,10 +8117,10 @@
         <v>1.35</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
@@ -8132,91 +8132,91 @@
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.12</v>
+        <v>3.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>106</v>
+        <v>105.28</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>34.16</v>
+        <v>37.86</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DO18" t="n">
-        <v>4.66</v>
+        <v>4</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.16</v>
+        <v>11.14</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.34</v>
+        <v>13.86</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.34</v>
+        <v>6.14</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.34</v>
+        <v>50.14</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.66</v>
+        <v>13.29</v>
       </c>
       <c r="DY18" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.83</v>
+        <v>20.72</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,124 +8319,124 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>82.33</v>
+        <v>93.25</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>5</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.67</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY19" t="n">
         <v>2.42</v>
@@ -8457,22 +8457,22 @@
         <v>2.4</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="CC19" t="n">
         <v>3.13</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CG19" t="n">
         <v>2.6</v>
@@ -8481,70 +8481,70 @@
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CR19" t="n">
         <v>1.52</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CU19" t="n">
         <v>1.34</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
@@ -8553,73 +8553,73 @@
         <v>1</v>
       </c>
       <c r="DG19" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DH19" t="n">
-        <v>85</v>
+        <v>90.86</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.16</v>
+        <v>4.57</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM19" t="n">
-        <v>29.5</v>
+        <v>32.43</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.33</v>
+        <v>13.86</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.33</v>
+        <v>12.86</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.84</v>
+        <v>7.57</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.34</v>
+        <v>55.86</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.16</v>
+        <v>11.28</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.34</v>
+        <v>4.14</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.84</v>
+        <v>16.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="20">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -8641,49 +8641,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
         <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.33</v>
+        <v>-0.25</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>10.33</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M20" t="n">
-        <v>59.67</v>
+        <v>58.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>6.33</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>12.33</v>
+        <v>11.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.33</v>
+        <v>13.25</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,25 +8695,25 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>59.67</v>
+        <v>57.75</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.33</v>
+        <v>22.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.67</v>
+        <v>15</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.67</v>
+        <v>7.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.67</v>
+        <v>15.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AE20" t="n">
         <v>2</v>
@@ -8800,70 +8800,70 @@
         <v>1.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="BH20" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="BI20" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU20" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV20" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BW20" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX20" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>4.17</v>
@@ -8875,25 +8875,25 @@
         <v>1.4</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK20" t="n">
         <v>1.48</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM20" t="n">
         <v>2.52</v>
@@ -8902,13 +8902,13 @@
         <v>1.94</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="CR20" t="n">
         <v>1.39</v>
@@ -8923,10 +8923,10 @@
         <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX20" t="n">
         <v>1.68</v>
@@ -8941,55 +8941,55 @@
         <v>2.05</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DH20" t="n">
-        <v>110.16</v>
+        <v>109.86</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ20" t="n">
         <v>2</v>
       </c>
       <c r="DK20" t="n">
-        <v>7</v>
+        <v>6.72</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="DM20" t="n">
-        <v>41.34</v>
+        <v>43.43</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DO20" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="DP20" t="n">
-        <v>12.33</v>
+        <v>11.71</v>
       </c>
       <c r="DQ20" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>55.34</v>
+        <v>54.86</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="DY20" t="n">
-        <v>13.34</v>
+        <v>12.86</v>
       </c>
       <c r="DZ20" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.17</v>
+        <v>16.57</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="21">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9125,49 +9125,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>26.33</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9179,61 +9179,61 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>38.5</v>
+        <v>44.67</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.5</v>
+        <v>5.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BD21" t="n">
-        <v>16</v>
+        <v>14.67</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG21" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BJ21" t="n">
         <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9242,19 +9242,19 @@
         <v>100</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV21" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW21" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>3.11</v>
@@ -9263,16 +9263,16 @@
         <v>3.42</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="CC21" t="n">
-        <v>6.1</v>
+        <v>5.57</v>
       </c>
       <c r="CD21" t="n">
-        <v>7.83</v>
+        <v>6.87</v>
       </c>
       <c r="CE21" t="n">
         <v>1.39</v>
@@ -9287,49 +9287,49 @@
         <v>1.38</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK21" t="n">
         <v>1.53</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO21" t="n">
         <v>1.3</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS21" t="n">
         <v>3.23</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU21" t="n">
         <v>1.37</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX21" t="n">
         <v>1.59</v>
@@ -9347,52 +9347,52 @@
         <v>1.37</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="DH21" t="n">
-        <v>81.40000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="DL21" t="n">
         <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>29.6</v>
+        <v>31.5</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="DP21" t="n">
-        <v>11.4</v>
+        <v>12.34</v>
       </c>
       <c r="DQ21" t="n">
-        <v>16</v>
+        <v>15.84</v>
       </c>
       <c r="DR21" t="n">
-        <v>7</v>
+        <v>6.66</v>
       </c>
       <c r="DS21" t="n">
         <v>0</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>39.2</v>
+        <v>42.17</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.8</v>
+        <v>10.34</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.4</v>
+        <v>19</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" t="n">
-        <v>90.67</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AL2" t="n">
-        <v>8.33</v>
+        <v>6.75</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.67</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.67</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.33</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.67</v>
+        <v>6.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.67</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.67</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>12.14</v>
+        <v>11.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.31</v>
@@ -1610,73 +1610,73 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.31</v>
+        <v>3.92</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.59</v>
+        <v>4.26</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
         <v>3.03</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL2" t="n">
         <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU2" t="n">
         <v>1.38</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CX2" t="n">
         <v>1.46</v>
@@ -1691,55 +1691,55 @@
         <v>2.11</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.72</v>
+        <v>85.25</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DK2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM2" t="n">
-        <v>36.14</v>
+        <v>35.88</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.72</v>
+        <v>12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.71</v>
+        <v>16.88</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.29</v>
+        <v>46.88</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.72</v>
+        <v>20</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>92.33</v>
+        <v>92.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.67</v>
+        <v>6.75</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>32.67</v>
+        <v>34.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>18.67</v>
+        <v>16.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>53.33</v>
+        <v>53.25</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.33</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.67</v>
+        <v>7</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.33</v>
+        <v>21.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.67</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="CA3" t="n">
         <v>3.22</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CC3" t="n">
         <v>4.3</v>
@@ -2025,49 +2025,49 @@
         <v>4.39</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CT3" t="n">
         <v>2.76</v>
@@ -2103,79 +2103,79 @@
         <v>4.2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="DH3" t="n">
-        <v>81.67</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.84</v>
+        <v>5.14</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>30.67</v>
+        <v>32</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.16</v>
+        <v>2.71</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.84</v>
+        <v>15</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="DR3" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.16</v>
+        <v>46.29</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.33</v>
+        <v>10.57</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.34</v>
+        <v>6.57</v>
       </c>
       <c r="DZ3" t="n">
         <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.33</v>
+        <v>21</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>77</v>
+        <v>81.75</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.67</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.67</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.67</v>
+        <v>14.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.33</v>
+        <v>20.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.67</v>
+        <v>11.14</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK4" t="n">
         <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.83</v>
+        <v>6.14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
         <v>1.92</v>
@@ -2416,169 +2416,169 @@
         <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF4" t="n">
         <v>2.81</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH4" t="n">
         <v>1.41</v>
       </c>
       <c r="CI4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CN4" t="n">
         <v>2</v>
       </c>
-      <c r="CJ4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CO4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CU4" t="n">
         <v>1.43</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.5</v>
+        <v>93</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.17</v>
+        <v>5.72</v>
       </c>
       <c r="DL4" t="n">
         <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.84</v>
+        <v>14.14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.84</v>
+        <v>15.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.17</v>
+        <v>11.86</v>
       </c>
       <c r="DY4" t="n">
         <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.16</v>
+        <v>4.86</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.5</v>
+        <v>18.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,139 +2678,139 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BL5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="BM5" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI5" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BN5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BP5" t="n">
         <v>3.33</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>3.2</v>
@@ -2819,31 +2819,31 @@
         <v>3.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.83</v>
+        <v>4.6</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
         <v>2.9</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.85</v>
@@ -2852,40 +2852,40 @@
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
         <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CU5" t="n">
         <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX5" t="n">
         <v>1.59</v>
@@ -2903,85 +2903,85 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="DG5" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.8</v>
+        <v>72.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DJ5" t="n">
         <v>3</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>20.8</v>
+        <v>22.83</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.2</v>
+        <v>12.83</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.6</v>
+        <v>8.33</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49</v>
+        <v>47.67</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="EA5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -3003,46 +3003,46 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2.75</v>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>78.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.67</v>
+        <v>6.25</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>15.33</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.33</v>
+        <v>11.5</v>
       </c>
       <c r="R6" t="n">
         <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.67</v>
+        <v>49</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>14.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.33</v>
+        <v>19.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,46 +3162,46 @@
         <v>3.75</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.43</v>
+        <v>11.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.57</v>
+        <v>5.62</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
         <v>3.49</v>
@@ -3234,10 +3234,10 @@
         <v>4.13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CG6" t="n">
         <v>2.64</v>
@@ -3246,49 +3246,49 @@
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.87</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
         <v>1.37</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX6" t="n">
         <v>1.49</v>
@@ -3303,55 +3303,55 @@
         <v>2.11</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.43</v>
+        <v>3.12</v>
       </c>
       <c r="DH6" t="n">
-        <v>92.14</v>
+        <v>91.75</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.29</v>
+        <v>41.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.43</v>
+        <v>15.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.86</v>
+        <v>12.38</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.29</v>
+        <v>51.38</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.14</v>
+        <v>16.38</v>
       </c>
       <c r="DY6" t="n">
-        <v>11</v>
+        <v>11.12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.28</v>
+        <v>19.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC7" t="n">
         <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
         <v>2.75</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>62.5</v>
+        <v>73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.5</v>
+        <v>-0.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.5</v>
+        <v>22.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>35</v>
+        <v>40.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>7.33</v>
       </c>
       <c r="BC7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1</v>
       </c>
-      <c r="BD7" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.5</v>
-      </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH7" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="BR7" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
         <v>2.87</v>
@@ -3625,28 +3625,28 @@
         <v>3.07</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.49</v>
+        <v>3.71</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.63</v>
+        <v>3.82</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.78</v>
+        <v>6.45</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.8</v>
+        <v>7.88</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
         <v>1.86</v>
@@ -3655,25 +3655,25 @@
         <v>1.87</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="CR7" t="n">
         <v>1.42</v>
@@ -3697,94 +3697,94 @@
         <v>1.51</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.45</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DG7" t="n">
         <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>65.5</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DM7" t="n">
-        <v>21.17</v>
+        <v>24</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.33</v>
+        <v>10.57</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10</v>
+        <v>10.86</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>37.67</v>
+        <v>39.72</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.33</v>
+        <v>11.14</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.83</v>
+        <v>19.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC7" t="n">
         <v>2</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -3809,46 +3809,46 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>97.33</v>
+        <v>103</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>12.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.67</v>
+        <v>17.25</v>
       </c>
       <c r="R8" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>64</v>
+        <v>61.5</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.67</v>
+        <v>13.25</v>
       </c>
       <c r="AA8" t="n">
         <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.67</v>
+        <v>19.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,46 +3968,46 @@
         <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,19 +4019,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC8" t="n">
         <v>3.17</v>
@@ -4040,43 +4040,43 @@
         <v>3.48</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
@@ -4091,73 +4091,73 @@
         <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.14</v>
+        <v>93</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="DK8" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM8" t="n">
-        <v>27.86</v>
+        <v>25.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.14</v>
+        <v>12.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.72</v>
+        <v>17.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.86</v>
+        <v>7.75</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.29</v>
+        <v>57.75</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.29</v>
+        <v>10.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.14</v>
+        <v>7.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.72</v>
+        <v>19.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AM9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>34.75</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT9" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
         <v>2.2</v>
@@ -4431,46 +4431,46 @@
         <v>2.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.7</v>
+        <v>5.36</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.25</v>
+        <v>5.91</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CO9" t="n">
         <v>1.36</v>
@@ -4479,19 +4479,19 @@
         <v>2.21</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CR9" t="n">
         <v>1.47</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV9" t="n">
         <v>1.81</v>
@@ -4524,43 +4524,43 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DH9" t="n">
-        <v>65.14</v>
+        <v>64.5</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="DM9" t="n">
-        <v>28.14</v>
+        <v>27.25</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="DR9" t="n">
-        <v>11.57</v>
+        <v>10.38</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>36</v>
+        <v>37.38</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.71</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.72</v>
+        <v>7.13</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>14.43</v>
+        <v>15.13</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="EC9" t="n">
         <v>2</v>
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>106.33</v>
+        <v>107.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="K10" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>30.67</v>
+        <v>33.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.67</v>
+        <v>59.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.67</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.33</v>
+        <v>10.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.14</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BZ10" t="n">
         <v>1.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CC10" t="n">
         <v>3.58</v>
@@ -4849,55 +4849,55 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CK10" t="n">
         <v>1.38</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="CN10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP10" t="n">
         <v>2.07</v>
       </c>
-      <c r="CO10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>2.09</v>
-      </c>
       <c r="CQ10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW10" t="n">
         <v>2.07</v>
@@ -4906,97 +4906,97 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="DH10" t="n">
-        <v>96.86</v>
+        <v>98.75</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>30.86</v>
+        <v>32.12</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.29</v>
+        <v>13.12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.43</v>
+        <v>15.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.57</v>
+        <v>55.38</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.29</v>
+        <v>13.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>10.43</v>
+        <v>9.75</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.29</v>
+        <v>19.12</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0.33</v>
@@ -5096,52 +5096,52 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>118.33</v>
+        <v>107.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>35.33</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>11.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,61 +5153,61 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>57.67</v>
+        <v>54.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>12.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.33</v>
+        <v>19.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5216,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
         <v>1.32</v>
@@ -5237,55 +5237,55 @@
         <v>1.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.64</v>
+        <v>4.44</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="CD11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CN11" t="n">
         <v>1.95</v>
       </c>
-      <c r="CE11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>1.97</v>
-      </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
@@ -5300,106 +5300,106 @@
         <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.69</v>
+        <v>3.82</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>123.33</v>
+        <v>116.28</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.66</v>
+        <v>36.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.84</v>
+        <v>14.86</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>57.84</v>
+        <v>56.14</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.84</v>
+        <v>13.29</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.66</v>
+        <v>4.29</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.33</v>
+        <v>16.28</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="12">
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>108.33</v>
+        <v>109.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>46.33</v>
+        <v>40.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>14.67</v>
+        <v>15.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>59.33</v>
+        <v>58.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.67</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.67</v>
+        <v>8.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.67</v>
+        <v>16.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.57</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>1.74</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CA12" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC12" t="n">
         <v>3.1</v>
@@ -5652,22 +5652,22 @@
         <v>3.34</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CK12" t="n">
         <v>1.46</v>
@@ -5676,7 +5676,7 @@
         <v>1.78</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN12" t="n">
         <v>1.97</v>
@@ -5685,28 +5685,28 @@
         <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
@@ -5724,49 +5724,49 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.71</v>
+        <v>105.75</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.71</v>
+        <v>42</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
         <v>7</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>59.43</v>
+        <v>59</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.57</v>
+        <v>8.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.43</v>
+        <v>15.25</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>92.67</v>
+        <v>99.75</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>29</v>
+        <v>33.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.67</v>
+        <v>9.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.33</v>
+        <v>12.75</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,61 +5959,61 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>52</v>
+        <v>54.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.33</v>
+        <v>7.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.67</v>
+        <v>18.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.289999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.14</v>
+        <v>3.62</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6022,19 +6022,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
         <v>2.12</v>
@@ -6043,40 +6043,40 @@
         <v>2.22</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CB13" t="n">
         <v>3.42</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="CE13" t="n">
         <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG13" t="n">
         <v>2.73</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
         <v>2.48</v>
@@ -6088,10 +6088,10 @@
         <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6106,106 +6106,106 @@
         <v>1.39</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG13" t="n">
         <v>1.5</v>
       </c>
-      <c r="CY13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>1.43</v>
-      </c>
       <c r="DH13" t="n">
-        <v>91.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.14</v>
+        <v>37.62</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.14</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.86</v>
+        <v>12.62</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.57</v>
+        <v>8</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.14</v>
+        <v>50.88</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.71</v>
+        <v>12.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>14.86</v>
+        <v>16.38</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -6227,82 +6227,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>6.67</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>120.33</v>
+        <v>115.75</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>61.33</v>
+        <v>56.75</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>14.33</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>11.75</v>
       </c>
       <c r="R14" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>62</v>
+        <v>58.5</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.67</v>
+        <v>18.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.33</v>
+        <v>13.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.33</v>
+        <v>20.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6389,46 +6389,46 @@
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>13.57</v>
+        <v>12.88</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.47</v>
+        <v>3.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="CC14" t="n">
         <v>3.98</v>
@@ -6458,43 +6458,43 @@
         <v>4.29</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6509,103 +6509,103 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX14" t="n">
         <v>1.49</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.5</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>5.72</v>
+        <v>5.25</v>
       </c>
       <c r="DH14" t="n">
-        <v>110.28</v>
+        <v>109.25</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
         <v>2</v>
       </c>
       <c r="DK14" t="n">
-        <v>10.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.71</v>
+        <v>49.75</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.86</v>
+        <v>13.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.86</v>
+        <v>54</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.43</v>
+        <v>17</v>
       </c>
       <c r="DY14" t="n">
-        <v>12.43</v>
+        <v>11.75</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.43</v>
+        <v>19.12</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC14" t="n">
         <v>2</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AN15" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>10.67</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.5</v>
+        <v>15.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.5</v>
+        <v>6.33</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6771,67 +6771,67 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.5</v>
+        <v>8.67</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>24.5</v>
+        <v>25.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BJ15" t="n">
         <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV15" t="n">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY15" t="n">
         <v>1.98</v>
@@ -6849,136 +6849,136 @@
         <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.94</v>
+        <v>3.61</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP15" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV15" t="n">
         <v>1.94</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.38</v>
       </c>
       <c r="DA15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DC15" t="n">
         <v>2.24</v>
       </c>
-      <c r="DB15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>2.22</v>
-      </c>
       <c r="DD15" t="n">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.5</v>
+        <v>101.29</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.5</v>
+        <v>51.14</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.17</v>
+        <v>12.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.67</v>
+        <v>6.28</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>57.67</v>
+        <v>58</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.33</v>
+        <v>21.28</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -7111,52 +7111,52 @@
         <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>68.33</v>
+        <v>73.25</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>27.33</v>
+        <v>25.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.67</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AU16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.33</v>
+        <v>43.25</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.67</v>
+        <v>9.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.67</v>
+        <v>15.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.14</v>
+        <v>6.38</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY16" t="n">
         <v>1.5</v>
@@ -7252,70 +7252,70 @@
         <v>1.56</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK16" t="n">
         <v>1.4</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW16" t="n">
         <v>1.9</v>
@@ -7333,88 +7333,88 @@
         <v>2.12</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>74.70999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="DK16" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>34</v>
+        <v>32.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.43</v>
+        <v>13.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.43</v>
+        <v>13.38</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.57</v>
+        <v>45.38</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.29</v>
+        <v>12.38</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.71</v>
+        <v>5.25</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.86</v>
+        <v>16.75</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="17">
@@ -7424,61 +7424,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>83.67</v>
+        <v>80.25</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K17" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.33</v>
+        <v>11.75</v>
       </c>
       <c r="R17" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>37</v>
+        <v>37.25</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.67</v>
+        <v>6.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.67</v>
+        <v>17.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.75</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.29</v>
+        <v>10.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.86</v>
+        <v>5.25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="CA17" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="CC17" t="n">
         <v>8.65</v>
@@ -7673,55 +7673,55 @@
         <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="CK17" t="n">
         <v>1.35</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.28</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DB17" t="n">
         <v>1.3</v>
@@ -7738,49 +7738,49 @@
         <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>85.29000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
-        <v>28.86</v>
+        <v>28.75</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.71</v>
+        <v>12.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.57</v>
+        <v>12.25</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.28</v>
+        <v>7.62</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.29</v>
+        <v>42.62</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.14</v>
+        <v>13.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.43</v>
+        <v>9</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.14</v>
+        <v>15.25</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>113.33</v>
+        <v>105</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.67</v>
+        <v>5.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>37.33</v>
+        <v>32.75</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52</v>
+        <v>48.75</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>10.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>24.67</v>
+        <v>24</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="n">
-        <v>11</v>
+        <v>10.38</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.14</v>
+        <v>5.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX18" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BY18" t="n">
         <v>2.19</v>
@@ -8054,169 +8054,169 @@
         <v>2.31</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.98</v>
+        <v>4.34</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.81</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CO18" t="n">
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DH18" t="n">
-        <v>105.28</v>
+        <v>102.12</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DK18" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>37.86</v>
+        <v>35.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DO18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.14</v>
+        <v>11.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.14</v>
+        <v>6.62</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.14</v>
+        <v>48.75</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.29</v>
+        <v>12.25</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.72</v>
+        <v>20.88</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="19">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="H19" t="n">
-        <v>87.67</v>
+        <v>102.75</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.33</v>
+        <v>6.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>43.67</v>
+        <v>50.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.33</v>
+        <v>14.5</v>
       </c>
       <c r="R19" t="n">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54</v>
+        <v>56.25</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.33</v>
+        <v>12.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.33</v>
+        <v>8.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.67</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,46 +8397,46 @@
         <v>2.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8448,19 +8448,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CC19" t="n">
         <v>3.13</v>
@@ -8469,19 +8469,19 @@
         <v>3.33</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.92</v>
@@ -8490,40 +8490,40 @@
         <v>1.44</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.99</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CU19" t="n">
         <v>1.34</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX19" t="n">
         <v>1.53</v>
@@ -8544,82 +8544,82 @@
         <v>2.31</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.86</v>
+        <v>98</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.57</v>
+        <v>5.25</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM19" t="n">
-        <v>32.43</v>
+        <v>37.12</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
         <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.86</v>
+        <v>13.62</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.86</v>
+        <v>13.88</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.86</v>
+        <v>56.75</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.28</v>
+        <v>10.25</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.14</v>
+        <v>6.62</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.14</v>
+        <v>3.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.29</v>
+        <v>16.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="20">
@@ -8629,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>120</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>9</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M20" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5</v>
-      </c>
       <c r="P20" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.25</v>
+        <v>11.4</v>
       </c>
       <c r="R20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,28 +8695,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>57.75</v>
+        <v>53.6</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.25</v>
+        <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>15</v>
+        <v>12.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.75</v>
+        <v>16.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8800,67 +8800,67 @@
         <v>1.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BH20" t="n">
-        <v>10.86</v>
+        <v>9.75</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN20" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BP20" t="n">
-        <v>6.29</v>
+        <v>5.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU20" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BW20" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX20" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CB20" t="n">
         <v>3.43</v>
@@ -8881,19 +8881,19 @@
         <v>2.77</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK20" t="n">
         <v>1.48</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM20" t="n">
         <v>2.52</v>
@@ -8905,10 +8905,10 @@
         <v>1.31</v>
       </c>
       <c r="CP20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="CR20" t="n">
         <v>1.39</v>
@@ -8923,73 +8923,73 @@
         <v>1.44</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="DH20" t="n">
-        <v>109.86</v>
+        <v>107.75</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DK20" t="n">
-        <v>6.72</v>
+        <v>5.88</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>43.43</v>
+        <v>44.38</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="DO20" t="n">
-        <v>3.57</v>
+        <v>3.13</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.71</v>
+        <v>11.37</v>
       </c>
       <c r="DQ20" t="n">
-        <v>13.86</v>
+        <v>12.63</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>54.86</v>
+        <v>52.62</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>19</v>
+        <v>17.75</v>
       </c>
       <c r="DY20" t="n">
-        <v>12.86</v>
+        <v>11.75</v>
       </c>
       <c r="DZ20" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.57</v>
+        <v>16.75</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="21">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -9044,49 +9044,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G21" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="H21" t="n">
-        <v>86.33</v>
+        <v>88</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M21" t="n">
-        <v>36.67</v>
+        <v>37.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>16.67</v>
+        <v>14.5</v>
       </c>
       <c r="R21" t="n">
-        <v>7.33</v>
+        <v>7.75</v>
       </c>
       <c r="S21" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>39.67</v>
+        <v>39.75</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -9107,19 +9107,19 @@
         <v>13</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AC21" t="n">
-        <v>23.33</v>
+        <v>23</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9158,7 +9158,7 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="AS21" t="n">
         <v>6</v>
@@ -9203,70 +9203,70 @@
         <v>2.67</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BJ21" t="n">
         <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP21" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU21" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV21" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW21" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="CC21" t="n">
         <v>5.57</v>
@@ -9275,16 +9275,16 @@
         <v>6.87</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI21" t="n">
         <v>1.82</v>
@@ -9293,106 +9293,106 @@
         <v>1.93</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP21" t="n">
         <v>2.06</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CX21" t="n">
         <v>1.59</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.34</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.16</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="DL21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DM21" t="n">
-        <v>31.5</v>
+        <v>32.71</v>
       </c>
       <c r="DN21" t="n">
         <v>1</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.34</v>
+        <v>12.71</v>
       </c>
       <c r="DQ21" t="n">
-        <v>15.84</v>
+        <v>14.57</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.66</v>
+        <v>7</v>
       </c>
       <c r="DS21" t="n">
         <v>0</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>42.17</v>
+        <v>41.86</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.34</v>
+        <v>10.72</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="EA21" t="n">
-        <v>19</v>
+        <v>19.43</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -2010,13 +2010,13 @@
         <v>2.16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CA3" t="n">
         <v>3.22</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CC3" t="n">
         <v>4.3</v>
@@ -2067,19 +2067,19 @@
         <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU3" t="n">
         <v>1.35</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX3" t="n">
         <v>1.49</v>
@@ -2097,10 +2097,10 @@
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="DE3" t="n">
         <v>0.72</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
         <v>1.5</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL4" t="n">
         <v>5</v>
@@ -2338,10 +2338,10 @@
         <v>0.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
         <v>3.25</v>
@@ -2350,10 +2350,10 @@
         <v>20.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="BG4" t="n">
         <v>2.29</v>
@@ -2425,7 +2425,7 @@
         <v>3.04</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CE4" t="n">
         <v>1.39</v>
@@ -2470,31 +2470,31 @@
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU4" t="n">
         <v>1.43</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX4" t="n">
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
@@ -2503,13 +2503,13 @@
         <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="DG4" t="n">
         <v>2</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="DK4" t="n">
         <v>5.72</v>
@@ -2563,10 +2563,10 @@
         <v>0.28</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.86</v>
+        <v>12</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.86</v>
@@ -2578,7 +2578,7 @@
         <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3628,13 +3628,13 @@
         <v>3.71</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC7" t="n">
         <v>6.45</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
@@ -3688,10 +3688,10 @@
         <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX7" t="n">
         <v>1.51</v>
@@ -3703,16 +3703,16 @@
         <v>2.45</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="G8" t="n">
         <v>3.25</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="K8" t="n">
         <v>5.25</v>
@@ -3839,7 +3839,7 @@
         <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>12.75</v>
+        <v>16.5</v>
       </c>
       <c r="Q8" t="n">
         <v>17.25</v>
@@ -3869,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AB8" t="n">
         <v>3.25</v>
@@ -3881,10 +3881,10 @@
         <v>19.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -4025,13 +4025,13 @@
         <v>2.22</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CA8" t="n">
         <v>3.29</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC8" t="n">
         <v>3.17</v>
@@ -4091,19 +4091,19 @@
         <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY8" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA8" t="n">
         <v>2.02</v>
@@ -4112,16 +4112,16 @@
         <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DG8" t="n">
         <v>2.62</v>
@@ -4133,7 +4133,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
         <v>4.25</v>
@@ -4151,7 +4151,7 @@
         <v>1.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.25</v>
+        <v>14.12</v>
       </c>
       <c r="DQ8" t="n">
         <v>17.12</v>
@@ -4175,10 +4175,10 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.5</v>
+        <v>10.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="DZ8" t="n">
         <v>3</v>
@@ -4187,10 +4187,10 @@
         <v>19.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4434,7 +4434,7 @@
         <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC9" t="n">
         <v>5.36</v>
@@ -4482,13 +4482,13 @@
         <v>3.94</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU9" t="n">
         <v>1.35</v>
@@ -4515,10 +4515,10 @@
         <v>1.4</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>59.25</v>
+        <v>59</v>
       </c>
       <c r="Y10" t="n">
         <v>0.25</v>
@@ -4684,7 +4684,7 @@
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="AD10" t="n">
         <v>1.44</v>
@@ -4888,7 +4888,7 @@
         <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CT10" t="n">
         <v>2.87</v>
@@ -4912,7 +4912,7 @@
         <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
@@ -4921,7 +4921,7 @@
         <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="DE10" t="n">
         <v>0.25</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.38</v>
+        <v>55.25</v>
       </c>
       <c r="DW10" t="n">
         <v>0.12</v>
@@ -4990,7 +4990,7 @@
         <v>3.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.12</v>
+        <v>19.25</v>
       </c>
       <c r="EB10" t="n">
         <v>1.35</v>
@@ -5129,7 +5129,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.75</v>
+        <v>13.75</v>
       </c>
       <c r="AR11" t="n">
         <v>15.75</v>
@@ -5240,13 +5240,13 @@
         <v>4.06</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="CC11" t="n">
         <v>2.04</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CE11" t="n">
         <v>1.41</v>
@@ -5300,10 +5300,10 @@
         <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX11" t="n">
         <v>1.63</v>
@@ -5318,13 +5318,13 @@
         <v>1.95</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="DE11" t="n">
         <v>0.28</v>
@@ -5360,7 +5360,7 @@
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>14</v>
+        <v>15.14</v>
       </c>
       <c r="DQ11" t="n">
         <v>14.86</v>
@@ -5965,10 +5965,10 @@
         <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
         <v>2.75</v>
@@ -5977,7 +5977,7 @@
         <v>18.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BF13" t="n">
         <v>2.25</v>
@@ -6052,7 +6052,7 @@
         <v>3.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="CE13" t="n">
         <v>1.39</v>
@@ -6115,22 +6115,22 @@
         <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="DE13" t="n">
         <v>0.12</v>
@@ -6190,10 +6190,10 @@
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.38</v>
+        <v>12.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.88</v>
+        <v>7.75</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.5</v>
@@ -6202,7 +6202,7 @@
         <v>16.38</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
         <v>2</v>
@@ -6449,7 +6449,7 @@
         <v>3.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC14" t="n">
         <v>3.98</v>
@@ -6509,10 +6509,10 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX14" t="n">
         <v>1.49</v>
@@ -6524,16 +6524,16 @@
         <v>2.5</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="DE14" t="n">
         <v>0.12</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>3.33</v>
@@ -6783,7 +6783,7 @@
         <v>25.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BF15" t="n">
         <v>2.67</v>
@@ -6903,40 +6903,40 @@
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB15" t="n">
         <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6996,10 +6996,10 @@
         <v>0.14</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.71</v>
+        <v>15.43</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ15" t="n">
         <v>5.71</v>
@@ -7008,7 +7008,7 @@
         <v>21.28</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC15" t="n">
         <v>2.29</v>
@@ -7324,13 +7324,13 @@
         <v>1.44</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DB16" t="n">
         <v>1.32</v>
@@ -7652,7 +7652,7 @@
         <v>3.2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CA17" t="n">
         <v>3.89</v>
@@ -7706,19 +7706,19 @@
         <v>3.28</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW17" t="n">
         <v>1.94</v>
@@ -7729,16 +7729,16 @@
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DB17" t="n">
         <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
         <v>1.25</v>
@@ -7928,7 +7928,7 @@
         <v>0.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>5.75</v>
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.75</v>
+        <v>49</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
         <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
         <v>2.88</v>
@@ -8063,7 +8063,7 @@
         <v>3.79</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
@@ -8108,10 +8108,10 @@
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU18" t="n">
         <v>1.36</v>
@@ -8138,16 +8138,16 @@
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
         <v>1.75</v>
@@ -8159,7 +8159,7 @@
         <v>0.25</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="DK18" t="n">
         <v>5.25</v>
@@ -8195,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.75</v>
+        <v>48.88</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
@@ -8216,7 +8216,7 @@
         <v>1.26</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="19">
@@ -8268,7 +8268,7 @@
         <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
         <v>14.5</v>
@@ -8529,13 +8529,13 @@
         <v>1.53</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.38</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
@@ -8580,7 +8580,7 @@
         <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.62</v>
+        <v>13.75</v>
       </c>
       <c r="DQ19" t="n">
         <v>13.88</v>
@@ -8701,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="AB20" t="n">
         <v>6.8</v>
@@ -8713,7 +8713,7 @@
         <v>16.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AE20" t="n">
         <v>2.2</v>
@@ -8857,7 +8857,7 @@
         <v>2.53</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CA20" t="n">
         <v>3.38</v>
@@ -8932,22 +8932,22 @@
         <v>1.57</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.34</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="DE20" t="n">
         <v>0.12</v>
@@ -9007,10 +9007,10 @@
         <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.75</v>
+        <v>17.88</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.75</v>
+        <v>11.88</v>
       </c>
       <c r="DZ20" t="n">
         <v>6</v>
@@ -9019,7 +9019,7 @@
         <v>16.75</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="EC20" t="n">
         <v>1.87</v>
@@ -9266,7 +9266,7 @@
         <v>3.53</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC21" t="n">
         <v>5.57</v>
@@ -9320,37 +9320,37 @@
         <v>3.27</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU21" t="n">
         <v>1.36</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB21" t="n">
         <v>1.38</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1421,7 +1421,7 @@
         <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
         <v>17.75</v>
@@ -1733,7 +1733,7 @@
         <v>1.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="DQ2" t="n">
         <v>16.88</v>
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.75</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>34.5</v>
+        <v>32.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="Q3" t="n">
         <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>53.25</v>
+        <v>51.8</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0.67</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN3" t="n">
         <v>1</v>
       </c>
-      <c r="BK3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BO3" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CC3" t="n">
         <v>4.3</v>
@@ -2028,10 +2028,10 @@
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
@@ -2040,7 +2040,7 @@
         <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
         <v>1.4</v>
@@ -2052,16 +2052,16 @@
         <v>2.75</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CR3" t="n">
         <v>1.48</v>
@@ -2100,19 +2100,19 @@
         <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DF3" t="n">
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.29000000000001</v>
+        <v>84.12</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,61 +2121,61 @@
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>32</v>
+        <v>31.12</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.86</v>
+        <v>13.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.57</v>
+        <v>7.12</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.29</v>
+        <v>46.25</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>21</v>
+        <v>20.25</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1.5</v>
@@ -2621,10 +2621,10 @@
         <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -2672,145 +2672,145 @@
         <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.75</v>
+        <v>78.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.5</v>
+        <v>50.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.25</v>
+        <v>17.8</v>
       </c>
       <c r="BE5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK5" t="n">
         <v>0.86</v>
       </c>
-      <c r="BF5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.83</v>
-      </c>
       <c r="BL5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
         <v>3.2</v>
@@ -2819,16 +2819,16 @@
         <v>3.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.88</v>
+        <v>4.73</v>
       </c>
       <c r="CE5" t="n">
         <v>1.44</v>
@@ -2837,10 +2837,10 @@
         <v>2.9</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI5" t="n">
         <v>1.88</v>
@@ -2852,31 +2852,31 @@
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
         <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CU5" t="n">
         <v>1.38</v>
@@ -2903,85 +2903,85 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="DH5" t="n">
-        <v>72.5</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DM5" t="n">
-        <v>22.83</v>
+        <v>25.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.83</v>
+        <v>13.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>47.67</v>
+        <v>48.57</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DY5" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="EA5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="6">
@@ -3114,7 +3114,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.25</v>
+        <v>16.5</v>
       </c>
       <c r="AR6" t="n">
         <v>13.25</v>
@@ -3345,7 +3345,7 @@
         <v>1.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.62</v>
+        <v>15.25</v>
       </c>
       <c r="DQ6" t="n">
         <v>12.38</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
         <v>1.25</v>
@@ -3436,7 +3436,7 @@
         <v>0.5</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -3478,7 +3478,7 @@
         <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
         <v>2.75</v>
@@ -3508,7 +3508,7 @@
         <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>22.67</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>0.33</v>
@@ -3559,7 +3559,7 @@
         <v>25</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BF7" t="n">
         <v>1</v>
@@ -3739,7 +3739,7 @@
         <v>0.14</v>
       </c>
       <c r="DM7" t="n">
-        <v>24</v>
+        <v>26.86</v>
       </c>
       <c r="DN7" t="n">
         <v>0.86</v>
@@ -3748,7 +3748,7 @@
         <v>0.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.57</v>
+        <v>10.43</v>
       </c>
       <c r="DQ7" t="n">
         <v>10.86</v>
@@ -3784,7 +3784,7 @@
         <v>19.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="EC7" t="n">
         <v>2</v>
@@ -3839,7 +3839,7 @@
         <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>16.5</v>
+        <v>14.75</v>
       </c>
       <c r="Q8" t="n">
         <v>17.25</v>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
@@ -3902,7 +3902,7 @@
         <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>3.25</v>
@@ -3965,7 +3965,7 @@
         <v>0.87</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BG8" t="n">
         <v>1.75</v>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG8" t="n">
         <v>2.62</v>
@@ -4133,7 +4133,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DK8" t="n">
         <v>4.25</v>
@@ -4151,7 +4151,7 @@
         <v>1.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.12</v>
+        <v>13.25</v>
       </c>
       <c r="DQ8" t="n">
         <v>17.12</v>
@@ -4190,7 +4190,7 @@
         <v>1.08</v>
       </c>
       <c r="EC8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9">
@@ -4615,7 +4615,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
         <v>5.5</v>
@@ -4627,7 +4627,7 @@
         <v>0.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>7</v>
@@ -4690,7 +4690,7 @@
         <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
         <v>0.25</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DG10" t="n">
         <v>3.88</v>
@@ -4939,7 +4939,7 @@
         <v>0.25</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DK10" t="n">
         <v>6</v>
@@ -4996,7 +4996,7 @@
         <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5120,7 +5120,7 @@
         <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>34.25</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
@@ -5171,7 +5171,7 @@
         <v>19.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BF11" t="n">
         <v>2.25</v>
@@ -5351,7 +5351,7 @@
         <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>36.86</v>
+        <v>41</v>
       </c>
       <c r="DN11" t="n">
         <v>0.86</v>
@@ -5396,7 +5396,7 @@
         <v>16.28</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
         <v>2.14</v>
@@ -5451,7 +5451,7 @@
         <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
         <v>12</v>
@@ -5763,7 +5763,7 @@
         <v>3</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.5</v>
+        <v>13.38</v>
       </c>
       <c r="DQ12" t="n">
         <v>12</v>
@@ -5935,7 +5935,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AR13" t="n">
         <v>12.75</v>
@@ -6166,7 +6166,7 @@
         <v>2.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.62</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>56.75</v>
+        <v>58.5</v>
       </c>
       <c r="N14" t="n">
         <v>0.5</v>
@@ -6299,7 +6299,7 @@
         <v>20.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AE14" t="n">
         <v>2.25</v>
@@ -6308,7 +6308,7 @@
         <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
         <v>5</v>
@@ -6320,7 +6320,7 @@
         <v>0.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>9.25</v>
@@ -6383,7 +6383,7 @@
         <v>1.69</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -6539,7 +6539,7 @@
         <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
         <v>5.25</v>
@@ -6551,7 +6551,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DK14" t="n">
         <v>9.619999999999999</v>
@@ -6560,7 +6560,7 @@
         <v>0.62</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.75</v>
+        <v>50.62</v>
       </c>
       <c r="DN14" t="n">
         <v>0.38</v>
@@ -6605,10 +6605,10 @@
         <v>19.12</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
         <v>4.25</v>
@@ -6642,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>6.75</v>
@@ -6654,7 +6654,7 @@
         <v>51.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
         <v>2.5</v>
@@ -6705,7 +6705,7 @@
         <v>2.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="DG15" t="n">
         <v>3.57</v>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="DK15" t="n">
         <v>5.71</v>
@@ -6966,7 +6966,7 @@
         <v>51.14</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="DO15" t="n">
         <v>2.14</v>
@@ -7011,7 +7011,7 @@
         <v>1.75</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="16">
@@ -7547,7 +7547,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.25</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>12.75</v>
@@ -7774,7 +7774,7 @@
         <v>1.88</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.75</v>
+        <v>11.62</v>
       </c>
       <c r="DQ17" t="n">
         <v>12.25</v>
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
         <v>1.25</v>
@@ -7928,7 +7928,7 @@
         <v>0.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>5.75</v>
@@ -7937,7 +7937,7 @@
         <v>0.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.75</v>
+        <v>41.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
@@ -7946,7 +7946,7 @@
         <v>4.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="AR18" t="n">
         <v>12.75</v>
@@ -7988,10 +7988,10 @@
         <v>24</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BG18" t="n">
         <v>2.88</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
         <v>1.75</v>
@@ -8159,7 +8159,7 @@
         <v>0.25</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="DK18" t="n">
         <v>5.25</v>
@@ -8168,7 +8168,7 @@
         <v>0.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.5</v>
+        <v>39.88</v>
       </c>
       <c r="DN18" t="n">
         <v>1.12</v>
@@ -8177,7 +8177,7 @@
         <v>3.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="DQ18" t="n">
         <v>14.38</v>
@@ -8213,10 +8213,10 @@
         <v>20.88</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8641,7 +8641,7 @@
         <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
         <v>3.2</v>
@@ -8653,7 +8653,7 @@
         <v>-0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="K20" t="n">
         <v>7.2</v>
@@ -8662,7 +8662,7 @@
         <v>0.6</v>
       </c>
       <c r="M20" t="n">
-        <v>57.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>0.6</v>
@@ -8713,16 +8713,16 @@
         <v>16.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
         <v>2</v>
@@ -8734,7 +8734,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL20" t="n">
         <v>3.67</v>
@@ -8797,7 +8797,7 @@
         <v>1.42</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="BG20" t="n">
         <v>3.25</v>
@@ -8953,7 +8953,7 @@
         <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="DG20" t="n">
         <v>2.75</v>
@@ -8965,7 +8965,7 @@
         <v>-0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="DK20" t="n">
         <v>5.88</v>
@@ -8974,7 +8974,7 @@
         <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>44.38</v>
+        <v>49</v>
       </c>
       <c r="DN20" t="n">
         <v>0.63</v>
@@ -9019,10 +9019,10 @@
         <v>16.75</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="21">
@@ -9158,7 +9158,7 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>6</v>
@@ -9389,7 +9389,7 @@
         <v>12.71</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.57</v>
+        <v>14.71</v>
       </c>
       <c r="DR21" t="n">
         <v>7</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.25</v>
+        <v>89.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>40.2</v>
       </c>
       <c r="AO2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>13.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.25</v>
+        <v>11.11</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>2.31</v>
@@ -1610,31 +1610,31 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.92</v>
+        <v>3.57</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.26</v>
+        <v>3.86</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH2" t="n">
         <v>1.35</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.86</v>
@@ -1655,13 +1655,13 @@
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS2" t="n">
         <v>3.21</v>
@@ -1682,64 +1682,64 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DA2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG2" t="n">
         <v>2.11</v>
       </c>
-      <c r="DB2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="DH2" t="n">
-        <v>85.25</v>
+        <v>85.22</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.88</v>
+        <v>35.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.5</v>
+        <v>10.78</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.88</v>
+        <v>17.11</v>
       </c>
       <c r="DR2" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.88</v>
+        <v>47.78</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.25</v>
+        <v>13.11</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.62</v>
+        <v>4.11</v>
       </c>
       <c r="EA2" t="n">
-        <v>20</v>
+        <v>20.22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0.8</v>
@@ -1872,31 +1872,31 @@
         <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>33.75</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1905,19 +1905,19 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>37</v>
+        <v>39.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.33</v>
+        <v>20.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
         <v>2.13</v>
@@ -2016,22 +2016,22 @@
         <v>3.24</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF3" t="n">
         <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
@@ -2040,13 +2040,13 @@
         <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CM3" t="n">
         <v>2.75</v>
@@ -2058,19 +2058,19 @@
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CU3" t="n">
         <v>1.35</v>
@@ -2085,13 +2085,13 @@
         <v>1.49</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.5</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
@@ -2103,16 +2103,16 @@
         <v>4.21</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DF3" t="n">
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DH3" t="n">
-        <v>84.12</v>
+        <v>86.22</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,61 +2121,61 @@
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.62</v>
+        <v>4.22</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>31.12</v>
+        <v>33</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.62</v>
+        <v>14.89</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.12</v>
+        <v>6.44</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.25</v>
+        <v>46.44</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.25</v>
+        <v>20.22</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="4">
@@ -2185,25 +2185,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>108</v>
+        <v>100.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2212,34 +2212,34 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.67</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>37.33</v>
+        <v>34.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.67</v>
+        <v>16.5</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="S4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.67</v>
+        <v>13.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.67</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.67</v>
+        <v>15.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.14</v>
+        <v>10.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.14</v>
+        <v>5.75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CC4" t="n">
         <v>3.04</v>
@@ -2431,52 +2431,52 @@
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CN4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV4" t="n">
         <v>2.08</v>
@@ -2488,13 +2488,13 @@
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
@@ -2506,76 +2506,76 @@
         <v>3.36</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DH4" t="n">
-        <v>93</v>
+        <v>91.12</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.72</v>
+        <v>5.38</v>
       </c>
       <c r="DL4" t="n">
         <v>1</v>
       </c>
       <c r="DM4" t="n">
-        <v>32</v>
+        <v>31.38</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.14</v>
+        <v>14.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50</v>
+        <v>50.25</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>12</v>
+        <v>11.38</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.14</v>
+        <v>6.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.72</v>
+        <v>17.88</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="EC4" t="n">
         <v>2</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="H5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>25.67</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2759,70 +2759,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.43</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.46</v>
+        <v>3.11</v>
       </c>
       <c r="CA5" t="n">
         <v>3.39</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC5" t="n">
         <v>4.45</v>
@@ -2831,13 +2831,13 @@
         <v>4.73</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2849,13 +2849,13 @@
         <v>1.85</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
         <v>1.83</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
         <v>1.95</v>
@@ -2867,16 +2867,16 @@
         <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
         <v>1.38</v>
@@ -2888,16 +2888,16 @@
         <v>1.97</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.38</v>
@@ -2909,79 +2909,79 @@
         <v>3.96</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>75.70999999999999</v>
+        <v>73.62</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>25.86</v>
+        <v>25.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.71</v>
+        <v>8.25</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.57</v>
+        <v>46.88</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="EA5" t="n">
-        <v>17</v>
+        <v>16.63</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>41</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49</v>
+        <v>50.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.25</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.75</v>
+        <v>18.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,46 +3162,46 @@
         <v>3.75</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.25</v>
+        <v>11.33</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC6" t="n">
         <v>3.49</v>
@@ -3234,13 +3234,13 @@
         <v>4.13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
@@ -3255,7 +3255,7 @@
         <v>1.4</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
         <v>2.74</v>
@@ -3270,7 +3270,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3279,10 +3279,10 @@
         <v>3.22</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV6" t="n">
         <v>1.87</v>
@@ -3306,52 +3306,52 @@
         <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.75</v>
+        <v>89.44</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.75</v>
+        <v>40.67</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.25</v>
+        <v>14.89</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.38</v>
+        <v>51.89</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.38</v>
+        <v>16.56</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.5</v>
+        <v>18.89</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>31.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P7" t="n">
-        <v>11.25</v>
+        <v>12.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="R7" t="n">
-        <v>11.25</v>
+        <v>10.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>39</v>
+        <v>40.2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.25</v>
+        <v>10.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="BR7" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
         <v>6.45</v>
@@ -3637,55 +3637,55 @@
         <v>7.86</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ7" t="n">
         <v>1.86</v>
       </c>
-      <c r="CJ7" t="n">
-        <v>1.87</v>
-      </c>
       <c r="CK7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL7" t="n">
         <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO7" t="n">
         <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV7" t="n">
         <v>1.93</v>
@@ -3694,100 +3694,100 @@
         <v>1.92</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DB7" t="n">
         <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>69.56999999999999</v>
+        <v>74.25</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM7" t="n">
-        <v>26.86</v>
+        <v>28.75</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.43</v>
+        <v>11.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.86</v>
+        <v>10.13</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.57</v>
+        <v>10.25</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>39.72</v>
+        <v>40.38</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.14</v>
+        <v>12.12</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.43</v>
+        <v>9.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.86</v>
+        <v>21.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,127 +3890,127 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>2</v>
       </c>
-      <c r="AI8" t="n">
-        <v>83</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BH8" t="n">
-        <v>9.25</v>
+        <v>10.22</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.25</v>
+        <v>6.11</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
         <v>2.22</v>
@@ -4028,46 +4028,46 @@
         <v>2.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CB8" t="n">
         <v>3.29</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.48</v>
+        <v>3.81</v>
       </c>
       <c r="CE8" t="n">
         <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH8" t="n">
         <v>1.33</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>1.36</v>
@@ -4076,16 +4076,16 @@
         <v>2.19</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU8" t="n">
         <v>1.35</v>
@@ -4097,67 +4097,67 @@
         <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC8" t="n">
         <v>2.29</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="DH8" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.25</v>
+        <v>4.89</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>25.38</v>
+        <v>26.11</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.12</v>
+        <v>16.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.75</v>
+        <v>55.67</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.5</v>
+        <v>18.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>71.33</v>
+        <v>83.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AC9" t="n">
-        <v>14.67</v>
+        <v>16.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.62</v>
+        <v>10.22</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.88</v>
+        <v>6.44</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT9" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX9" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="CC9" t="n">
         <v>5.36</v>
@@ -4443,52 +4443,52 @@
         <v>5.91</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI9" t="n">
         <v>1.72</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="CU9" t="n">
         <v>1.35</v>
@@ -4500,67 +4500,67 @@
         <v>2.08</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="CZ9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DC9" t="n">
         <v>2.33</v>
       </c>
-      <c r="DA9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2.28</v>
-      </c>
       <c r="DD9" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>64.5</v>
+        <v>70.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.25</v>
+        <v>29.11</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>37.38</v>
+        <v>40.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.869999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.13</v>
+        <v>7.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.13</v>
+        <v>15.78</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="EC9" t="n">
         <v>2</v>
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>107.75</v>
+        <v>109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>33.25</v>
+        <v>37.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4672,25 +4672,25 @@
         <v>59</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.25</v>
+        <v>18.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4777,67 +4777,67 @@
         <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CC10" t="n">
         <v>3.58</v>
@@ -4846,28 +4846,28 @@
         <v>4.43</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CG10" t="n">
         <v>2.69</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK10" t="n">
         <v>1.38</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM10" t="n">
         <v>2.78</v>
@@ -4876,22 +4876,22 @@
         <v>2.11</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP10" t="n">
         <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4906,7 +4906,7 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.46</v>
@@ -4918,85 +4918,85 @@
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="DH10" t="n">
-        <v>98.75</v>
+        <v>100.44</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="DM10" t="n">
-        <v>32.12</v>
+        <v>34.78</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.12</v>
+        <v>13.33</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.119999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.25</v>
+        <v>55.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.25</v>
+        <v>18.78</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0.33</v>
@@ -5096,52 +5096,52 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.25</v>
+        <v>97.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>34.25</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.75</v>
+        <v>13.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,61 +5153,61 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>54.75</v>
+        <v>52.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.25</v>
+        <v>11.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.25</v>
+        <v>19.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5216,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>1.32</v>
@@ -5237,67 +5237,67 @@
         <v>1.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.42</v>
+        <v>4.27</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
         <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV11" t="n">
         <v>1.74</v>
@@ -5309,97 +5309,97 @@
         <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>116.28</v>
+        <v>109.25</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>41</v>
+        <v>38.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.14</v>
+        <v>14.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.86</v>
+        <v>14.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.14</v>
+        <v>54.62</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.29</v>
+        <v>12.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>9</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.28</v>
+        <v>16.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5409,62 +5409,62 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.5</v>
+        <v>59</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.25</v>
+        <v>8.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.75</v>
+        <v>17.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.38</v>
+        <v>5.33</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CA12" t="n">
         <v>3.38</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC12" t="n">
         <v>3.1</v>
@@ -5655,52 +5655,52 @@
         <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CH12" t="n">
         <v>1.35</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CL12" t="n">
         <v>1.82</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="CM12" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV12" t="n">
         <v>1.86</v>
@@ -5709,67 +5709,67 @@
         <v>2.01</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>105.75</v>
+        <v>102.22</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.12</v>
+        <v>5.44</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM12" t="n">
-        <v>42</v>
+        <v>42.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
         <v>3</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.38</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12</v>
+        <v>12.11</v>
       </c>
       <c r="DR12" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>59</v>
+        <v>59.22</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.75</v>
+        <v>15.33</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.25</v>
+        <v>15.78</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>99.75</v>
+        <v>93.8</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.75</v>
+        <v>32.2</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.75</v>
+        <v>12.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,61 +5959,61 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.75</v>
+        <v>51.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6022,19 +6022,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY13" t="n">
         <v>2.12</v>
@@ -6043,31 +6043,31 @@
         <v>2.22</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.7</v>
+        <v>4.26</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.38</v>
+        <v>4.73</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.78</v>
@@ -6076,34 +6076,34 @@
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CV13" t="n">
         <v>2</v>
@@ -6112,100 +6112,100 @@
         <v>1.87</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="EB13" t="n">
         <v>1.34</v>
       </c>
-      <c r="DC13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>95</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>37.62</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>8</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="EA13" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="EB13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
@@ -6227,82 +6227,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>115.75</v>
+        <v>107.2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>58.5</v>
+        <v>52.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>14.5</v>
+        <v>15.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.75</v>
+        <v>12.4</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>58.5</v>
+        <v>53.6</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.25</v>
+        <v>15.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.25</v>
+        <v>11</v>
       </c>
       <c r="AB14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.75</v>
+        <v>19.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6389,46 +6389,46 @@
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="CC14" t="n">
         <v>3.98</v>
@@ -6461,13 +6461,13 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI14" t="n">
         <v>1.95</v>
@@ -6479,22 +6479,22 @@
         <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6518,97 +6518,97 @@
         <v>1.49</v>
       </c>
       <c r="CY14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>105.22</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>48</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="EB14" t="n">
         <v>1.7</v>
       </c>
-      <c r="CZ14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>109.25</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>50.62</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV14" t="n">
-        <v>54</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>17</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>1.81</v>
-      </c>
       <c r="EC14" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.67</v>
+        <v>3.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>104</v>
+        <v>113.25</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>51</v>
+        <v>54.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.67</v>
+        <v>11.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.67</v>
+        <v>15.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>60</v>
+        <v>61.25</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.33</v>
+        <v>13.25</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>25.33</v>
+        <v>23.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
         <v>1.98</v>
@@ -6849,25 +6849,25 @@
         <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="CE15" t="n">
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
@@ -6876,28 +6876,28 @@
         <v>1.91</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CO15" t="n">
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6918,67 +6918,67 @@
         <v>1.93</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="DB15" t="n">
         <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.29</v>
+        <v>106.25</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.14</v>
+        <v>52.75</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.28</v>
+        <v>5.75</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>58</v>
+        <v>58.88</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.43</v>
+        <v>15.88</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.710000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.28</v>
+        <v>20.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
-        <v>79.5</v>
+        <v>91.2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>44.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.25</v>
+        <v>15.2</v>
       </c>
       <c r="R16" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.25</v>
+        <v>15.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.75</v>
+        <v>16.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
         <v>0.25</v>
@@ -7192,70 +7192,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BH16" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX16" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BZ16" t="n">
         <v>1.56</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.63</v>
+        <v>3.76</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CC16" t="n">
         <v>2.43</v>
@@ -7264,16 +7264,16 @@
         <v>2.57</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI16" t="n">
         <v>1.91</v>
@@ -7282,37 +7282,37 @@
         <v>1.81</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CO16" t="n">
         <v>1.28</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CV16" t="n">
         <v>1.96</v>
@@ -7321,100 +7321,100 @@
         <v>1.9</v>
       </c>
       <c r="CX16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF16" t="n">
         <v>1.44</v>
       </c>
-      <c r="CY16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="DG16" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DH16" t="n">
-        <v>76.38</v>
+        <v>83.22</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>32.38</v>
+        <v>36</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.25</v>
+        <v>7.11</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.38</v>
+        <v>47</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.38</v>
+        <v>12.78</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.12</v>
+        <v>7.67</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="EA16" t="n">
-        <v>16.75</v>
+        <v>16</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>86.5</v>
+        <v>88.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN17" t="n">
-        <v>31</v>
+        <v>32.2</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.75</v>
+        <v>13.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48</v>
+        <v>46.8</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.25</v>
+        <v>12.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.25</v>
+        <v>15.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU17" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY17" t="n">
         <v>3.2</v>
@@ -7658,13 +7658,13 @@
         <v>3.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.65</v>
+        <v>7.97</v>
       </c>
       <c r="CD17" t="n">
-        <v>9.92</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="CE17" t="n">
         <v>1.37</v>
@@ -7685,16 +7685,16 @@
         <v>1.9</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
@@ -7703,16 +7703,16 @@
         <v>1.94</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
@@ -7725,62 +7725,62 @@
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.38</v>
+        <v>85</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>28.75</v>
+        <v>29.67</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.62</v>
+        <v>11.89</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.25</v>
+        <v>12.78</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.62</v>
+        <v>7.22</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42.62</v>
+        <v>42.56</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="DY17" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.25</v>
+        <v>16.11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>99.25</v>
+        <v>99.2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M18" t="n">
-        <v>38.25</v>
+        <v>41</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>12.5</v>
+        <v>13.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="R18" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.75</v>
+        <v>50.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.75</v>
+        <v>17.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BR18" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS18" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="CC18" t="n">
         <v>3.79</v>
@@ -8069,31 +8069,31 @@
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CH18" t="n">
         <v>1.37</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.81</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CO18" t="n">
         <v>1.31</v>
@@ -8102,19 +8102,19 @@
         <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV18" t="n">
         <v>1.94</v>
@@ -8126,97 +8126,97 @@
         <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DG18" t="n">
         <v>2</v>
       </c>
-      <c r="DG18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="DH18" t="n">
-        <v>102.12</v>
+        <v>101.78</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.88</v>
+        <v>41.22</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.38</v>
+        <v>12</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.38</v>
+        <v>14.33</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.88</v>
+        <v>49.89</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.25</v>
+        <v>11.67</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.88</v>
+        <v>20.56</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC18" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="19">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,124 +8319,124 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>93.25</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>31.2</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.25</v>
+        <v>14.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AU19" t="n">
         <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>57.25</v>
+        <v>59</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.25</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.95</v>
+        <v>1.08</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.75</v>
+        <v>10.11</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.38</v>
+        <v>4.78</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY19" t="n">
         <v>2.5</v>
@@ -8457,40 +8457,40 @@
         <v>2.48</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CB19" t="n">
         <v>3.31</v>
       </c>
-      <c r="CB19" t="n">
-        <v>3.32</v>
-      </c>
       <c r="CC19" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK19" t="n">
         <v>1.44</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM19" t="n">
         <v>2.63</v>
@@ -8505,7 +8505,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CR19" t="n">
         <v>1.51</v>
@@ -8526,13 +8526,13 @@
         <v>2</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY19" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="DA19" t="n">
         <v>2.02</v>
@@ -8550,76 +8550,76 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="DH19" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.25</v>
+        <v>5.89</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.12</v>
+        <v>39.67</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.88</v>
+        <v>14.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.75</v>
+        <v>57.78</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.25</v>
+        <v>10.78</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.62</v>
+        <v>7.22</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.5</v>
+        <v>16.11</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0.2</v>
@@ -8722,136 +8722,136 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>91</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>96.33</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>51</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BF20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.75</v>
+        <v>9.44</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT20" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV20" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW20" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX20" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BY20" t="n">
         <v>2.53</v>
@@ -8860,34 +8860,34 @@
         <v>2.51</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="CC20" t="n">
-        <v>4.17</v>
+        <v>3.84</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.23</v>
+        <v>3.9</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CJ20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK20" t="n">
         <v>1.48</v>
@@ -8896,31 +8896,31 @@
         <v>1.86</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN20" t="n">
         <v>1.94</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="CT20" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CV20" t="n">
         <v>2</v>
@@ -8929,67 +8929,67 @@
         <v>1.87</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="DH20" t="n">
-        <v>107.75</v>
+        <v>104.11</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM20" t="n">
-        <v>49</v>
+        <v>46.78</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO20" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.37</v>
+        <v>11</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.63</v>
+        <v>12.44</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.62</v>
+        <v>50.67</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.88</v>
+        <v>17.11</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.88</v>
+        <v>11.56</v>
       </c>
       <c r="DZ20" t="n">
-        <v>6</v>
+        <v>5.56</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.75</v>
+        <v>16</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9128,31 +9128,31 @@
         <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>82</v>
+        <v>81.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.33</v>
+        <v>31</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21" t="n">
         <v>11</v>
@@ -9164,10 +9164,10 @@
         <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9179,82 +9179,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.67</v>
+        <v>43.75</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.67</v>
+        <v>6.75</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.33</v>
+        <v>4.75</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BD21" t="n">
-        <v>14.67</v>
+        <v>15.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BN21" t="n">
         <v>1</v>
       </c>
-      <c r="BK21" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BO21" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.71</v>
+        <v>4.25</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX21" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY21" t="n">
         <v>2.98</v>
@@ -9263,22 +9263,22 @@
         <v>3.24</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.87</v>
+        <v>6.96</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG21" t="n">
         <v>2.71</v>
@@ -9287,43 +9287,43 @@
         <v>1.37</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP21" t="n">
         <v>2.06</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV21" t="n">
         <v>1.8</v>
@@ -9335,64 +9335,64 @@
         <v>1.56</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.38</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DB21" t="n">
         <v>1.38</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DH21" t="n">
-        <v>85.43000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM21" t="n">
-        <v>32.71</v>
+        <v>34.25</v>
       </c>
       <c r="DN21" t="n">
         <v>1</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.71</v>
+        <v>12.5</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.71</v>
+        <v>14.75</v>
       </c>
       <c r="DR21" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="DS21" t="n">
         <v>0</v>
@@ -9404,28 +9404,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>41.86</v>
+        <v>41.75</v>
       </c>
       <c r="DW21" t="n">
         <v>0</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.72</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.86</v>
+        <v>6.38</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.43</v>
+        <v>19.12</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
@@ -2136,7 +2136,7 @@
         <v>2.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.89</v>
+        <v>15.11</v>
       </c>
       <c r="DQ3" t="n">
         <v>13.89</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="Q5" t="n">
         <v>11.67</v>
@@ -2678,139 +2678,139 @@
         <v>2.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.8</v>
+        <v>75.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.4</v>
+        <v>27.17</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.4</v>
+        <v>48.17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.2</v>
+        <v>4.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.8</v>
+        <v>17.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.92</v>
+        <v>1.11</v>
       </c>
       <c r="BF5" t="n">
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>2.86</v>
@@ -2819,25 +2819,25 @@
         <v>3.11</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2852,7 +2852,7 @@
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CM5" t="n">
         <v>2.54</v>
@@ -2867,7 +2867,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
@@ -2888,100 +2888,100 @@
         <v>1.97</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA5" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.62</v>
+        <v>72</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="DK5" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>25.5</v>
+        <v>26.67</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.5</v>
+        <v>12.11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.13</v>
+        <v>12.89</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.25</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.88</v>
+        <v>45.78</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>8.5</v>
+        <v>9.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.13</v>
+        <v>5.56</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>16.63</v>
+        <v>16.34</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>83.5</v>
+        <v>79</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>27.75</v>
+        <v>29.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="P9" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>13.6</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.5</v>
+        <v>41.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.25</v>
+        <v>13.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT9" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="CC9" t="n">
         <v>5.36</v>
@@ -4443,55 +4443,55 @@
         <v>5.91</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.98</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS9" t="n">
         <v>3.36</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV9" t="n">
         <v>1.81</v>
@@ -4509,58 +4509,58 @@
         <v>2.39</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DH9" t="n">
-        <v>70.67</v>
+        <v>69.7</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>29.11</v>
+        <v>29.8</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.89</v>
+        <v>11.5</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>40.44</v>
+        <v>39.4</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.89</v>
+        <v>7.7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.78</v>
+        <v>14.3</v>
       </c>
       <c r="EB9" t="n">
         <v>1.1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0.4</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AO10" t="n">
         <v>1</v>
       </c>
-      <c r="AH10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AP10" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.25</v>
+        <v>13.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.5</v>
+        <v>53.8</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.25</v>
+        <v>20.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.44</v>
+        <v>4.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.66</v>
@@ -4834,55 +4834,55 @@
         <v>1.67</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.58</v>
+        <v>3.49</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL10" t="n">
         <v>1.73</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO10" t="n">
         <v>1.34</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4903,100 +4903,100 @@
         <v>2.07</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>100.44</v>
+        <v>102.7</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="DM10" t="n">
-        <v>34.78</v>
+        <v>35.6</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.11</v>
+        <v>15.7</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.67</v>
+        <v>56.4</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.220000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.78</v>
+        <v>19.4</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
@@ -5499,52 +5499,52 @@
         <v>2.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>102</v>
+        <v>101.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.5</v>
+        <v>45.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.75</v>
+        <v>12.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.5</v>
+        <v>61.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5565,73 +5565,73 @@
         <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>13.75</v>
+        <v>12.4</v>
       </c>
       <c r="BE12" t="n">
         <v>1.66</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
         <v>1.7</v>
@@ -5640,67 +5640,67 @@
         <v>1.76</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.51</v>
+        <v>3.46</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK12" t="n">
         <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.69</v>
+        <v>3.83</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV12" t="n">
         <v>1.86</v>
@@ -5712,64 +5712,64 @@
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>102.22</v>
+        <v>101.8</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.44</v>
+        <v>5.9</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.78</v>
+        <v>43.9</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.11</v>
+        <v>11.1</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>59.22</v>
+        <v>60.3</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.890000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.78</v>
+        <v>14.9</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -6094,16 +6094,16 @@
         <v>3.29</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="CT13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CV13" t="n">
         <v>2</v>
@@ -6741,7 +6741,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
         <v>15.25</v>
@@ -6972,7 +6972,7 @@
         <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.25</v>
+        <v>11.38</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.38</v>
@@ -7303,16 +7303,16 @@
         <v>3.22</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CV16" t="n">
         <v>1.96</v>
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="n">
         <v>1.4</v>
@@ -7529,7 +7529,7 @@
         <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AL17" t="n">
         <v>3.6</v>
@@ -7592,7 +7592,7 @@
         <v>1.23</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BG17" t="n">
         <v>3</v>
@@ -7744,7 +7744,7 @@
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DG17" t="n">
         <v>2.33</v>
@@ -7756,7 +7756,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="DK17" t="n">
         <v>4.44</v>
@@ -7813,7 +7813,7 @@
         <v>1.36</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="18">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
@@ -8238,82 +8238,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="n">
-        <v>102.75</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>50.25</v>
+        <v>46</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.25</v>
+        <v>52.4</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.78</v>
+        <v>4.2</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.33</v>
+        <v>4.7</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT19" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC19" t="n">
         <v>3.14</v>
@@ -8469,22 +8469,22 @@
         <v>3.39</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK19" t="n">
         <v>1.44</v>
@@ -8493,19 +8493,19 @@
         <v>1.81</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
         <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="CR19" t="n">
         <v>1.51</v>
@@ -8526,16 +8526,16 @@
         <v>2</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
@@ -8544,82 +8544,82 @@
         <v>2.31</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>101</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="DM19" t="n">
-        <v>39.67</v>
+        <v>38.6</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.89</v>
+        <v>14.6</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>57.78</v>
+        <v>55.7</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.22</v>
+        <v>7.1</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.11</v>
+        <v>16.3</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -8629,61 +8629,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="H20" t="n">
-        <v>114.6</v>
+        <v>113.33</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>64.59999999999999</v>
+        <v>66.17</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="P20" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.4</v>
+        <v>12.17</v>
       </c>
       <c r="R20" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8695,28 +8695,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.6</v>
+        <v>55.17</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.8</v>
+        <v>19.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.2</v>
+        <v>16.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8752,7 +8752,7 @@
         <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>13.75</v>
@@ -8800,70 +8800,70 @@
         <v>1.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.44</v>
+        <v>9</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT20" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU20" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW20" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX20" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC20" t="n">
         <v>3.84</v>
@@ -8875,13 +8875,13 @@
         <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG20" t="n">
         <v>2.72</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI20" t="n">
         <v>1.9</v>
@@ -8893,7 +8893,7 @@
         <v>1.48</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM20" t="n">
         <v>2.51</v>
@@ -8905,10 +8905,10 @@
         <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CR20" t="n">
         <v>1.45</v>
@@ -8929,13 +8929,13 @@
         <v>1.87</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DA20" t="n">
         <v>2.03</v>
@@ -8950,46 +8950,46 @@
         <v>3.77</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="DH20" t="n">
-        <v>104.11</v>
+        <v>104.4</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>46.78</v>
+        <v>49.5</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DO20" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="DP20" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.44</v>
+        <v>12.8</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.44</v>
+        <v>6.6</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>50.67</v>
+        <v>51.9</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.11</v>
+        <v>17.1</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="EC20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -9155,7 +9155,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -9386,7 +9386,7 @@
         <v>1.5</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.5</v>
+        <v>12.62</v>
       </c>
       <c r="DQ21" t="n">
         <v>14.75</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>80.25</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>29.75</v>
+        <v>31.8</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>17.75</v>
+        <v>16.8</v>
       </c>
       <c r="R2" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.75</v>
+        <v>44.8</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC2" t="n">
         <v>3.57</v>
@@ -1625,40 +1625,40 @@
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.35</v>
       </c>
       <c r="CI2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>1.87</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.86</v>
       </c>
       <c r="CK2" t="n">
         <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN2" t="n">
         <v>2.02</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1667,7 +1667,7 @@
         <v>3.21</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU2" t="n">
         <v>1.38</v>
@@ -1694,52 +1694,52 @@
         <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.22</v>
+        <v>85.3</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.56</v>
+        <v>36</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.11</v>
+        <v>16.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.78</v>
+        <v>47.9</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.11</v>
+        <v>13.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.22</v>
+        <v>19.7</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0.8</v>
@@ -1872,49 +1872,49 @@
         <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>79</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>33.75</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU3" t="n">
         <v>1</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>39.75</v>
+        <v>42</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.25</v>
+        <v>19.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>2.13</v>
@@ -2019,16 +2019,16 @@
         <v>3.29</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="CE3" t="n">
         <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG3" t="n">
         <v>2.58</v>
@@ -2043,37 +2043,37 @@
         <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR3" t="n">
         <v>1.47</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV3" t="n">
         <v>1.86</v>
@@ -2097,85 +2097,85 @@
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="DH3" t="n">
-        <v>86.22</v>
+        <v>87.7</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.22</v>
+        <v>4.6</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.11</v>
+        <v>14.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.89</v>
+        <v>13.4</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.44</v>
+        <v>46.9</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.22</v>
+        <v>20</v>
       </c>
       <c r="EB3" t="n">
         <v>1.24</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -2185,25 +2185,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>100.5</v>
+        <v>105</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2212,34 +2212,34 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>34.75</v>
+        <v>40.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>14.25</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="R4" t="n">
-        <v>8.75</v>
+        <v>7.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.5</v>
+        <v>54.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.5</v>
+        <v>16.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>2.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="CC4" t="n">
         <v>3.04</v>
@@ -2431,16 +2431,16 @@
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CH4" t="n">
         <v>1.4</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.76</v>
@@ -2449,13 +2449,13 @@
         <v>1.44</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CO4" t="n">
         <v>1.29</v>
@@ -2464,13 +2464,13 @@
         <v>1.94</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT4" t="n">
         <v>3.06</v>
@@ -2488,13 +2488,13 @@
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
@@ -2503,79 +2503,79 @@
         <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.12</v>
+        <v>94.67</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.38</v>
+        <v>5.56</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DM4" t="n">
-        <v>31.38</v>
+        <v>35</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.25</v>
+        <v>14.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.619999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.25</v>
+        <v>51.22</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.38</v>
+        <v>12.22</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.5</v>
+        <v>7.22</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.88</v>
+        <v>18.11</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="EC4" t="n">
         <v>2</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3087,46 +3087,46 @@
         <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>105</v>
+        <v>100.8</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.5</v>
+        <v>41</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.5</v>
+        <v>15.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.25</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.75</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,70 +3138,70 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>53.75</v>
+        <v>52.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.25</v>
+        <v>19.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN6" t="n">
         <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.67</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>2.47</v>
@@ -3222,25 +3222,25 @@
         <v>2.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB6" t="n">
         <v>3.31</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.13</v>
+        <v>3.98</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
@@ -3249,28 +3249,28 @@
         <v>1.88</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3294,64 +3294,64 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DB6" t="n">
         <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.44</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.67</v>
+        <v>40.1</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.89</v>
+        <v>14.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.33</v>
+        <v>11.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.67</v>
+        <v>6.1</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.89</v>
+        <v>51.3</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.56</v>
+        <v>16.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.89</v>
+        <v>19.2</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
+        <v>77.33</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>31.6</v>
+        <v>34.83</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>12.8</v>
+        <v>13.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="R7" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>40.2</v>
+        <v>43.17</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.6</v>
+        <v>16.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.4</v>
+        <v>11.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.8</v>
+        <v>19.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.75</v>
+        <v>11.56</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW7" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="CC7" t="n">
         <v>6.45</v>
@@ -3640,49 +3640,49 @@
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.86</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO7" t="n">
         <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR7" t="n">
         <v>1.43</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
@@ -3697,97 +3697,97 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.49</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="DH7" t="n">
-        <v>74.25</v>
+        <v>75.89</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.25</v>
+        <v>4.78</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM7" t="n">
-        <v>28.75</v>
+        <v>31.22</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.13</v>
+        <v>10.56</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.38</v>
+        <v>42.34</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.12</v>
+        <v>13.55</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.25</v>
+        <v>10.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.12</v>
+        <v>21.11</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>103</v>
+        <v>105.4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>29.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.25</v>
+        <v>17.6</v>
       </c>
       <c r="R8" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.5</v>
+        <v>62.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.25</v>
+        <v>21.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,49 +3968,49 @@
         <v>3.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT8" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -4019,16 +4019,16 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB8" t="n">
         <v>3.29</v>
@@ -4040,16 +4040,16 @@
         <v>3.81</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI8" t="n">
         <v>1.81</v>
@@ -4061,19 +4061,19 @@
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO8" t="n">
         <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.95</v>
@@ -4100,64 +4100,64 @@
         <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.29</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DH8" t="n">
-        <v>92</v>
+        <v>94.3</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>26.11</v>
+        <v>28</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.22</v>
+        <v>13.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.33</v>
+        <v>16.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.56</v>
+        <v>7.1</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>55.67</v>
+        <v>56.6</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.67</v>
+        <v>7.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.33</v>
+        <v>19.4</v>
       </c>
       <c r="EB8" t="n">
         <v>1.1</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4245,10 +4245,10 @@
         <v>8.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S9" t="n">
         <v>0.8</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>41.6</v>
+        <v>42.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0.2</v>
@@ -4281,7 +4281,7 @@
         <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
@@ -4557,10 +4557,10 @@
         <v>10.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="DW9" t="n">
         <v>0.2</v>
@@ -4587,7 +4587,7 @@
         <v>3</v>
       </c>
       <c r="EA9" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="EB9" t="n">
         <v>1.1</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC10" t="n">
         <v>4.2</v>
@@ -4768,7 +4768,7 @@
         <v>20.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF10" t="n">
         <v>1.8</v>
@@ -4975,16 +4975,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.3</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>128.33</v>
+        <v>129.75</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M11" t="n">
         <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>13.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.67</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58</v>
+        <v>59.25</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.67</v>
+        <v>15.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>12.33</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.2</v>
@@ -5177,37 +5177,37 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5216,10 +5216,10 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BZ11" t="n">
         <v>1.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="CC11" t="n">
         <v>2.07</v>
@@ -5249,43 +5249,43 @@
         <v>2.07</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CN11" t="n">
         <v>1.97</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
@@ -5309,97 +5309,97 @@
         <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.91</v>
+        <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DH11" t="n">
-        <v>109.25</v>
+        <v>112</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>38.75</v>
+        <v>40</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO11" t="n">
         <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.75</v>
+        <v>13.33</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.5</v>
+        <v>14.11</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>54.62</v>
+        <v>55.56</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.5</v>
+        <v>13.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.630000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.87</v>
+        <v>17.11</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="12">
@@ -5535,7 +5535,7 @@
         <v>12.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="AS12" t="n">
         <v>8.199999999999999</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>61.6</v>
+        <v>61</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
         <v>5.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>12.4</v>
+        <v>14.2</v>
       </c>
       <c r="BE12" t="n">
         <v>1.66</v>
@@ -5766,7 +5766,7 @@
         <v>13.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="DR12" t="n">
         <v>6.7</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
@@ -5796,7 +5796,7 @@
         <v>6.2</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="EB12" t="n">
         <v>1.72</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.75</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>90.25</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>41.5</v>
+        <v>45.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="R13" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>47</v>
+        <v>50.2</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.75</v>
+        <v>15.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.25</v>
+        <v>15.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.78</v>
+        <v>8.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.11</v>
+        <v>4.7</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BS13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="CC13" t="n">
         <v>4.26</v>
@@ -6055,13 +6055,13 @@
         <v>4.73</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CH13" t="n">
         <v>1.4</v>
@@ -6073,25 +6073,25 @@
         <v>1.78</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
         <v>1.89</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CO13" t="n">
         <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6127,85 +6127,85 @@
         <v>1.32</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.53</v>
+        <v>3.46</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.22</v>
+        <v>95.2</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.33</v>
+        <v>38.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.56</v>
+        <v>12.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.67</v>
+        <v>51</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.44</v>
+        <v>8.4</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.89</v>
+        <v>17.4</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,49 +6305,49 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>102.75</v>
+        <v>94.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.75</v>
+        <v>40.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.25</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
@@ -6362,73 +6362,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.5</v>
+        <v>46.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.75</v>
+        <v>14.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BT14" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU14" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>1.99</v>
@@ -6446,55 +6446,55 @@
         <v>2.14</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CK14" t="n">
         <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CN14" t="n">
         <v>2.04</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6518,97 +6518,97 @@
         <v>1.49</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.52</v>
       </c>
       <c r="DA14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>101</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ14" t="n">
         <v>2.1</v>
       </c>
-      <c r="DB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>105.22</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>2</v>
-      </c>
       <c r="DK14" t="n">
-        <v>8.779999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
-        <v>48</v>
+        <v>46.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.22</v>
+        <v>15.6</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.33</v>
+        <v>13.6</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.78</v>
+        <v>50.1</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>15.78</v>
+        <v>15</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.67</v>
+        <v>10.1</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.44</v>
+        <v>19.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="EC14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -6630,49 +6630,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>4.25</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>99.25</v>
+        <v>95.8</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K15" t="n">
-        <v>6.75</v>
+        <v>7.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M15" t="n">
-        <v>51.25</v>
+        <v>49.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>11.25</v>
+        <v>10.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="R15" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.25</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.25</v>
+        <v>10.22</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.62</v>
+        <v>6.22</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BT15" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC15" t="n">
         <v>3.37</v>
@@ -6864,7 +6864,7 @@
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG15" t="n">
         <v>2.69</v>
@@ -6876,28 +6876,28 @@
         <v>1.91</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6921,64 +6921,64 @@
         <v>1.51</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.46</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DG15" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="DH15" t="n">
-        <v>106.25</v>
+        <v>103.56</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>52.75</v>
+        <v>51.56</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DO15" t="n">
         <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.38</v>
+        <v>12.11</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>58.88</v>
+        <v>58.33</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.38</v>
+        <v>10.67</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.75</v>
+        <v>20.89</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0.4</v>
@@ -7111,52 +7111,52 @@
         <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP16" t="n">
         <v>2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="AS16" t="n">
         <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43.25</v>
+        <v>42.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
         <v>1.11</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY16" t="n">
         <v>1.49</v>
@@ -7252,16 +7252,16 @@
         <v>1.56</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CE16" t="n">
         <v>1.39</v>
@@ -7270,46 +7270,46 @@
         <v>2.79</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CH16" t="n">
         <v>1.42</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK16" t="n">
         <v>1.41</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CO16" t="n">
         <v>1.28</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR16" t="n">
         <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU16" t="n">
         <v>1.43</v>
@@ -7324,97 +7324,97 @@
         <v>1.47</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.56</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.22</v>
+        <v>81.3</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.33</v>
+        <v>13.7</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.56</v>
+        <v>14</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.78</v>
+        <v>12.3</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.67</v>
+        <v>7.2</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="EA16" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>88.8</v>
+        <v>88.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.8</v>
+        <v>45.17</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>15.2</v>
+        <v>16.33</v>
       </c>
       <c r="BE17" t="n">
         <v>1.23</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.44</v>
+        <v>5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.33</v>
+        <v>5.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY17" t="n">
         <v>3.2</v>
@@ -7655,55 +7655,55 @@
         <v>3.4</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CC17" t="n">
-        <v>7.97</v>
+        <v>7.42</v>
       </c>
       <c r="CD17" t="n">
-        <v>9.130000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="CE17" t="n">
         <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7732,55 +7732,55 @@
         <v>2.39</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DH17" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DM17" t="n">
-        <v>29.67</v>
+        <v>30.4</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.89</v>
+        <v>11.6</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.78</v>
+        <v>12.2</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.22</v>
+        <v>7.8</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42.56</v>
+        <v>42</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.22</v>
+        <v>13</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.779999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.11</v>
+        <v>16.7</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>105</v>
+        <v>100.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.5</v>
+        <v>40.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.25</v>
+        <v>10.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.75</v>
+        <v>10.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49</v>
+        <v>46.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.75</v>
+        <v>11.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
-        <v>24</v>
+        <v>22.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT18" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY18" t="n">
         <v>2.08</v>
@@ -8054,55 +8054,55 @@
         <v>2.18</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.41</v>
+        <v>3.54</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.79</v>
+        <v>4.58</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.38</v>
+        <v>5.35</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CK18" t="n">
         <v>1.39</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO18" t="n">
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
@@ -8135,88 +8135,88 @@
         <v>2.2</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH18" t="n">
-        <v>101.78</v>
+        <v>99.7</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.44</v>
+        <v>5.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.22</v>
+        <v>40.9</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="DP18" t="n">
         <v>12</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.33</v>
+        <v>13.1</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.67</v>
+        <v>6.9</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.89</v>
+        <v>48.6</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.67</v>
+        <v>12.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.56</v>
+        <v>20.2</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8292,7 +8292,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9128,133 +9128,133 @@
         <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>81.5</v>
+        <v>83.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>31</v>
+        <v>30.4</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43.75</v>
+        <v>43.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.75</v>
+        <v>8.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>15.25</v>
+        <v>14.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BN21" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU21" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV21" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW21" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX21" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY21" t="n">
         <v>2.98</v>
@@ -9263,52 +9263,52 @@
         <v>3.24</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.56</v>
+        <v>3.49</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.6</v>
+        <v>5.06</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.96</v>
+        <v>6.16</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH21" t="n">
         <v>1.37</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK21" t="n">
         <v>1.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO21" t="n">
         <v>1.32</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ21" t="n">
         <v>3.57</v>
@@ -9317,7 +9317,7 @@
         <v>1.46</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CT21" t="n">
         <v>2.82</v>
@@ -9335,97 +9335,97 @@
         <v>1.56</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.38</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC21" t="n">
         <v>2.17</v>
       </c>
       <c r="DD21" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DG21" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="DH21" t="n">
-        <v>84.75</v>
+        <v>85.33</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.62</v>
+        <v>4.22</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM21" t="n">
-        <v>34.25</v>
+        <v>33.56</v>
       </c>
       <c r="DN21" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.75</v>
+        <v>14.78</v>
       </c>
       <c r="DR21" t="n">
-        <v>6.88</v>
+        <v>7.78</v>
       </c>
       <c r="DS21" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT21" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>41.75</v>
+        <v>41.78</v>
       </c>
       <c r="DW21" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX21" t="n">
-        <v>9.880000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.5</v>
+        <v>4.11</v>
       </c>
       <c r="EA21" t="n">
-        <v>19.12</v>
+        <v>18.33</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -3120,7 +3120,7 @@
         <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -3351,7 +3351,7 @@
         <v>11.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
         <v>2.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>16.33</v>
+        <v>16.5</v>
       </c>
       <c r="BE17" t="n">
         <v>1.23</v>
@@ -7807,7 +7807,7 @@
         <v>4.4</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="EB17" t="n">
         <v>1.35</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.4</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.2</v>
+        <v>41.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="BB2" t="n">
         <v>9</v>
       </c>
-      <c r="AR2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>51</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.2</v>
+        <v>20.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BH2" t="n">
-        <v>11</v>
+        <v>11.09</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU2" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY2" t="n">
         <v>2.19</v>
@@ -1613,52 +1613,52 @@
         <v>3.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.86</v>
+        <v>3.79</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH2" t="n">
         <v>1.35</v>
       </c>
       <c r="CI2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>1.86</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.87</v>
       </c>
       <c r="CK2" t="n">
         <v>1.45</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
         <v>2.57</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP2" t="n">
         <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1682,13 +1682,13 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.55</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB2" t="n">
         <v>1.38</v>
@@ -1697,49 +1697,49 @@
         <v>2.21</v>
       </c>
       <c r="DD2" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.3</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DM2" t="n">
-        <v>36</v>
+        <v>37.18</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.6</v>
+        <v>10.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.7</v>
+        <v>15.91</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>47.9</v>
+        <v>48.55</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.7</v>
+        <v>19.55</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.75</v>
+        <v>85.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1</v>
       </c>
-      <c r="AN4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AP4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.25</v>
+        <v>14.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47</v>
+        <v>49.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.25</v>
+        <v>10.2</v>
       </c>
       <c r="BB4" t="n">
         <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.25</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="BF4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG4" t="n">
         <v>2.5</v>
       </c>
-      <c r="BG4" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BH4" t="n">
-        <v>10.44</v>
+        <v>10.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>2.06</v>
@@ -2416,16 +2416,16 @@
         <v>2.05</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC4" t="n">
         <v>3.04</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CE4" t="n">
         <v>1.39</v>
@@ -2443,34 +2443,34 @@
         <v>2.01</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL4" t="n">
         <v>1.83</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP4" t="n">
         <v>1.94</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CR4" t="n">
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CT4" t="n">
         <v>3.06</v>
@@ -2488,13 +2488,13 @@
         <v>1.58</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.31</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB4" t="n">
         <v>1.3</v>
@@ -2503,82 +2503,82 @@
         <v>1.96</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DH4" t="n">
-        <v>94.67</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DM4" t="n">
-        <v>35</v>
+        <v>36.9</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.11</v>
+        <v>16.4</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.22</v>
+        <v>51.9</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.22</v>
+        <v>7.1</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.11</v>
+        <v>17.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>93.8</v>
+        <v>89.17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>32.2</v>
+        <v>32.67</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.6</v>
+        <v>13.67</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.4</v>
+        <v>9.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="BR13" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BY13" t="n">
         <v>2.03</v>
@@ -6043,31 +6043,31 @@
         <v>2.07</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CB13" t="n">
         <v>3.58</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="CE13" t="n">
         <v>1.37</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CH13" t="n">
         <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.78</v>
@@ -6076,10 +6076,10 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN13" t="n">
         <v>1.98</v>
@@ -6124,88 +6124,88 @@
         <v>1.97</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
         <v>2.01</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.2</v>
+        <v>92.55</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.9</v>
+        <v>38.55</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.9</v>
+        <v>10.45</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.2</v>
+        <v>12.82</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51</v>
+        <v>50.64</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.4</v>
+        <v>7.91</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="EA13" t="n">
-        <v>17.4</v>
+        <v>17.91</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
@@ -6227,82 +6227,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="n">
-        <v>107.2</v>
+        <v>106.67</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M14" t="n">
-        <v>52.2</v>
+        <v>52.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P14" t="n">
-        <v>15.2</v>
+        <v>13.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.4</v>
+        <v>13.67</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.2</v>
+        <v>19.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6386,49 +6386,49 @@
         <v>2.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.2</v>
+        <v>5.91</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT14" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU14" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
         <v>3.96</v>
@@ -6464,7 +6464,7 @@
         <v>2.83</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
@@ -6494,7 +6494,7 @@
         <v>1.97</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.36</v>
@@ -6533,82 +6533,82 @@
         <v>1.96</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="DH14" t="n">
-        <v>101</v>
+        <v>101.27</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.5</v>
+        <v>47.27</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.6</v>
+        <v>14.82</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.6</v>
+        <v>14.18</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.1</v>
+        <v>50.36</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>15</v>
+        <v>14.64</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.4</v>
+        <v>19.45</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -6630,49 +6630,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H15" t="n">
-        <v>95.8</v>
+        <v>93.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="K15" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>49.4</v>
+        <v>47</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>10.4</v>
+        <v>11.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>10.33</v>
       </c>
       <c r="R15" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56</v>
+        <v>53.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
         <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT15" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC15" t="n">
         <v>3.37</v>
@@ -6861,55 +6861,55 @@
         <v>3.5</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK15" t="n">
         <v>1.36</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CN15" t="n">
         <v>2.17</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
         <v>1.93</v>
@@ -6930,55 +6930,55 @@
         <v>2.17</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="DH15" t="n">
-        <v>103.56</v>
+        <v>101.3</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.56</v>
+        <v>49.9</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.11</v>
+        <v>12.3</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>58.33</v>
+        <v>56.7</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.78</v>
+        <v>15.8</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.89</v>
+        <v>20.4</v>
       </c>
       <c r="EB15" t="n">
         <v>1.72</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -7424,61 +7424,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>80.25</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M17" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.75</v>
+        <v>11.4</v>
       </c>
       <c r="R17" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>37.25</v>
+        <v>38.4</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>13.75</v>
+        <v>13.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.25</v>
+        <v>17.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP17" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU17" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX17" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
         <v>7.42</v>
@@ -7670,37 +7670,37 @@
         <v>1.37</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.22</v>
@@ -7721,66 +7721,66 @@
         <v>1.94</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DB17" t="n">
         <v>1.3</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DH17" t="n">
-        <v>85.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.4</v>
+        <v>30.27</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7792,28 +7792,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42</v>
+        <v>42.09</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13</v>
+        <v>12.91</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="H18" t="n">
-        <v>99.2</v>
+        <v>100.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>13.4</v>
+        <v>12.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.6</v>
+        <v>15.83</v>
       </c>
       <c r="R18" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.6</v>
+        <v>49.67</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.800000000000001</v>
+        <v>11.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.8</v>
+        <v>8.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BR18" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS18" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC18" t="n">
         <v>4.58</v>
@@ -8069,7 +8069,7 @@
         <v>1.4</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG18" t="n">
         <v>2.71</v>
@@ -8084,13 +8084,13 @@
         <v>1.84</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CN18" t="n">
         <v>2.13</v>
@@ -8099,10 +8099,10 @@
         <v>1.31</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
@@ -8111,7 +8111,7 @@
         <v>3.22</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU18" t="n">
         <v>1.37</v>
@@ -8132,7 +8132,7 @@
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB18" t="n">
         <v>1.36</v>
@@ -8147,73 +8147,73 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DH18" t="n">
-        <v>99.7</v>
+        <v>100.18</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.9</v>
+        <v>42</v>
       </c>
       <c r="DN18" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="DP18" t="n">
-        <v>12</v>
+        <v>11.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.1</v>
+        <v>13.45</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.6</v>
+        <v>48.27</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.2</v>
+        <v>12.73</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.2</v>
+        <v>20.36</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
         <v>3</v>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8319,55 +8319,55 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AI19" t="n">
-        <v>99.59999999999999</v>
+        <v>99.67</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.2</v>
+        <v>36.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.2</v>
+        <v>15.33</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.2</v>
+        <v>13.67</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
@@ -8376,79 +8376,79 @@
         <v>59</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.6</v>
+        <v>10.67</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="BD19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.1</v>
+        <v>9.82</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT19" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU19" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY19" t="n">
         <v>2.41</v>
@@ -8457,25 +8457,25 @@
         <v>2.44</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CH19" t="n">
         <v>1.32</v>
@@ -8484,7 +8484,7 @@
         <v>1.8</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK19" t="n">
         <v>1.44</v>
@@ -8496,25 +8496,25 @@
         <v>2.61</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CU19" t="n">
         <v>1.34</v>
@@ -8526,100 +8526,100 @@
         <v>2</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY19" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DA19" t="n">
         <v>2.01</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="DG19" t="n">
         <v>3</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.09999999999999</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.6</v>
+        <v>40.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.6</v>
+        <v>14.27</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.6</v>
+        <v>55.91</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.8</v>
+        <v>11.27</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.1</v>
+        <v>7.45</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.3</v>
+        <v>16.27</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="20">
@@ -8629,13 +8629,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0.17</v>
@@ -8722,13 +8722,13 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -8737,34 +8737,34 @@
         <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AN20" t="n">
-        <v>24.5</v>
+        <v>31.4</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.75</v>
+        <v>13.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8776,82 +8776,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>13.75</v>
+        <v>14.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>15.75</v>
+        <v>17.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BH20" t="n">
         <v>9</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT20" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV20" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW20" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX20" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BY20" t="n">
         <v>2.44</v>
@@ -8860,46 +8860,46 @@
         <v>2.43</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="CE20" t="n">
         <v>1.41</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.8</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CL20" t="n">
         <v>1.87</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO20" t="n">
         <v>1.32</v>
@@ -8908,7 +8908,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CR20" t="n">
         <v>1.45</v>
@@ -8932,64 +8932,64 @@
         <v>1.54</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.41</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF20" t="n">
         <v>1.36</v>
       </c>
-      <c r="DC20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="DE20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="DG20" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DH20" t="n">
-        <v>104.4</v>
+        <v>105.91</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ20" t="n">
         <v>2</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.5</v>
+        <v>50.37</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DO20" t="n">
         <v>3</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.3</v>
+        <v>11.36</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.6</v>
+        <v>6.91</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -9001,28 +9001,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>51.9</v>
+        <v>52.37</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.1</v>
+        <v>17.27</v>
       </c>
       <c r="DY20" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="EA20" t="n">
-        <v>16.3</v>
+        <v>17</v>
       </c>
       <c r="EB20" t="n">
         <v>1.82</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="21">
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -9044,49 +9044,49 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>88</v>
+        <v>86.8</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M21" t="n">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="R21" t="n">
-        <v>7.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -9098,28 +9098,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>39.75</v>
+        <v>40</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9203,70 +9203,70 @@
         <v>2.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.67</v>
+        <v>9.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT21" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU21" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV21" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW21" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX21" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="CC21" t="n">
         <v>5.06</v>
@@ -9275,55 +9275,55 @@
         <v>6.16</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.93</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN21" t="n">
         <v>1.93</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV21" t="n">
         <v>1.8</v>
@@ -9332,100 +9332,100 @@
         <v>2.07</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY21" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="DA21" t="n">
         <v>1.97</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DD21" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>85</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DK21" t="n">
         <v>3.9</v>
       </c>
-      <c r="DE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DG21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="DH21" t="n">
-        <v>85.33</v>
-      </c>
-      <c r="DI21" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DJ21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="DK21" t="n">
-        <v>4.22</v>
-      </c>
       <c r="DL21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM21" t="n">
-        <v>33.56</v>
+        <v>32.7</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.78</v>
+        <v>12.5</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="DR21" t="n">
-        <v>7.78</v>
+        <v>8</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>41.78</v>
+        <v>41.7</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.44</v>
+        <v>10.9</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="DZ21" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="EA21" t="n">
-        <v>18.33</v>
+        <v>17.9</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1439,19 +1439,19 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.62</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
         <v>9.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
         <v>18.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
         <v>0.88</v>
@@ -1745,19 +1745,19 @@
         <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.93</v>
+        <v>13.88</v>
       </c>
       <c r="DY2" t="n">
         <v>9.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="EA2" t="n">
         <v>19.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
         <v>1.56</v>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>55.38</v>
+        <v>55.25</v>
       </c>
       <c r="Y4" t="n">
         <v>0.12</v>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.2</v>
+        <v>53.13</v>
       </c>
       <c r="DW4" t="n">
         <v>0.13</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.75</v>
+        <v>51.62</v>
       </c>
       <c r="Y6" t="n">
         <v>0.25</v>
@@ -3060,7 +3060,7 @@
         <v>4.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.12</v>
+        <v>18.25</v>
       </c>
       <c r="AD6" t="n">
         <v>1.74</v>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.12</v>
+        <v>51.06</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
@@ -3366,7 +3366,7 @@
         <v>4.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.37</v>
+        <v>19.44</v>
       </c>
       <c r="EB6" t="n">
         <v>1.66</v>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>51</v>
+        <v>51.11</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.33</v>
@@ -6172,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.88</v>
+        <v>49.94</v>
       </c>
       <c r="DW13" t="n">
         <v>0.19</v>
@@ -9167,16 +9167,16 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43.5</v>
+        <v>43.62</v>
       </c>
       <c r="AZ21" t="n">
         <v>0.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.25</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="BC21" t="n">
         <v>3</v>
@@ -9185,7 +9185,7 @@
         <v>13.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="BF21" t="n">
         <v>2.75</v>
@@ -9392,16 +9392,16 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.2</v>
+        <v>44.26</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.47</v>
+        <v>10.54</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.6</v>
+        <v>6.67</v>
       </c>
       <c r="DZ21" t="n">
         <v>3.87</v>
@@ -9410,7 +9410,7 @@
         <v>16.8</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC21" t="n">
         <v>2.54</v>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1460,136 +1460,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>94.25</v>
+        <v>91.56</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.75</v>
+        <v>5.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>42.12</v>
+        <v>40.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.12</v>
+        <v>11.44</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.38</v>
+        <v>15.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52.25</v>
+        <v>51.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.88</v>
+        <v>19.78</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.5</v>
+        <v>10.06</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.19</v>
+        <v>4.94</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY2" t="n">
         <v>2.37</v>
@@ -1601,61 +1601,61 @@
         <v>3.32</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.54</v>
+        <v>3.63</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.91</v>
+        <v>4.06</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL2" t="n">
         <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
         <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS2" t="n">
         <v>3.24</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU2" t="n">
         <v>1.37</v>
@@ -1676,91 +1676,91 @@
         <v>2.54</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="DE2" t="n">
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.44</v>
+        <v>86.41</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.25</v>
+        <v>4.94</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.18</v>
+        <v>38.41</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.93</v>
+        <v>11.12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.32</v>
+        <v>15.29</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.06</v>
+        <v>48.65</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.88</v>
+        <v>13.71</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.69</v>
+        <v>19.18</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="3">
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.44</v>
@@ -1860,52 +1860,52 @@
         <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>84.29000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.43</v>
+        <v>4.25</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.71</v>
+        <v>39</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.71</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1917,82 +1917,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.86</v>
+        <v>45.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.859999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.57</v>
+        <v>18.38</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.44</v>
+        <v>9.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY3" t="n">
         <v>2.04</v>
@@ -2001,16 +2001,16 @@
         <v>2.19</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.85</v>
+        <v>4.69</v>
       </c>
       <c r="CE3" t="n">
         <v>1.43</v>
@@ -2022,34 +2022,34 @@
         <v>2.61</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL3" t="n">
         <v>1.75</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP3" t="n">
         <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CR3" t="n">
         <v>1.46</v>
@@ -2073,97 +2073,97 @@
         <v>1.5</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>85.25</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.81</v>
+        <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.81</v>
+        <v>37.47</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.81</v>
+        <v>12.58</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.19</v>
+        <v>7.3</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.88</v>
+        <v>48.36</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>12</v>
+        <v>12.23</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.75</v>
+        <v>19.59</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="4">
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2666,139 +2666,139 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.12</v>
+        <v>80.22</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.75</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.38</v>
+        <v>12.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>12.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.62</v>
+        <v>49.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.12</v>
+        <v>11.44</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.25</v>
+        <v>17.44</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.73</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT5" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BY5" t="n">
         <v>2.39</v>
@@ -2807,55 +2807,55 @@
         <v>2.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="CE5" t="n">
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK5" t="n">
         <v>1.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
         <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
@@ -2888,88 +2888,88 @@
         <v>1.95</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>81.73</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.8</v>
+        <v>38.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.93</v>
+        <v>13.31</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.33</v>
+        <v>11.88</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.46</v>
+        <v>48.31</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.2</v>
+        <v>12.31</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.27</v>
+        <v>7.32</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.13</v>
+        <v>17.69</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="6">
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3069,52 +3069,52 @@
         <v>2.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>96.62</v>
+        <v>94.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.38</v>
+        <v>38.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.62</v>
+        <v>15.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.12</v>
+        <v>11.22</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.88</v>
+        <v>7.44</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3126,82 +3126,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>50.5</v>
+        <v>49.56</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.38</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.88</v>
+        <v>5.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.62</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.88</v>
+        <v>10.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.56</v>
+        <v>5.18</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY6" t="n">
         <v>2.32</v>
@@ -3210,7 +3210,7 @@
         <v>2.32</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB6" t="n">
         <v>3.43</v>
@@ -3219,13 +3219,13 @@
         <v>3.38</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CE6" t="n">
         <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG6" t="n">
         <v>2.68</v>
@@ -3243,16 +3243,16 @@
         <v>1.37</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM6" t="n">
         <v>2.83</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
         <v>2.11</v>
@@ -3261,13 +3261,13 @@
         <v>3.68</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
@@ -3282,7 +3282,7 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
@@ -3294,22 +3294,22 @@
         <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.18000000000001</v>
+        <v>87.47</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
@@ -3318,28 +3318,28 @@
         <v>3.06</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.56</v>
+        <v>43.76</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.81</v>
+        <v>14.76</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.06</v>
+        <v>11.59</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.75</v>
+        <v>6.58</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3351,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.06</v>
+        <v>50.53</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>16</v>
+        <v>16.29</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.12</v>
+        <v>11.18</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.44</v>
+        <v>19.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
         <v>2.94</v>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3475,136 +3475,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" t="n">
-        <v>73.17</v>
+        <v>71</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL7" t="n">
         <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>27.29</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>13.71</v>
       </c>
       <c r="AR7" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>39</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>13.33</v>
-      </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY7" t="n">
         <v>2.95</v>
@@ -3613,31 +3613,31 @@
         <v>3.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.83</v>
+        <v>3.96</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.03</v>
+        <v>7.53</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.33</v>
+        <v>8.68</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.86</v>
@@ -3649,19 +3649,19 @@
         <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN7" t="n">
         <v>2.15</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3697,85 +3697,85 @@
         <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.93000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.4</v>
+        <v>33.13</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.34</v>
+        <v>12.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.93</v>
+        <v>10.12</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.13</v>
+        <v>10.25</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.27</v>
+        <v>42.69</v>
       </c>
       <c r="DW7" t="n">
         <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.6</v>
+        <v>9.25</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="EA7" t="n">
-        <v>20</v>
+        <v>20.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="8">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3797,46 +3797,46 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H8" t="n">
-        <v>94.5</v>
+        <v>96.56</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="K8" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>36.11</v>
       </c>
       <c r="N8" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P8" t="n">
-        <v>14.5</v>
+        <v>14.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.75</v>
+        <v>16.44</v>
       </c>
       <c r="R8" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -3851,28 +3851,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>54.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.38</v>
+        <v>12.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.88</v>
+        <v>20.11</v>
       </c>
       <c r="AD8" t="n">
         <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3956,67 +3956,67 @@
         <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.69</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.56</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB8" t="n">
         <v>3.22</v>
@@ -4028,13 +4028,13 @@
         <v>3.49</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH8" t="n">
         <v>1.31</v>
@@ -4043,16 +4043,16 @@
         <v>1.78</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK8" t="n">
         <v>1.43</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN8" t="n">
         <v>1.99</v>
@@ -4061,10 +4061,10 @@
         <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4073,7 +4073,7 @@
         <v>3.35</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CU8" t="n">
         <v>1.34</v>
@@ -4103,46 +4103,46 @@
         <v>2.39</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.88</v>
+        <v>93.12</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.81</v>
+        <v>34</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.19</v>
+        <v>13.3</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.62</v>
+        <v>16.47</v>
       </c>
       <c r="DR8" t="n">
         <v>8.119999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.69</v>
+        <v>53.94</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="EA8" t="n">
-        <v>17.81</v>
+        <v>18.06</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="9">
@@ -4591,94 +4591,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="H10" t="n">
-        <v>106.62</v>
+        <v>104.44</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="L10" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>40.88</v>
+        <v>43.67</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>14.25</v>
+        <v>14.11</v>
       </c>
       <c r="Q10" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z10" t="n">
         <v>15</v>
       </c>
-      <c r="R10" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>56.75</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14.62</v>
-      </c>
       <c r="AA10" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.88</v>
+        <v>19.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
         <v>2.94</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="BI10" t="n">
         <v>2.94</v>
@@ -4774,58 +4774,58 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
         <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.59</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="CC10" t="n">
         <v>3.43</v>
@@ -4834,22 +4834,22 @@
         <v>3.98</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK10" t="n">
         <v>1.39</v>
@@ -4864,13 +4864,13 @@
         <v>2.08</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4903,88 +4903,88 @@
         <v>2.1</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="DH10" t="n">
-        <v>100.37</v>
+        <v>99.58</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.12</v>
+        <v>5.35</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.75</v>
+        <v>41.29</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.57</v>
+        <v>14.47</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.94</v>
+        <v>15.83</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.75</v>
+        <v>7.82</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.25</v>
+        <v>55.88</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.62</v>
+        <v>13.88</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.63</v>
+        <v>19.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="11">
@@ -4994,94 +4994,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>113.5</v>
+        <v>116.71</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="K11" t="n">
-        <v>4.67</v>
+        <v>5.14</v>
       </c>
       <c r="L11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M11" t="n">
-        <v>52.17</v>
+        <v>56.57</v>
       </c>
       <c r="N11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P11" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.67</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>56.33</v>
+        <v>55.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.83</v>
+        <v>16.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.5</v>
+        <v>11.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5165,49 +5165,49 @@
         <v>2.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5216,19 +5216,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CC11" t="n">
         <v>2.1</v>
@@ -5237,34 +5237,34 @@
         <v>2.09</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH11" t="n">
         <v>1.38</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.96</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.31</v>
@@ -5273,7 +5273,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5297,7 +5297,7 @@
         <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.33</v>
@@ -5309,85 +5309,85 @@
         <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD11" t="n">
         <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>106.19</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DO11" t="n">
         <v>2.13</v>
       </c>
-      <c r="DH11" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>45.13</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2</v>
-      </c>
       <c r="DP11" t="n">
-        <v>12.87</v>
+        <v>12.63</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>54.8</v>
+        <v>54.38</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.93</v>
+        <v>14.44</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="EA11" t="n">
-        <v>15</v>
+        <v>15.25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5487,52 +5487,52 @@
         <v>2.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>99.43000000000001</v>
+        <v>99.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.14</v>
+        <v>44.38</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.29</v>
+        <v>13.38</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5544,82 +5544,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>60.71</v>
+        <v>61.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.71</v>
+        <v>13.25</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>15.29</v>
+        <v>15.88</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU12" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY12" t="n">
         <v>1.77</v>
@@ -5628,34 +5628,34 @@
         <v>1.85</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK12" t="n">
         <v>1.47</v>
@@ -5664,28 +5664,28 @@
         <v>1.86</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN12" t="n">
         <v>1.94</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU12" t="n">
         <v>1.38</v>
@@ -5697,67 +5697,67 @@
         <v>2.01</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY12" t="n">
         <v>1.81</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA12" t="n">
         <v>2</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="DH12" t="n">
-        <v>104.19</v>
+        <v>103.82</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM12" t="n">
-        <v>48.19</v>
+        <v>47.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.19</v>
+        <v>13.24</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.38</v>
+        <v>12.36</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.38</v>
+        <v>6.53</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>59.93</v>
+        <v>60.35</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.31</v>
+        <v>15</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.06</v>
+        <v>5.76</v>
       </c>
       <c r="EA12" t="n">
-        <v>17</v>
+        <v>17.18</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="13">
@@ -5800,94 +5800,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>85.43000000000001</v>
+        <v>87.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="J13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K13" t="n">
-        <v>4.43</v>
+        <v>4.88</v>
       </c>
       <c r="L13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>45.43</v>
+        <v>45.5</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="R13" t="n">
-        <v>7.29</v>
+        <v>6.88</v>
       </c>
       <c r="S13" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.43</v>
+        <v>48.62</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.29</v>
+        <v>14.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.29</v>
+        <v>14.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,70 +5971,70 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.06</v>
+        <v>8.35</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BL13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.88</v>
       </c>
-      <c r="BM13" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BP13" t="n">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT13" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC13" t="n">
         <v>4.5</v>
@@ -6043,19 +6043,19 @@
         <v>4.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH13" t="n">
         <v>1.39</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.81</v>
@@ -6064,7 +6064,7 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM13" t="n">
         <v>2.52</v>
@@ -6076,10 +6076,10 @@
         <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6103,64 +6103,64 @@
         <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="DE13" t="n">
         <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG13" t="n">
         <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.19</v>
+        <v>86</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.63</v>
+        <v>3.88</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.19</v>
+        <v>38.65</v>
       </c>
       <c r="DN13" t="n">
         <v>0.88</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.44</v>
+        <v>12.41</v>
       </c>
       <c r="DQ13" t="n">
         <v>12.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.94</v>
+        <v>8.65</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6175,25 +6175,25 @@
         <v>49.94</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.38</v>
+        <v>16.12</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6293,139 +6293,139 @@
         <v>2.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="AI14" t="n">
-        <v>103.43</v>
+        <v>105</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.86</v>
+        <v>54.25</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN14" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>49.14</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.31</v>
       </c>
       <c r="BO14" t="n">
         <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.12</v>
+        <v>5.29</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.12</v>
+        <v>5.88</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY14" t="n">
         <v>1.96</v>
@@ -6434,22 +6434,22 @@
         <v>2.08</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG14" t="n">
         <v>2.75</v>
@@ -6470,19 +6470,19 @@
         <v>1.82</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO14" t="n">
         <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
@@ -6506,64 +6506,64 @@
         <v>1.48</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.53</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB14" t="n">
         <v>1.33</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.75</v>
+        <v>107.29</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="DM14" t="n">
-        <v>54.31</v>
+        <v>55.29</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.44</v>
+        <v>15.59</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.19</v>
+        <v>14.24</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.44</v>
+        <v>7</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.69</v>
+        <v>51.06</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>15.38</v>
+        <v>15.64</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.12</v>
+        <v>10.59</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.31</v>
+        <v>20.71</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6618,82 +6618,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="H15" t="n">
-        <v>94.75</v>
+        <v>93.22</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M15" t="n">
-        <v>45.38</v>
+        <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>12.62</v>
+        <v>12.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>52.5</v>
+        <v>50.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.88</v>
+        <v>16.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.88</v>
+        <v>6.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.62</v>
+        <v>19.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6777,70 @@
         <v>2.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CC15" t="n">
         <v>3.7</v>
@@ -6852,52 +6852,52 @@
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH15" t="n">
         <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL15" t="n">
         <v>1.7</v>
       </c>
       <c r="CM15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CT15" t="n">
         <v>2.88</v>
       </c>
-      <c r="CN15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>2.93</v>
-      </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV15" t="n">
         <v>1.93</v>
@@ -6906,67 +6906,67 @@
         <v>1.93</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DD15" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DG15" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.67</v>
+        <v>91.94</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.93</v>
+        <v>5.81</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.27</v>
+        <v>44.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.66</v>
+        <v>12.63</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.93</v>
+        <v>7.06</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.73</v>
+        <v>51.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.34</v>
+        <v>14.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.74</v>
+        <v>9.44</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.46</v>
+        <v>20.25</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7099,52 +7099,52 @@
         <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.25</v>
+        <v>78.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.25</v>
+        <v>36.22</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.5</v>
+        <v>15.89</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.38</v>
+        <v>48.78</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.75</v>
+        <v>16.11</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.38</v>
+        <v>12.35</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.81</v>
+        <v>6.76</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU16" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY16" t="n">
         <v>1.55</v>
@@ -7240,25 +7240,25 @@
         <v>1.62</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="CE16" t="n">
         <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH16" t="n">
         <v>1.39</v>
@@ -7273,7 +7273,7 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM16" t="n">
         <v>2.79</v>
@@ -7288,7 +7288,7 @@
         <v>1.98</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CR16" t="n">
         <v>1.43</v>
@@ -7312,64 +7312,64 @@
         <v>1.47</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.54</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC16" t="n">
         <v>2.1</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DE16" t="n">
         <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.81999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.32</v>
+        <v>6.18</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.06</v>
+        <v>39.35</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.31</v>
+        <v>13.65</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.5</v>
+        <v>13.23</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.25</v>
+        <v>7.59</v>
       </c>
       <c r="DS16" t="n">
         <v>0.06</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.25</v>
+        <v>49.41</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.18</v>
+        <v>13.12</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.56</v>
+        <v>17.18</v>
       </c>
       <c r="EB16" t="n">
         <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="17">
@@ -7412,61 +7412,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="H17" t="n">
-        <v>83.70999999999999</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="K17" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="M17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="R17" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7478,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39</v>
+        <v>39.62</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>13.71</v>
+        <v>12.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.859999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>19</v>
+        <v>18.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7586,67 +7586,67 @@
         <v>2.88</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.81</v>
+        <v>10.94</v>
       </c>
       <c r="BI17" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.06</v>
+        <v>5.29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.69</v>
+        <v>5.59</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CC17" t="n">
         <v>6.49</v>
@@ -7658,19 +7658,19 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK17" t="n">
         <v>1.34</v>
@@ -7685,13 +7685,13 @@
         <v>2.23</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
@@ -7713,62 +7713,62 @@
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DH17" t="n">
-        <v>87.69</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DO17" t="n">
         <v>2.18</v>
       </c>
-      <c r="DK17" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="DL17" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DM17" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DO17" t="n">
-        <v>2.19</v>
-      </c>
       <c r="DP17" t="n">
-        <v>11.06</v>
+        <v>10.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.18</v>
+        <v>12.3</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7780,28 +7780,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42.69</v>
+        <v>42.76</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.93</v>
+        <v>12.35</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.75</v>
+        <v>18.59</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="18">
@@ -7811,13 +7811,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7904,136 +7904,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>89.29000000000001</v>
+        <v>90.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>42</v>
+        <v>42.12</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45</v>
+        <v>45.62</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
       <c r="BE18" t="n">
         <v>1.43</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.12</v>
+        <v>10.29</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX18" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY18" t="n">
         <v>2.13</v>
@@ -8042,22 +8042,22 @@
         <v>2.13</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.73</v>
+        <v>4.51</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.59</v>
+        <v>5.34</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CG18" t="n">
         <v>2.71</v>
@@ -8072,16 +8072,16 @@
         <v>1.86</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CO18" t="n">
         <v>1.32</v>
@@ -8090,7 +8090,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
@@ -8111,16 +8111,16 @@
         <v>1.92</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DB18" t="n">
         <v>1.35</v>
@@ -8129,82 +8129,82 @@
         <v>2.11</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.44</v>
+        <v>94.52</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.19</v>
+        <v>42.23</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.81</v>
+        <v>11.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.63</v>
+        <v>13.53</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.5</v>
+        <v>48.58</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.13</v>
+        <v>12.18</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.94</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.94</v>
+        <v>18.65</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="19">
@@ -8214,94 +8214,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="H19" t="n">
-        <v>85.14</v>
+        <v>87.12</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="K19" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>47.29</v>
+        <v>46.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>12.57</v>
+        <v>13.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.86</v>
+        <v>14.5</v>
       </c>
       <c r="R19" t="n">
-        <v>6.14</v>
+        <v>6.88</v>
       </c>
       <c r="S19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.43</v>
+        <v>50.88</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.57</v>
+        <v>13.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>15</v>
+        <v>16.12</v>
       </c>
       <c r="AD19" t="n">
         <v>1.49</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AF19" t="n">
         <v>0.11</v>
@@ -8385,70 +8385,70 @@
         <v>2.56</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.31</v>
+        <v>11.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO19" t="n">
         <v>0.88</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT19" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CC19" t="n">
         <v>3.29</v>
@@ -8460,10 +8460,10 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8472,7 +8472,7 @@
         <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK19" t="n">
         <v>1.42</v>
@@ -8487,13 +8487,13 @@
         <v>2.04</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CR19" t="n">
         <v>1.51</v>
@@ -8526,88 +8526,88 @@
         <v>2.02</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.12</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.75</v>
+        <v>6.59</v>
       </c>
       <c r="DL19" t="n">
         <v>0.06</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.25</v>
+        <v>42.29</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DP19" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="DQ19" t="n">
         <v>13.94</v>
       </c>
-      <c r="DQ19" t="n">
-        <v>13.62</v>
-      </c>
       <c r="DR19" t="n">
-        <v>7.06</v>
+        <v>7.36</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.88</v>
+        <v>52.94</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.75</v>
+        <v>7.88</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.87</v>
+        <v>17.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="20">
@@ -8617,94 +8617,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>116.25</v>
+        <v>113.89</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="L20" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="M20" t="n">
-        <v>63.75</v>
+        <v>61</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O20" t="n">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="P20" t="n">
-        <v>10.62</v>
+        <v>10.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>12.62</v>
+        <v>11.67</v>
       </c>
       <c r="R20" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>55.75</v>
+        <v>56</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>18.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.12</v>
+        <v>17.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8791,67 +8791,67 @@
         <v>2.94</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.19</v>
+        <v>9.35</v>
       </c>
       <c r="BI20" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BO20" t="n">
         <v>1.12</v>
       </c>
       <c r="BP20" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.19</v>
+        <v>3.88</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT20" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX20" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC20" t="n">
         <v>3.9</v>
@@ -8863,7 +8863,7 @@
         <v>1.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG20" t="n">
         <v>2.7</v>
@@ -8872,25 +8872,25 @@
         <v>1.36</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ20" t="n">
         <v>1.83</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP20" t="n">
         <v>2.07</v>
@@ -8905,7 +8905,7 @@
         <v>3.09</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU20" t="n">
         <v>1.4</v>
@@ -8941,43 +8941,43 @@
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.38</v>
+        <v>105.71</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="DM20" t="n">
-        <v>50.56</v>
+        <v>49.88</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.43</v>
+        <v>11.53</v>
       </c>
       <c r="DQ20" t="n">
-        <v>13.25</v>
+        <v>12.71</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="DS20" t="n">
         <v>0.06</v>
@@ -8989,28 +8989,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>53.88</v>
+        <v>54.12</v>
       </c>
       <c r="DW20" t="n">
         <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.56</v>
+        <v>17.35</v>
       </c>
       <c r="DY20" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.25</v>
+        <v>17.41</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="21">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -9032,82 +9032,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H21" t="n">
-        <v>88.14</v>
+        <v>84.75</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M21" t="n">
-        <v>33.71</v>
+        <v>32.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O21" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.29</v>
+        <v>13.88</v>
       </c>
       <c r="R21" t="n">
-        <v>7.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45</v>
+        <v>44.75</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.140000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>20.57</v>
+        <v>20.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9191,70 +9191,70 @@
         <v>2.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.07</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL21" t="n">
         <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR21" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS21" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV21" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX21" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BZ21" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC21" t="n">
         <v>5.44</v>
@@ -9266,7 +9266,7 @@
         <v>1.43</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG21" t="n">
         <v>2.64</v>
@@ -9275,16 +9275,16 @@
         <v>1.35</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM21" t="n">
         <v>2.52</v>
@@ -9299,7 +9299,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CR21" t="n">
         <v>1.47</v>
@@ -9326,7 +9326,7 @@
         <v>1.8</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA21" t="n">
         <v>1.99</v>
@@ -9335,85 +9335,85 @@
         <v>1.39</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DH21" t="n">
-        <v>83.33</v>
+        <v>81.94</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM21" t="n">
-        <v>32.33</v>
+        <v>31.94</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.34</v>
+        <v>12.5</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.6</v>
+        <v>14.82</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.4</v>
+        <v>8.75</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.26</v>
+        <v>44.18</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.54</v>
+        <v>10.38</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="EA21" t="n">
-        <v>16.8</v>
+        <v>16.94</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1460,136 +1460,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>91.56</v>
+        <v>91.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.33</v>
+        <v>39.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BP2" t="n">
         <v>4</v>
       </c>
-      <c r="BD2" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>3.94</v>
-      </c>
       <c r="BQ2" t="n">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY2" t="n">
         <v>2.37</v>
@@ -1598,16 +1598,16 @@
         <v>2.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
@@ -1616,13 +1616,13 @@
         <v>3.07</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.34</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.88</v>
@@ -1631,7 +1631,7 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM2" t="n">
         <v>2.59</v>
@@ -1640,13 +1640,13 @@
         <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,7 +1673,7 @@
         <v>1.73</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DA2" t="n">
         <v>2.08</v>
@@ -1682,52 +1682,52 @@
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.41</v>
+        <v>86.5</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.41</v>
+        <v>37.89</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.12</v>
+        <v>11.44</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.29</v>
+        <v>15.56</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DS2" t="n">
         <v>0.11</v>
@@ -1739,28 +1739,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>48.65</v>
+        <v>48.17</v>
       </c>
       <c r="DW2" t="n">
         <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.24</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.18</v>
+        <v>18.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="3">
@@ -1770,94 +1770,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>86</v>
+        <v>86.7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>36.11</v>
+        <v>36.9</v>
       </c>
       <c r="N3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.44</v>
+        <v>13.2</v>
       </c>
       <c r="R3" t="n">
-        <v>7.56</v>
+        <v>8.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.67</v>
+        <v>13.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.78</v>
+        <v>8.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.67</v>
+        <v>20.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
         <v>0.25</v>
@@ -1941,64 +1941,64 @@
         <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.65</v>
+        <v>9.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CA3" t="n">
         <v>3.35</v>
@@ -2016,49 +2016,49 @@
         <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK3" t="n">
         <v>1.42</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN3" t="n">
         <v>2.05</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CR3" t="n">
         <v>1.46</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2073,64 +2073,64 @@
         <v>1.5</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DH3" t="n">
-        <v>86.23999999999999</v>
+        <v>86.61</v>
       </c>
       <c r="DI3" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.47</v>
+        <v>37.83</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.41</v>
+        <v>14.22</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.58</v>
+        <v>12.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.3</v>
+        <v>7.61</v>
       </c>
       <c r="DS3" t="n">
         <v>0.17</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.36</v>
+        <v>48.45</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.23</v>
+        <v>12.28</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.23</v>
+        <v>7.44</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.59</v>
+        <v>19.61</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -2173,274 +2173,274 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
       <c r="E4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>0.12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="BA4" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>101.88</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M4" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P4" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>90.43000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.27</v>
+        <v>11.29</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM4" t="n">
         <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>5.88</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>86.67</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.33</v>
+        <v>58.82</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>23.53</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>70.59</v>
       </c>
       <c r="BY4" t="n">
         <v>1.98</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CA4" t="n">
         <v>3.41</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="CD4" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="CE4" t="n">
         <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK4" t="n">
         <v>1.42</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN4" t="n">
         <v>2.06</v>
@@ -2449,10 +2449,10 @@
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2461,7 +2461,7 @@
         <v>2.89</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CU4" t="n">
         <v>1.44</v>
@@ -2485,88 +2485,88 @@
         <v>2.07</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.54000000000001</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.53</v>
+        <v>5.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.26</v>
+        <v>45.71</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.27</v>
+        <v>14.41</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.6</v>
+        <v>15.35</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.47</v>
+        <v>7.41</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.13</v>
+        <v>54.24</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.27</v>
+        <v>13.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.93</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.8</v>
+        <v>18.71</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="5">
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2666,139 +2666,139 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.22</v>
+        <v>78.2</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>30.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.22</v>
+        <v>12.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.22</v>
+        <v>47.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>17.44</v>
+        <v>17.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN5" t="n">
         <v>2.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.81</v>
+        <v>4.94</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>2.39</v>
@@ -2807,40 +2807,40 @@
         <v>2.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.99</v>
+        <v>3.94</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
         <v>1.46</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM5" t="n">
         <v>2.54</v>
@@ -2852,10 +2852,10 @@
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
@@ -2879,64 +2879,64 @@
         <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>82.18000000000001</v>
+        <v>80.88</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.06</v>
+        <v>37</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.31</v>
+        <v>13.47</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2948,28 +2948,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.31</v>
+        <v>47.29</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.31</v>
+        <v>12.35</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.32</v>
+        <v>7.3</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.69</v>
+        <v>17.47</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -2991,82 +2991,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="H6" t="n">
-        <v>79.75</v>
+        <v>81.67</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="K6" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>49.75</v>
+        <v>51.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>14.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>12.44</v>
       </c>
       <c r="R6" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.62</v>
+        <v>51.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.62</v>
+        <v>16.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.75</v>
+        <v>11.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.25</v>
+        <v>17.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3105,7 +3105,7 @@
         <v>15.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.22</v>
+        <v>12.11</v>
       </c>
       <c r="AS6" t="n">
         <v>7.44</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49.56</v>
+        <v>49.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3150,70 +3150,70 @@
         <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.94</v>
+        <v>10.72</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CA6" t="n">
         <v>3.37</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CC6" t="n">
         <v>3.38</v>
@@ -3222,19 +3222,19 @@
         <v>3.67</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.86</v>
@@ -3246,19 +3246,19 @@
         <v>1.7</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3282,7 +3282,7 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
@@ -3294,85 +3294,85 @@
         <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.47</v>
+        <v>88</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.76</v>
+        <v>44.78</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.76</v>
+        <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.59</v>
+        <v>12.27</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.53</v>
+        <v>50.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.29</v>
+        <v>16.39</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.71</v>
+        <v>19.22</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="7">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3478,46 +3478,46 @@
         <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>71</v>
+        <v>76.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL7" t="n">
         <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.29</v>
+        <v>30.12</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.57</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3529,82 +3529,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>38.29</v>
+        <v>39.88</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.43</v>
+        <v>9.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.43</v>
+        <v>7.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.71</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.25</v>
+        <v>9.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
         <v>1.06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.69</v>
+        <v>4.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY7" t="n">
         <v>2.95</v>
@@ -3613,28 +3613,28 @@
         <v>3.22</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.53</v>
+        <v>7.59</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.68</v>
+        <v>8.59</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI7" t="n">
         <v>1.85</v>
@@ -3643,37 +3643,37 @@
         <v>1.86</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CO7" t="n">
         <v>1.29</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CT7" t="n">
         <v>3</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV7" t="n">
         <v>1.93</v>
@@ -3685,64 +3685,64 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.49</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.5</v>
+        <v>81.53</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="DL7" t="n">
         <v>0.06</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.13</v>
+        <v>34.12</v>
       </c>
       <c r="DN7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO7" t="n">
         <v>0.82</v>
       </c>
-      <c r="DO7" t="n">
-        <v>0.87</v>
-      </c>
       <c r="DP7" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="DR7" t="n">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3754,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.69</v>
+        <v>43.18</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.69</v>
+        <v>12.82</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.25</v>
+        <v>9.41</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.12</v>
+        <v>19.83</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="8">
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3878,49 +3878,49 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AI8" t="n">
-        <v>89.25</v>
+        <v>92</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.62</v>
+        <v>32.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.88</v>
+        <v>12.78</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>17.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>7.89</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3932,82 +3932,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>53.38</v>
+        <v>54</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>11.56</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.62</v>
+        <v>8.44</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.38</v>
+        <v>3.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>15.75</v>
+        <v>15.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.28</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT8" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.2</v>
@@ -4022,40 +4022,40 @@
         <v>3.22</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.98</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO8" t="n">
         <v>1.4</v>
@@ -4064,10 +4064,10 @@
         <v>2.3</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS8" t="n">
         <v>3.35</v>
@@ -4085,16 +4085,16 @@
         <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB8" t="n">
         <v>1.44</v>
@@ -4103,49 +4103,49 @@
         <v>2.39</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.12</v>
+        <v>94.28</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.53</v>
+        <v>4.72</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>34</v>
+        <v>34.39</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.3</v>
+        <v>13.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.47</v>
+        <v>16.83</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.119999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.94</v>
+        <v>54.22</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.12</v>
+        <v>11.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.06</v>
+        <v>17.89</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="9">
@@ -4188,61 +4188,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>72.56999999999999</v>
+        <v>74.25</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M9" t="n">
-        <v>27.43</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.43</v>
+        <v>13.88</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4254,118 +4254,118 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>38.57</v>
+        <v>39.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.29</v>
+        <v>10.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.06</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>63.22</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>31.33</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.5600000000000001</v>
@@ -4374,43 +4374,43 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.75</v>
+        <v>72.22</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>27.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.75</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
         <v>2.52</v>
@@ -4419,40 +4419,40 @@
         <v>2.63</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.73</v>
+        <v>4.9</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.44</v>
+        <v>5.83</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM9" t="n">
         <v>2.74</v>
@@ -4461,25 +4461,25 @@
         <v>2.08</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.06</v>
+        <v>3.97</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CV9" t="n">
         <v>1.81</v>
@@ -4488,67 +4488,67 @@
         <v>2.08</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DB9" t="n">
         <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="DH9" t="n">
-        <v>67.31</v>
+        <v>67.56</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DM9" t="n">
-        <v>29.62</v>
+        <v>30.56</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.19</v>
+        <v>10.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.5</v>
+        <v>12.61</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.619999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4560,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>38.44</v>
+        <v>38.72</v>
       </c>
       <c r="DW9" t="n">
         <v>0.5</v>
       </c>
       <c r="DX9" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.12</v>
+        <v>14.56</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="10">
@@ -4591,94 +4591,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>104.44</v>
+        <v>107.7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>43.67</v>
+        <v>48.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>14.11</v>
+        <v>13.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.89</v>
+        <v>14.9</v>
       </c>
       <c r="R10" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.78</v>
+        <v>58.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.11</v>
+        <v>10.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.22</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4762,70 +4762,70 @@
         <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC10" t="n">
         <v>3.43</v>
@@ -4837,10 +4837,10 @@
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH10" t="n">
         <v>1.36</v>
@@ -4852,16 +4852,16 @@
         <v>1.91</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO10" t="n">
         <v>1.33</v>
@@ -4870,7 +4870,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4879,7 +4879,7 @@
         <v>3.17</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
         <v>1.38</v>
@@ -4891,100 +4891,100 @@
         <v>2.07</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DH10" t="n">
-        <v>99.58</v>
+        <v>101.66</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.29</v>
+        <v>44.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.47</v>
+        <v>14.34</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.83</v>
+        <v>15.78</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.88</v>
+        <v>56.17</v>
       </c>
       <c r="DW10" t="n">
         <v>0.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.88</v>
+        <v>14.16</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.06</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.3</v>
+        <v>19.17</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="11">
@@ -4994,94 +4994,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="H11" t="n">
-        <v>116.71</v>
+        <v>119</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>56.57</v>
+        <v>58.38</v>
       </c>
       <c r="N11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O11" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>12.71</v>
+        <v>12.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.86</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>55.14</v>
+        <v>56</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.71</v>
+        <v>17.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.71</v>
+        <v>11.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5165,49 +5165,49 @@
         <v>2.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT11" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5216,19 +5216,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="CC11" t="n">
         <v>2.1</v>
@@ -5237,19 +5237,19 @@
         <v>2.09</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CH11" t="n">
         <v>1.38</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.96</v>
@@ -5261,31 +5261,31 @@
         <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
         <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
         <v>1.74</v>
@@ -5294,13 +5294,13 @@
         <v>2.16</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA11" t="n">
         <v>1.97</v>
@@ -5315,79 +5315,79 @@
         <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.19</v>
+        <v>107.88</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.5</v>
+        <v>48.88</v>
       </c>
       <c r="DN11" t="n">
         <v>1.06</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.63</v>
+        <v>12.48</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>12.35</v>
       </c>
       <c r="DR11" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>54.38</v>
+        <v>54.82</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.44</v>
+        <v>14.83</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.81</v>
+        <v>9.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.62</v>
+        <v>4.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5487,52 +5487,52 @@
         <v>2.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AO12" t="n">
         <v>1</v>
       </c>
-      <c r="AH12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>99.25</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AP12" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.25</v>
+        <v>13.11</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.62</v>
+        <v>8.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5544,82 +5544,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>61.5</v>
+        <v>59</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.25</v>
+        <v>12.89</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="BD12" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.59</v>
+        <v>9.56</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL12" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY12" t="n">
         <v>1.77</v>
@@ -5631,13 +5631,13 @@
         <v>3.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.23</v>
+        <v>3.37</v>
       </c>
       <c r="CE12" t="n">
         <v>1.43</v>
@@ -5661,10 +5661,10 @@
         <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
         <v>1.94</v>
@@ -5682,10 +5682,10 @@
         <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU12" t="n">
         <v>1.38</v>
@@ -5697,16 +5697,16 @@
         <v>2.01</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB12" t="n">
         <v>1.39</v>
@@ -5715,49 +5715,49 @@
         <v>2.21</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="DE12" t="n">
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DH12" t="n">
-        <v>103.82</v>
+        <v>101.11</v>
       </c>
       <c r="DI12" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>47.65</v>
+        <v>46.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.24</v>
+        <v>13.34</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.53</v>
+        <v>6.94</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>60.35</v>
+        <v>59.16</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.23</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.76</v>
+        <v>5.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.18</v>
+        <v>17.05</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="13">
@@ -5800,94 +5800,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F13" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="G13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>87.12</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.62</v>
-      </c>
       <c r="K13" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="L13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>13.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.62</v>
+        <v>12.56</v>
       </c>
       <c r="R13" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.62</v>
+        <v>47.78</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.88</v>
+        <v>14.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.88</v>
+        <v>14.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,70 +5971,70 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.35</v>
+        <v>8.56</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="BM13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.88</v>
-      </c>
       <c r="BP13" t="n">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BR13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT13" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="CC13" t="n">
         <v>4.5</v>
@@ -6043,52 +6043,52 @@
         <v>4.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI13" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CU13" t="n">
         <v>1.39</v>
@@ -6100,67 +6100,67 @@
         <v>1.87</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB13" t="n">
         <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH13" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.65</v>
+        <v>37.78</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.41</v>
+        <v>13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.94</v>
+        <v>13.34</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.65</v>
+        <v>8.77</v>
       </c>
       <c r="DS13" t="n">
         <v>0.06</v>
@@ -6172,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.94</v>
+        <v>49.44</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.3</v>
+        <v>11.34</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.7</v>
+        <v>7.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.12</v>
+        <v>15.83</v>
       </c>
       <c r="EB13" t="n">
         <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6293,52 +6293,52 @@
         <v>2.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>105</v>
+        <v>105.56</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>7.5</v>
+        <v>6.78</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN14" t="n">
-        <v>54.25</v>
+        <v>53</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.25</v>
+        <v>15.44</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6350,82 +6350,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.12</v>
+        <v>49.78</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.12</v>
+        <v>14.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.75</v>
+        <v>10.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BD14" t="n">
-        <v>22.5</v>
+        <v>22.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.29</v>
+        <v>11.06</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.29</v>
+        <v>5.11</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
         <v>1.96</v>
@@ -6434,16 +6434,16 @@
         <v>2.08</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
@@ -6452,7 +6452,7 @@
         <v>2.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH14" t="n">
         <v>1.38</v>
@@ -6467,13 +6467,13 @@
         <v>1.43</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CO14" t="n">
         <v>1.31</v>
@@ -6482,7 +6482,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CR14" t="n">
         <v>1.42</v>
@@ -6506,13 +6506,13 @@
         <v>1.48</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.53</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB14" t="n">
         <v>1.33</v>
@@ -6521,49 +6521,49 @@
         <v>2.06</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.29</v>
+        <v>107.44</v>
       </c>
       <c r="DI14" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.47</v>
+        <v>7.11</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DM14" t="n">
-        <v>55.29</v>
+        <v>54.61</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.59</v>
+        <v>15.66</v>
       </c>
       <c r="DQ14" t="n">
-        <v>14.24</v>
+        <v>14.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>7</v>
+        <v>7.34</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.06</v>
+        <v>50.84</v>
       </c>
       <c r="DW14" t="n">
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>15.64</v>
+        <v>15.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.59</v>
+        <v>10.33</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.71</v>
+        <v>20.72</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6699,136 +6699,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN15" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH15" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>53</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP15" t="n">
         <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY15" t="n">
         <v>2.08</v>
@@ -6843,34 +6843,34 @@
         <v>3.43</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ15" t="n">
         <v>1.88</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.87</v>
       </c>
       <c r="CK15" t="n">
         <v>1.36</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
         <v>2.86</v>
@@ -6882,22 +6882,22 @@
         <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="CR15" t="n">
         <v>1.45</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV15" t="n">
         <v>1.93</v>
@@ -6921,52 +6921,52 @@
         <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.94</v>
+        <v>92.23</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.5</v>
+        <v>43.88</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.63</v>
+        <v>12.53</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12</v>
+        <v>11.94</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.5</v>
+        <v>51.41</v>
       </c>
       <c r="DW15" t="n">
         <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="DY15" t="n">
-        <v>9.44</v>
+        <v>9.35</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.25</v>
+        <v>20.29</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="16">
@@ -7009,94 +7009,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="H16" t="n">
-        <v>89.38</v>
+        <v>89.67</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K16" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M16" t="n">
-        <v>42.88</v>
+        <v>43</v>
       </c>
       <c r="N16" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="P16" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.62</v>
+        <v>14</v>
       </c>
       <c r="R16" t="n">
-        <v>6.38</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.12</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.62</v>
+        <v>15.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.38</v>
+        <v>17.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7180,70 +7180,70 @@
         <v>2.78</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.35</v>
+        <v>11.94</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
         <v>1.06</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.41</v>
+        <v>5.17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.76</v>
+        <v>6.61</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="CC16" t="n">
         <v>2.62</v>
@@ -7252,19 +7252,19 @@
         <v>2.89</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.85</v>
@@ -7273,34 +7273,34 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CR16" t="n">
         <v>1.43</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="CT16" t="n">
         <v>2.97</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV16" t="n">
         <v>1.96</v>
@@ -7312,64 +7312,64 @@
         <v>1.47</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.54</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.53</v>
+        <v>84</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>39.35</v>
+        <v>39.61</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.65</v>
+        <v>13.39</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.23</v>
+        <v>13</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.59</v>
+        <v>7.84</v>
       </c>
       <c r="DS16" t="n">
         <v>0.06</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.41</v>
+        <v>49.39</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.65</v>
+        <v>8.66</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.18</v>
+        <v>17</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="17">
@@ -7412,61 +7412,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>82</v>
+        <v>83.22</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K17" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="L17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M17" t="n">
-        <v>33</v>
+        <v>33.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="P17" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.38</v>
+        <v>12.56</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7478,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39.62</v>
+        <v>39.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.62</v>
+        <v>17.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>2.11</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.94</v>
+        <v>11.06</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.29</v>
+        <v>5.39</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC17" t="n">
         <v>6.49</v>
@@ -7658,10 +7658,10 @@
         <v>1.38</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH17" t="n">
         <v>1.41</v>
@@ -7676,31 +7676,31 @@
         <v>1.34</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CO17" t="n">
         <v>1.28</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
@@ -7709,7 +7709,7 @@
         <v>1.94</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
@@ -7717,58 +7717,58 @@
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DB17" t="n">
         <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DH17" t="n">
-        <v>86.65000000000001</v>
+        <v>87</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>34.7</v>
+        <v>34.66</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.95</v>
+        <v>10.73</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.3</v>
+        <v>12.39</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7780,28 +7780,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42.76</v>
+        <v>42.62</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.35</v>
+        <v>12.16</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.59</v>
+        <v>18.12</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="18">
@@ -7811,94 +7811,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>98.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>5.22</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>42.33</v>
+        <v>40.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>12.67</v>
+        <v>13.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.78</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>6.11</v>
+        <v>6.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.22</v>
+        <v>50.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.67</v>
+        <v>10.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.11</v>
+        <v>18.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7967,85 +7967,85 @@
         <v>13.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BD18" t="n">
         <v>19.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BF18" t="n">
         <v>2.38</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX18" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CC18" t="n">
         <v>4.51</v>
@@ -8060,7 +8060,7 @@
         <v>2.91</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH18" t="n">
         <v>1.37</v>
@@ -8075,7 +8075,7 @@
         <v>1.39</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM18" t="n">
         <v>2.78</v>
@@ -8090,7 +8090,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CR18" t="n">
         <v>1.45</v>
@@ -8126,85 +8126,85 @@
         <v>1.35</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.52</v>
+        <v>94.55</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.23</v>
+        <v>41.44</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.88</v>
+        <v>12.17</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.53</v>
+        <v>13.22</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.23</v>
+        <v>7.44</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.58</v>
+        <v>48.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.18</v>
+        <v>11.78</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.949999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.65</v>
+        <v>18.89</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="19">
@@ -8214,13 +8214,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8304,139 +8304,139 @@
         <v>2.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>94</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.33</v>
+        <v>39</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.44</v>
+        <v>12.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.78</v>
+        <v>55.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.33</v>
+        <v>18.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.06</v>
+        <v>11.17</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY19" t="n">
         <v>2.22</v>
@@ -8445,16 +8445,16 @@
         <v>2.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="CE19" t="n">
         <v>1.45</v>
@@ -8466,25 +8466,25 @@
         <v>2.62</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK19" t="n">
         <v>1.42</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CO19" t="n">
         <v>1.36</v>
@@ -8493,16 +8493,16 @@
         <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CU19" t="n">
         <v>1.35</v>
@@ -8517,97 +8517,97 @@
         <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.48</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DE19" t="n">
         <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.76000000000001</v>
+        <v>90.16</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.59</v>
+        <v>6.61</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.29</v>
+        <v>42.44</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.94</v>
+        <v>13.56</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.36</v>
+        <v>7.34</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.94</v>
+        <v>53.34</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.88</v>
+        <v>7.72</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.11</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.29</v>
+        <v>17.66</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="20">
@@ -8617,94 +8617,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H20" t="n">
-        <v>113.89</v>
+        <v>116.1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.11</v>
+        <v>5.8</v>
       </c>
       <c r="L20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>60.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>10.89</v>
+        <v>11.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.67</v>
+        <v>13.2</v>
       </c>
       <c r="R20" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>56</v>
+        <v>56.6</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.44</v>
+        <v>19.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.22</v>
+        <v>12.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.44</v>
+        <v>17.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8788,70 +8788,70 @@
         <v>2.12</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.35</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BR20" t="n">
         <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT20" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV20" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX20" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>3.9</v>
@@ -8881,7 +8881,7 @@
         <v>1.46</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM20" t="n">
         <v>2.54</v>
@@ -8893,10 +8893,10 @@
         <v>1.32</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ20" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR20" t="n">
         <v>1.44</v>
@@ -8917,13 +8917,13 @@
         <v>1.87</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY20" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DA20" t="n">
         <v>2.02</v>
@@ -8932,52 +8932,52 @@
         <v>1.36</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="DE20" t="n">
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DH20" t="n">
-        <v>105.71</v>
+        <v>107.39</v>
       </c>
       <c r="DI20" t="n">
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.47</v>
+        <v>5.33</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.88</v>
+        <v>50.11</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.53</v>
+        <v>12</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.71</v>
+        <v>13.5</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.41</v>
+        <v>6.17</v>
       </c>
       <c r="DS20" t="n">
         <v>0.06</v>
@@ -8989,28 +8989,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>54.12</v>
+        <v>54.56</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>17.35</v>
+        <v>17.83</v>
       </c>
       <c r="DY20" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="DZ20" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="EA20" t="n">
-        <v>17.41</v>
+        <v>17.5</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -9020,13 +9020,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9086,25 +9086,25 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44.75</v>
+        <v>44.88</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.38</v>
+        <v>12.25</v>
       </c>
       <c r="AA21" t="n">
         <v>7.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="AC21" t="n">
         <v>20.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE21" t="n">
         <v>2.25</v>
@@ -9113,136 +9113,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>79.12</v>
+        <v>84.33</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AL21" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN21" t="n">
-        <v>31.12</v>
+        <v>32.89</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="AR21" t="n">
-        <v>15.75</v>
+        <v>15.89</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>43.62</v>
+        <v>45</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.380000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.38</v>
+        <v>6.22</v>
       </c>
       <c r="BC21" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="BD21" t="n">
-        <v>13.5</v>
+        <v>14.56</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.119999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ21" t="n">
         <v>1.06</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="BQ21" t="n">
         <v>5</v>
       </c>
       <c r="BR21" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS21" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV21" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX21" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY21" t="n">
         <v>2.82</v>
@@ -9251,16 +9251,16 @@
         <v>3</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CC21" t="n">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.16</v>
+        <v>6.11</v>
       </c>
       <c r="CE21" t="n">
         <v>1.43</v>
@@ -9269,7 +9269,7 @@
         <v>3.03</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH21" t="n">
         <v>1.35</v>
@@ -9287,10 +9287,10 @@
         <v>1.87</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO21" t="n">
         <v>1.34</v>
@@ -9299,7 +9299,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CR21" t="n">
         <v>1.47</v>
@@ -9335,85 +9335,85 @@
         <v>1.39</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="DH21" t="n">
-        <v>81.94</v>
+        <v>84.53</v>
       </c>
       <c r="DI21" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM21" t="n">
-        <v>31.94</v>
+        <v>32.82</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.5</v>
+        <v>12.23</v>
       </c>
       <c r="DQ21" t="n">
-        <v>14.82</v>
+        <v>14.94</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.75</v>
+        <v>8.35</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.18</v>
+        <v>44.94</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="DY21" t="n">
-        <v>6.5</v>
+        <v>6.88</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.88</v>
+        <v>4.12</v>
       </c>
       <c r="EA21" t="n">
-        <v>16.94</v>
+        <v>17.3</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
+++ b/data/teams/leagues/Averages_Brasileirão_Série_A_2026.xlsx
@@ -1673,7 +1673,7 @@
         <v>1.73</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DA2" t="n">
         <v>2.08</v>
@@ -2073,13 +2073,13 @@
         <v>1.5</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.47</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
@@ -3261,13 +3261,13 @@
         <v>3.67</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
@@ -4067,7 +4067,7 @@
         <v>4.32</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS8" t="n">
         <v>3.35</v>
@@ -4085,16 +4085,16 @@
         <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB8" t="n">
         <v>1.44</v>
@@ -4488,25 +4488,25 @@
         <v>2.08</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="DE9" t="n">
         <v>0.11</v>
@@ -5294,25 +5294,25 @@
         <v>2.16</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA11" t="n">
         <v>1.97</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="DE11" t="n">
         <v>0.29</v>
@@ -6085,10 +6085,10 @@
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CU13" t="n">
         <v>1.39</v>
@@ -6100,16 +6100,16 @@
         <v>1.87</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
         <v>1.34</v>
@@ -6488,13 +6488,13 @@
         <v>1.42</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CT14" t="n">
         <v>2.99</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV14" t="n">
         <v>2.07</v>
@@ -7478,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39.67</v>
+        <v>39.56</v>
       </c>
       <c r="Y17" t="n">
         <v>0.22</v>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>42.62</v>
+        <v>42.56</v>
       </c>
       <c r="DW17" t="n">
         <v>0.16</v>
@@ -8093,13 +8093,13 @@
         <v>3.5</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CU18" t="n">
         <v>1.38</v>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.1</v>
@@ -8586,7 +8586,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.34</v>
+        <v>53.39</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
@@ -8917,13 +8917,13 @@
         <v>1.87</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY20" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA20" t="n">
         <v>2.02</v>
@@ -9302,16 +9302,16 @@
         <v>3.78</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV21" t="n">
         <v>1.8</v>
@@ -9329,7 +9329,7 @@
         <v>2.48</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB21" t="n">
         <v>1.39</v>
